--- a/hema/3-单袋比.xlsx
+++ b/hema/3-单袋比.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="16360" activeTab="1"/>
+    <workbookView windowHeight="16760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="盘点表" sheetId="2" r:id="rId1"/>
@@ -17,7 +17,7 @@
     <sheet name="月报" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">盘点表!$A$7:$L$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">盘点表!$A$7:$K$88</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">单量排行榜!$A$2:$AB$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">耗材申请表!$A$1:$K$107</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">配送员履约明细表!$A$2:$AZ$1213</definedName>
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>购物袋差异</t>
   </si>
@@ -261,6 +261,9 @@
     <t>计费单量</t>
   </si>
   <si>
+    <t>须补数量</t>
+  </si>
+  <si>
     <t>当前时间</t>
   </si>
   <si>
@@ -291,6 +294,9 @@
     <t>购物袋-库存</t>
   </si>
   <si>
+    <t>库存实物</t>
+  </si>
+  <si>
     <t>库存应有</t>
   </si>
   <si>
@@ -309,6 +315,9 @@
     <t>白板</t>
   </si>
   <si>
+    <t>库存实物差</t>
+  </si>
+  <si>
     <t>实物数量</t>
   </si>
   <si>
@@ -319,19 +328,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="12">
+  <numFmts count="13">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="[DBNum1][$-804]m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="178" formatCode="0_ "/>
-    <numFmt numFmtId="179" formatCode="0.00_ "/>
-    <numFmt numFmtId="180" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="181" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="182" formatCode="&quot;需&quot;&quot;补&quot;\:???0;[Red]&quot;超&quot;&quot;标&quot;\:???0"/>
-    <numFmt numFmtId="183" formatCode="0&quot;单&quot;"/>
+    <numFmt numFmtId="177" formatCode="[Green]&quot;盈&quot;\:???0;[Red]&quot;亏&quot;\:???0"/>
+    <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="179" formatCode="0_ "/>
+    <numFmt numFmtId="180" formatCode="0.00_ "/>
+    <numFmt numFmtId="181" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+    <numFmt numFmtId="182" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="183" formatCode="&quot;需&quot;&quot;补&quot;\:???0;[Red]&quot;超&quot;&quot;标&quot;\:???0"/>
+    <numFmt numFmtId="184" formatCode="0&quot;单&quot;"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -342,32 +352,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="30"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Kaiti SC Regular"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="28"/>
+      <b/>
+      <sz val="30"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Kaiti SC Regular"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <sz val="30"/>
+      <color indexed="8"/>
+      <name val="Kaiti SC Regular"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="28"/>
-      <color indexed="8"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -423,6 +424,13 @@
       <sz val="36"/>
       <name val="黑体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -591,7 +599,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -627,7 +635,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,12 +643,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00B050"/>
         <bgColor rgb="FFFF0000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -682,6 +684,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -836,7 +844,9 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -857,9 +867,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -872,10 +880,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color auto="1"/>
-      </right>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -1024,19 +1032,19 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1045,7 +1053,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1069,16 +1077,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1087,16 +1095,16 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1168,100 +1176,100 @@
     <xf numFmtId="0" fontId="31" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="68">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="182" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1270,10 +1278,10 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1282,25 +1290,25 @@
     <xf numFmtId="176" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="58" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="58" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="9" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1315,110 +1323,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="179" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="180" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="183" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="13" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="184" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="183" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="182" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="183" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="1"/>
     </xf>
@@ -1857,95 +1865,94 @@
   <sheetFormatPr defaultColWidth="36.5" defaultRowHeight="28.8"/>
   <cols>
     <col min="1" max="1" width="13.2142857142857" style="44" customWidth="1"/>
-    <col min="2" max="2" width="16.0714285714286" style="44" customWidth="1"/>
+    <col min="2" max="2" width="15.7142857142857" style="44" customWidth="1"/>
     <col min="3" max="3" width="17.1428571428571" style="44" customWidth="1"/>
     <col min="4" max="5" width="12.1428571428571" style="44" customWidth="1"/>
-    <col min="6" max="6" width="19.5714285714286" style="45" customWidth="1"/>
+    <col min="6" max="6" width="19.2142857142857" style="45" customWidth="1"/>
     <col min="7" max="7" width="21.1428571428571" style="46" customWidth="1"/>
     <col min="8" max="8" width="15.7142857142857" style="44" customWidth="1"/>
     <col min="9" max="9" width="13.1607142857143" style="44" customWidth="1"/>
-    <col min="10" max="10" width="9.28571428571429" style="44" customWidth="1"/>
-    <col min="11" max="11" width="17.1428571428571" style="44" customWidth="1"/>
-    <col min="12" max="12" width="16.0714285714286" style="44" customWidth="1"/>
+    <col min="10" max="10" width="17.1428571428571" style="44" customWidth="1"/>
+    <col min="11" max="12" width="15.7142857142857" style="44" customWidth="1"/>
     <col min="13" max="16384" width="36.5" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="47">
         <f ca="1">TODAY()</f>
-        <v>45849</v>
+        <v>45983</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
       <c r="D1" s="47"/>
-      <c r="E1" s="55" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="56"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="64"/>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="48" t="s">
+      <c r="E1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="49"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="50"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="49">
+      <c r="B2" s="52">
         <v>1.3</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="50">
+      <c r="D2" s="53">
         <f>代码!K1</f>
         <v>0</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="57" t="s">
+      <c r="E2" s="53"/>
+      <c r="F2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="58">
+      <c r="G2" s="55">
         <f>代码!K2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="58"/>
-    </row>
-    <row r="3" s="41" customFormat="1" ht="51.2" spans="1:9">
-      <c r="A3" s="51" t="s">
+      <c r="H2" s="55"/>
+    </row>
+    <row r="3" s="41" customFormat="1" ht="51.2" spans="1:12">
+      <c r="A3" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
+      <c r="F3" s="56"/>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
       <c r="I3" s="44"/>
     </row>
     <row r="4" s="41" customFormat="1" ht="58" spans="1:12">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="52" t="s">
+      <c r="D4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="G4" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="57" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="44"/>
@@ -1960,22 +1967,22 @@
       </c>
     </row>
     <row r="5" s="42" customFormat="1" spans="1:12">
-      <c r="A5" s="53" t="s">
+      <c r="A5" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="50" t="e">
+      <c r="B5" s="53" t="e">
         <f>DGET(代码!$A$1:$H$300,B$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="C5" s="50" t="e">
+      <c r="C5" s="53" t="e">
         <f>DGET(代码!$A$1:$H$300,C$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="D5" s="50" t="e">
+      <c r="D5" s="53" t="e">
         <f>DGET(代码!$A$1:$H$300,D$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="E5" s="50" t="e">
+      <c r="E5" s="53" t="e">
         <f>DGET(代码!$A$1:$H$300,E$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
@@ -1983,18 +1990,18 @@
         <f>DGET(代码!$A$1:$H$300,F$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="G5" s="60" t="e">
+      <c r="G5" s="59" t="e">
         <f>DGET(代码!$A$1:$H$300,G$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H5" s="50" t="e">
+      <c r="H5" s="53" t="e">
         <f>DGET(代码!$A$1:$H$300,H$4,$A$4:$A$5)</f>
         <v>#VALUE!</v>
       </c>
       <c r="J5" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="65" t="e">
+      <c r="K5" s="62" t="e">
         <f>(B5+D5+F5)/B2+N("（需补数量+确认数量+当日申请）/单袋比")</f>
         <v>#VALUE!</v>
       </c>
@@ -2003,83 +2010,85 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="6" s="42" customFormat="1" spans="1:11">
-      <c r="A6" s="48"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
+    <row r="6" s="42" customFormat="1" spans="1:12">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
       <c r="I6" s="44"/>
       <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
     </row>
     <row r="7" s="43" customFormat="1" ht="66" customHeight="1" spans="1:12">
-      <c r="A7" s="54" t="str" cm="1">
+      <c r="A7" s="63" t="str" cm="1">
         <f t="array" ref="A7:H7">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(代码!A1:H300,代码!F1:F300&lt;&gt;0),6,-1)</f>
         <v>配送员名字</v>
       </c>
-      <c r="B7" s="54" t="str">
+      <c r="B7" s="63" t="str">
         <v>确认申领商品数量</v>
       </c>
-      <c r="C7" s="54" t="str">
+      <c r="C7" s="63" t="str">
         <v>o2o签收单量</v>
       </c>
-      <c r="D7" s="54" t="str">
+      <c r="D7" s="63" t="str">
         <v>今日
 已申请</v>
       </c>
-      <c r="E7" s="54" t="str">
+      <c r="E7" s="63" t="str">
         <v>今日
 配送单</v>
       </c>
-      <c r="F7" s="62" t="str">
+      <c r="F7" s="64" t="str">
         <v>需要
 申请数量</v>
       </c>
-      <c r="G7" s="63" t="str">
+      <c r="G7" s="65" t="str">
         <v>目前
 单袋比</v>
       </c>
-      <c r="H7" s="54" t="str">
+      <c r="H7" s="63" t="str">
         <v>当前状态</v>
       </c>
       <c r="I7" s="66"/>
-      <c r="K7" s="67" t="str" cm="1">
-        <f t="array" ref="K7:L7">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(代码!O1:P200,代码!P1:P200&lt;&gt;0),2,-1)</f>
+      <c r="J7" s="67" t="str" cm="1">
+        <f t="array" ref="J7:L7">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(代码!O1:Q200,代码!P1:P200&lt;&gt;0),2,-1)</f>
         <v>挂零人员</v>
       </c>
+      <c r="K7" s="43" t="str">
+        <v>计费单量</v>
+      </c>
       <c r="L7" s="43" t="str">
-        <v>计费单量</v>
-      </c>
-    </row>
-    <row r="8" spans="9:9">
+        <v>须补数量</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
       <c r="I8" s="43"/>
     </row>
-    <row r="9" spans="9:9">
+    <row r="9" spans="1:12">
       <c r="I9" s="43"/>
     </row>
-    <row r="10" spans="9:9">
+    <row r="10" spans="1:12">
       <c r="I10" s="43"/>
     </row>
-    <row r="11" spans="9:9">
+    <row r="11" spans="1:12">
       <c r="I11" s="43"/>
     </row>
-    <row r="12" spans="9:9">
+    <row r="12" spans="1:12">
       <c r="I12" s="43"/>
     </row>
-    <row r="13" spans="9:9">
+    <row r="13" spans="1:12">
       <c r="I13" s="43"/>
     </row>
-    <row r="14" spans="9:9">
+    <row r="14" spans="1:12">
       <c r="I14" s="43"/>
     </row>
-    <row r="15" spans="9:9">
+    <row r="15" spans="1:12">
       <c r="I15" s="43"/>
     </row>
-    <row r="16" spans="9:9">
+    <row r="16" spans="1:12">
       <c r="I16" s="43"/>
     </row>
     <row r="17" spans="9:9">
@@ -2303,7 +2312,7 @@
       <formula>NOT(ISERROR(SEARCH("缺勤",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="$A1:$XFD2 A3 M3:XFD4 I3:I4 $A7:$XFD1048576 A5:H5 K5:XFD5 I6:XFD6 J4:L4">
+  <conditionalFormatting sqref="$A1:$XFD2 A5:H5 A7:I1048576 A3 I3:I4 I6 J4 K4:L5 J6:XFD1048576 M3:XFD5 L3">
     <cfRule type="notContainsBlanks" dxfId="0" priority="23">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
@@ -2538,1291 +2547,1291 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="30"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="38"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
       <c r="J3" s="38"/>
-      <c r="K3" s="30"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="30"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="38"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
       <c r="J4" s="38"/>
-      <c r="K4" s="30"/>
+      <c r="K4" s="32"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="30"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="38"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="J5" s="38"/>
-      <c r="K5" s="30"/>
+      <c r="K5" s="32"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="30"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="38"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
       <c r="J6" s="38"/>
-      <c r="K6" s="30"/>
+      <c r="K6" s="32"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="30"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="38"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
       <c r="J7" s="38"/>
-      <c r="K7" s="30"/>
+      <c r="K7" s="32"/>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="30"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="38"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
       <c r="J8" s="38"/>
-      <c r="K8" s="30"/>
+      <c r="K8" s="32"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="30"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="38"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
       <c r="J9" s="38"/>
-      <c r="K9" s="30"/>
+      <c r="K9" s="32"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="30"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="38"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="38"/>
-      <c r="K10" s="30"/>
+      <c r="K10" s="32"/>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="30"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="38"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
       <c r="J11" s="38"/>
-      <c r="K11" s="30"/>
+      <c r="K11" s="32"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="30"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="38"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="30"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
       <c r="J12" s="38"/>
-      <c r="K12" s="30"/>
+      <c r="K12" s="32"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="30"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="38"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
       <c r="J13" s="38"/>
-      <c r="K13" s="30"/>
+      <c r="K13" s="32"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="30"/>
+      <c r="A14" s="32"/>
       <c r="B14" s="38"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="30"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
       <c r="J14" s="38"/>
-      <c r="K14" s="30"/>
+      <c r="K14" s="32"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="30"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="38"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="30"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
       <c r="J15" s="38"/>
-      <c r="K15" s="30"/>
+      <c r="K15" s="32"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="30"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="38"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
       <c r="J16" s="38"/>
-      <c r="K16" s="30"/>
+      <c r="K16" s="32"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="30"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="38"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
       <c r="J17" s="38"/>
-      <c r="K17" s="30"/>
+      <c r="K17" s="32"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="30"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="38"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
       <c r="J18" s="38"/>
-      <c r="K18" s="30"/>
+      <c r="K18" s="32"/>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="30"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="38"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
       <c r="J19" s="38"/>
-      <c r="K19" s="30"/>
+      <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="30"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="38"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
       <c r="J20" s="38"/>
-      <c r="K20" s="30"/>
+      <c r="K20" s="32"/>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="30"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="38"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
       <c r="J21" s="38"/>
-      <c r="K21" s="30"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="30"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="38"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
       <c r="J22" s="38"/>
-      <c r="K22" s="30"/>
+      <c r="K22" s="32"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="30"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="38"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
       <c r="J23" s="38"/>
-      <c r="K23" s="30"/>
+      <c r="K23" s="32"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="30"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="38"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
       <c r="J24" s="38"/>
-      <c r="K24" s="30"/>
+      <c r="K24" s="32"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="30"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="38"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
       <c r="J25" s="38"/>
-      <c r="K25" s="30"/>
+      <c r="K25" s="32"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="30"/>
+      <c r="A26" s="32"/>
       <c r="B26" s="38"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
       <c r="J26" s="38"/>
-      <c r="K26" s="30"/>
+      <c r="K26" s="32"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="30"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="38"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
       <c r="J27" s="38"/>
-      <c r="K27" s="30"/>
+      <c r="K27" s="32"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="30"/>
+      <c r="A28" s="32"/>
       <c r="B28" s="38"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
       <c r="J28" s="38"/>
-      <c r="K28" s="30"/>
+      <c r="K28" s="32"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="30"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="38"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
       <c r="J29" s="38"/>
-      <c r="K29" s="30"/>
+      <c r="K29" s="32"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="30"/>
+      <c r="A30" s="32"/>
       <c r="B30" s="38"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
       <c r="J30" s="38"/>
-      <c r="K30" s="30"/>
+      <c r="K30" s="32"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="30"/>
+      <c r="A31" s="32"/>
       <c r="B31" s="38"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
       <c r="J31" s="38"/>
-      <c r="K31" s="30"/>
+      <c r="K31" s="32"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="30"/>
+      <c r="A32" s="32"/>
       <c r="B32" s="38"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
       <c r="J32" s="38"/>
-      <c r="K32" s="30"/>
+      <c r="K32" s="32"/>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="30"/>
+      <c r="A33" s="32"/>
       <c r="B33" s="38"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="30"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
       <c r="J33" s="38"/>
-      <c r="K33" s="30"/>
+      <c r="K33" s="32"/>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="30"/>
+      <c r="A34" s="32"/>
       <c r="B34" s="38"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="30"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
       <c r="J34" s="38"/>
-      <c r="K34" s="30"/>
+      <c r="K34" s="32"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="30"/>
+      <c r="A35" s="32"/>
       <c r="B35" s="38"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="30"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
       <c r="J35" s="38"/>
-      <c r="K35" s="30"/>
+      <c r="K35" s="32"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="30"/>
+      <c r="A36" s="32"/>
       <c r="B36" s="38"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="30"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
       <c r="J36" s="38"/>
-      <c r="K36" s="30"/>
+      <c r="K36" s="32"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="30"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="38"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
       <c r="J37" s="38"/>
-      <c r="K37" s="30"/>
+      <c r="K37" s="32"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="30"/>
+      <c r="A38" s="32"/>
       <c r="B38" s="38"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
       <c r="J38" s="38"/>
-      <c r="K38" s="30"/>
+      <c r="K38" s="32"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="30"/>
+      <c r="A39" s="32"/>
       <c r="B39" s="38"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="30"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
       <c r="J39" s="38"/>
-      <c r="K39" s="30"/>
+      <c r="K39" s="32"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="30"/>
+      <c r="A40" s="32"/>
       <c r="B40" s="38"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
       <c r="J40" s="38"/>
-      <c r="K40" s="30"/>
+      <c r="K40" s="32"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="30"/>
+      <c r="A41" s="32"/>
       <c r="B41" s="38"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="30"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
       <c r="J41" s="38"/>
-      <c r="K41" s="30"/>
+      <c r="K41" s="32"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="30"/>
+      <c r="A42" s="32"/>
       <c r="B42" s="38"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="30"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
       <c r="J42" s="38"/>
-      <c r="K42" s="30"/>
+      <c r="K42" s="32"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="30"/>
+      <c r="A43" s="32"/>
       <c r="B43" s="38"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
       <c r="J43" s="38"/>
-      <c r="K43" s="30"/>
+      <c r="K43" s="32"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="30"/>
+      <c r="A44" s="32"/>
       <c r="B44" s="38"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="30"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="30"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
       <c r="J44" s="38"/>
-      <c r="K44" s="30"/>
+      <c r="K44" s="32"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="30"/>
+      <c r="A45" s="32"/>
       <c r="B45" s="38"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="30"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="32"/>
       <c r="J45" s="38"/>
-      <c r="K45" s="30"/>
+      <c r="K45" s="32"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="30"/>
+      <c r="A46" s="32"/>
       <c r="B46" s="38"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
       <c r="J46" s="38"/>
-      <c r="K46" s="30"/>
+      <c r="K46" s="32"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="30"/>
+      <c r="A47" s="32"/>
       <c r="B47" s="38"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="30"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="32"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
       <c r="J47" s="38"/>
-      <c r="K47" s="30"/>
+      <c r="K47" s="32"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="30"/>
+      <c r="A48" s="32"/>
       <c r="B48" s="38"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
       <c r="J48" s="38"/>
-      <c r="K48" s="30"/>
+      <c r="K48" s="32"/>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="30"/>
+      <c r="A49" s="32"/>
       <c r="B49" s="38"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
       <c r="J49" s="38"/>
-      <c r="K49" s="30"/>
+      <c r="K49" s="32"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="30"/>
+      <c r="A50" s="32"/>
       <c r="B50" s="38"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="30"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
       <c r="J50" s="38"/>
-      <c r="K50" s="30"/>
+      <c r="K50" s="32"/>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="30"/>
+      <c r="A51" s="32"/>
       <c r="B51" s="38"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="30"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
       <c r="J51" s="38"/>
-      <c r="K51" s="30"/>
+      <c r="K51" s="32"/>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="30"/>
+      <c r="A52" s="32"/>
       <c r="B52" s="38"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
       <c r="J52" s="38"/>
-      <c r="K52" s="30"/>
+      <c r="K52" s="32"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="30"/>
+      <c r="A53" s="32"/>
       <c r="B53" s="38"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="30"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="32"/>
       <c r="J53" s="38"/>
-      <c r="K53" s="30"/>
+      <c r="K53" s="32"/>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="30"/>
+      <c r="A54" s="32"/>
       <c r="B54" s="38"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
       <c r="J54" s="38"/>
-      <c r="K54" s="30"/>
+      <c r="K54" s="32"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="30"/>
+      <c r="A55" s="32"/>
       <c r="B55" s="38"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
       <c r="J55" s="38"/>
-      <c r="K55" s="30"/>
+      <c r="K55" s="32"/>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="30"/>
+      <c r="A56" s="32"/>
       <c r="B56" s="38"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="30"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
       <c r="J56" s="38"/>
-      <c r="K56" s="30"/>
+      <c r="K56" s="32"/>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="30"/>
+      <c r="A57" s="32"/>
       <c r="B57" s="38"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="30"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
       <c r="J57" s="38"/>
-      <c r="K57" s="30"/>
+      <c r="K57" s="32"/>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="30"/>
+      <c r="A58" s="32"/>
       <c r="B58" s="38"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
       <c r="J58" s="38"/>
-      <c r="K58" s="30"/>
+      <c r="K58" s="32"/>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="30"/>
+      <c r="A59" s="32"/>
       <c r="B59" s="38"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="30"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
       <c r="J59" s="38"/>
-      <c r="K59" s="30"/>
+      <c r="K59" s="32"/>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="30"/>
+      <c r="A60" s="32"/>
       <c r="B60" s="38"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="30"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="32"/>
       <c r="J60" s="38"/>
-      <c r="K60" s="30"/>
+      <c r="K60" s="32"/>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="30"/>
+      <c r="A61" s="32"/>
       <c r="B61" s="38"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="32"/>
       <c r="J61" s="38"/>
-      <c r="K61" s="30"/>
+      <c r="K61" s="32"/>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="30"/>
+      <c r="A62" s="32"/>
       <c r="B62" s="38"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="30"/>
-      <c r="H62" s="30"/>
-      <c r="I62" s="30"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="32"/>
       <c r="J62" s="38"/>
-      <c r="K62" s="30"/>
+      <c r="K62" s="32"/>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="30"/>
+      <c r="A63" s="32"/>
       <c r="B63" s="38"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="30"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="32"/>
       <c r="J63" s="38"/>
-      <c r="K63" s="30"/>
+      <c r="K63" s="32"/>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="30"/>
+      <c r="A64" s="32"/>
       <c r="B64" s="38"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
       <c r="J64" s="38"/>
-      <c r="K64" s="30"/>
+      <c r="K64" s="32"/>
     </row>
     <row r="65" spans="1:11">
-      <c r="A65" s="30"/>
+      <c r="A65" s="32"/>
       <c r="B65" s="38"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="30"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="32"/>
       <c r="J65" s="38"/>
-      <c r="K65" s="30"/>
+      <c r="K65" s="32"/>
     </row>
     <row r="66" spans="1:11">
-      <c r="A66" s="30"/>
+      <c r="A66" s="32"/>
       <c r="B66" s="38"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="30"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="32"/>
       <c r="J66" s="38"/>
-      <c r="K66" s="30"/>
+      <c r="K66" s="32"/>
     </row>
     <row r="67" spans="1:11">
-      <c r="A67" s="30"/>
+      <c r="A67" s="32"/>
       <c r="B67" s="38"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="32"/>
       <c r="J67" s="38"/>
-      <c r="K67" s="30"/>
+      <c r="K67" s="32"/>
     </row>
     <row r="68" spans="1:11">
-      <c r="A68" s="30"/>
+      <c r="A68" s="32"/>
       <c r="B68" s="38"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="32"/>
       <c r="J68" s="38"/>
-      <c r="K68" s="30"/>
+      <c r="K68" s="32"/>
     </row>
     <row r="69" spans="1:11">
-      <c r="A69" s="30"/>
+      <c r="A69" s="32"/>
       <c r="B69" s="38"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="30"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="32"/>
       <c r="J69" s="38"/>
-      <c r="K69" s="30"/>
+      <c r="K69" s="32"/>
     </row>
     <row r="70" spans="1:11">
-      <c r="A70" s="30"/>
+      <c r="A70" s="32"/>
       <c r="B70" s="38"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="32"/>
       <c r="J70" s="38"/>
-      <c r="K70" s="30"/>
+      <c r="K70" s="32"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="30"/>
+      <c r="A71" s="32"/>
       <c r="B71" s="38"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="32"/>
       <c r="J71" s="38"/>
-      <c r="K71" s="30"/>
+      <c r="K71" s="32"/>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="30"/>
+      <c r="A72" s="32"/>
       <c r="B72" s="38"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
       <c r="J72" s="38"/>
-      <c r="K72" s="30"/>
+      <c r="K72" s="32"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="30"/>
+      <c r="A73" s="32"/>
       <c r="B73" s="38"/>
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="32"/>
       <c r="J73" s="38"/>
-      <c r="K73" s="30"/>
+      <c r="K73" s="32"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="30"/>
+      <c r="A74" s="32"/>
       <c r="B74" s="38"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="32"/>
       <c r="J74" s="38"/>
-      <c r="K74" s="30"/>
+      <c r="K74" s="32"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="30"/>
+      <c r="A75" s="32"/>
       <c r="B75" s="38"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="32"/>
       <c r="J75" s="38"/>
-      <c r="K75" s="30"/>
+      <c r="K75" s="32"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="30"/>
+      <c r="A76" s="32"/>
       <c r="B76" s="38"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="32"/>
       <c r="J76" s="38"/>
-      <c r="K76" s="30"/>
+      <c r="K76" s="32"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="30"/>
+      <c r="A77" s="32"/>
       <c r="B77" s="38"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="30"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
       <c r="J77" s="38"/>
-      <c r="K77" s="30"/>
+      <c r="K77" s="32"/>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="30"/>
+      <c r="A78" s="32"/>
       <c r="B78" s="38"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="30"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
       <c r="J78" s="38"/>
-      <c r="K78" s="30"/>
+      <c r="K78" s="32"/>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="30"/>
+      <c r="A79" s="32"/>
       <c r="B79" s="38"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
       <c r="J79" s="38"/>
-      <c r="K79" s="30"/>
+      <c r="K79" s="32"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="30"/>
+      <c r="A80" s="32"/>
       <c r="B80" s="38"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="30"/>
-      <c r="H80" s="30"/>
-      <c r="I80" s="30"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="32"/>
       <c r="J80" s="38"/>
-      <c r="K80" s="30"/>
+      <c r="K80" s="32"/>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="30"/>
+      <c r="A81" s="32"/>
       <c r="B81" s="38"/>
-      <c r="C81" s="30"/>
-      <c r="D81" s="30"/>
-      <c r="E81" s="30"/>
-      <c r="F81" s="30"/>
-      <c r="G81" s="30"/>
-      <c r="H81" s="30"/>
-      <c r="I81" s="30"/>
+      <c r="C81" s="32"/>
+      <c r="D81" s="32"/>
+      <c r="E81" s="32"/>
+      <c r="F81" s="32"/>
+      <c r="G81" s="32"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="32"/>
       <c r="J81" s="38"/>
-      <c r="K81" s="30"/>
+      <c r="K81" s="32"/>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="30"/>
+      <c r="A82" s="32"/>
       <c r="B82" s="38"/>
-      <c r="C82" s="30"/>
-      <c r="D82" s="30"/>
-      <c r="E82" s="30"/>
-      <c r="F82" s="30"/>
-      <c r="G82" s="30"/>
-      <c r="H82" s="30"/>
-      <c r="I82" s="30"/>
+      <c r="C82" s="32"/>
+      <c r="D82" s="32"/>
+      <c r="E82" s="32"/>
+      <c r="F82" s="32"/>
+      <c r="G82" s="32"/>
+      <c r="H82" s="32"/>
+      <c r="I82" s="32"/>
       <c r="J82" s="38"/>
-      <c r="K82" s="30"/>
+      <c r="K82" s="32"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="30"/>
+      <c r="A83" s="32"/>
       <c r="B83" s="38"/>
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-      <c r="F83" s="30"/>
-      <c r="G83" s="30"/>
-      <c r="H83" s="30"/>
-      <c r="I83" s="30"/>
+      <c r="C83" s="32"/>
+      <c r="D83" s="32"/>
+      <c r="E83" s="32"/>
+      <c r="F83" s="32"/>
+      <c r="G83" s="32"/>
+      <c r="H83" s="32"/>
+      <c r="I83" s="32"/>
       <c r="J83" s="38"/>
-      <c r="K83" s="30"/>
+      <c r="K83" s="32"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="30"/>
+      <c r="A84" s="32"/>
       <c r="B84" s="38"/>
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-      <c r="F84" s="30"/>
-      <c r="G84" s="30"/>
-      <c r="H84" s="30"/>
-      <c r="I84" s="30"/>
+      <c r="C84" s="32"/>
+      <c r="D84" s="32"/>
+      <c r="E84" s="32"/>
+      <c r="F84" s="32"/>
+      <c r="G84" s="32"/>
+      <c r="H84" s="32"/>
+      <c r="I84" s="32"/>
       <c r="J84" s="38"/>
-      <c r="K84" s="30"/>
+      <c r="K84" s="32"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="30"/>
+      <c r="A85" s="32"/>
       <c r="B85" s="38"/>
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-      <c r="F85" s="30"/>
-      <c r="G85" s="30"/>
-      <c r="H85" s="30"/>
-      <c r="I85" s="30"/>
+      <c r="C85" s="32"/>
+      <c r="D85" s="32"/>
+      <c r="E85" s="32"/>
+      <c r="F85" s="32"/>
+      <c r="G85" s="32"/>
+      <c r="H85" s="32"/>
+      <c r="I85" s="32"/>
       <c r="J85" s="38"/>
-      <c r="K85" s="30"/>
+      <c r="K85" s="32"/>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="30"/>
+      <c r="A86" s="32"/>
       <c r="B86" s="38"/>
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-      <c r="F86" s="30"/>
-      <c r="G86" s="30"/>
-      <c r="H86" s="30"/>
-      <c r="I86" s="30"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
       <c r="J86" s="38"/>
-      <c r="K86" s="30"/>
+      <c r="K86" s="32"/>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="30"/>
+      <c r="A87" s="32"/>
       <c r="B87" s="38"/>
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-      <c r="F87" s="30"/>
-      <c r="G87" s="30"/>
-      <c r="H87" s="30"/>
-      <c r="I87" s="30"/>
+      <c r="C87" s="32"/>
+      <c r="D87" s="32"/>
+      <c r="E87" s="32"/>
+      <c r="F87" s="32"/>
+      <c r="G87" s="32"/>
+      <c r="H87" s="32"/>
+      <c r="I87" s="32"/>
       <c r="J87" s="38"/>
-      <c r="K87" s="30"/>
+      <c r="K87" s="32"/>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="30"/>
+      <c r="A88" s="32"/>
       <c r="B88" s="38"/>
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-      <c r="F88" s="30"/>
-      <c r="G88" s="30"/>
-      <c r="H88" s="30"/>
-      <c r="I88" s="30"/>
+      <c r="C88" s="32"/>
+      <c r="D88" s="32"/>
+      <c r="E88" s="32"/>
+      <c r="F88" s="32"/>
+      <c r="G88" s="32"/>
+      <c r="H88" s="32"/>
+      <c r="I88" s="32"/>
       <c r="J88" s="38"/>
-      <c r="K88" s="30"/>
+      <c r="K88" s="32"/>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="30"/>
+      <c r="A89" s="32"/>
       <c r="B89" s="38"/>
-      <c r="C89" s="30"/>
-      <c r="D89" s="30"/>
-      <c r="E89" s="30"/>
-      <c r="F89" s="30"/>
-      <c r="G89" s="30"/>
-      <c r="H89" s="30"/>
-      <c r="I89" s="30"/>
+      <c r="C89" s="32"/>
+      <c r="D89" s="32"/>
+      <c r="E89" s="32"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="32"/>
+      <c r="H89" s="32"/>
+      <c r="I89" s="32"/>
       <c r="J89" s="38"/>
-      <c r="K89" s="30"/>
+      <c r="K89" s="32"/>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="30"/>
+      <c r="A90" s="32"/>
       <c r="B90" s="38"/>
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="30"/>
-      <c r="F90" s="30"/>
-      <c r="G90" s="30"/>
-      <c r="H90" s="30"/>
-      <c r="I90" s="30"/>
+      <c r="C90" s="32"/>
+      <c r="D90" s="32"/>
+      <c r="E90" s="32"/>
+      <c r="F90" s="32"/>
+      <c r="G90" s="32"/>
+      <c r="H90" s="32"/>
+      <c r="I90" s="32"/>
       <c r="J90" s="38"/>
-      <c r="K90" s="30"/>
+      <c r="K90" s="32"/>
     </row>
     <row r="91" spans="1:11">
-      <c r="A91" s="30"/>
+      <c r="A91" s="32"/>
       <c r="B91" s="38"/>
-      <c r="C91" s="30"/>
-      <c r="D91" s="30"/>
-      <c r="E91" s="30"/>
-      <c r="F91" s="30"/>
-      <c r="G91" s="30"/>
-      <c r="H91" s="30"/>
-      <c r="I91" s="30"/>
+      <c r="C91" s="32"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="32"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="32"/>
+      <c r="H91" s="32"/>
+      <c r="I91" s="32"/>
       <c r="J91" s="38"/>
-      <c r="K91" s="30"/>
+      <c r="K91" s="32"/>
     </row>
     <row r="92" spans="1:11">
-      <c r="A92" s="30"/>
+      <c r="A92" s="32"/>
       <c r="B92" s="38"/>
-      <c r="C92" s="30"/>
-      <c r="D92" s="30"/>
-      <c r="E92" s="30"/>
-      <c r="F92" s="30"/>
-      <c r="G92" s="30"/>
-      <c r="H92" s="30"/>
-      <c r="I92" s="30"/>
+      <c r="C92" s="32"/>
+      <c r="D92" s="32"/>
+      <c r="E92" s="32"/>
+      <c r="F92" s="32"/>
+      <c r="G92" s="32"/>
+      <c r="H92" s="32"/>
+      <c r="I92" s="32"/>
       <c r="J92" s="38"/>
-      <c r="K92" s="30"/>
+      <c r="K92" s="32"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="30"/>
+      <c r="A93" s="32"/>
       <c r="B93" s="38"/>
-      <c r="C93" s="30"/>
-      <c r="D93" s="30"/>
-      <c r="E93" s="30"/>
-      <c r="F93" s="30"/>
-      <c r="G93" s="30"/>
-      <c r="H93" s="30"/>
-      <c r="I93" s="30"/>
+      <c r="C93" s="32"/>
+      <c r="D93" s="32"/>
+      <c r="E93" s="32"/>
+      <c r="F93" s="32"/>
+      <c r="G93" s="32"/>
+      <c r="H93" s="32"/>
+      <c r="I93" s="32"/>
       <c r="J93" s="38"/>
-      <c r="K93" s="30"/>
+      <c r="K93" s="32"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="30"/>
+      <c r="A94" s="32"/>
       <c r="B94" s="38"/>
-      <c r="C94" s="30"/>
-      <c r="D94" s="30"/>
-      <c r="E94" s="30"/>
-      <c r="F94" s="30"/>
-      <c r="G94" s="30"/>
-      <c r="H94" s="30"/>
-      <c r="I94" s="30"/>
+      <c r="C94" s="32"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="32"/>
+      <c r="F94" s="32"/>
+      <c r="G94" s="32"/>
+      <c r="H94" s="32"/>
+      <c r="I94" s="32"/>
       <c r="J94" s="38"/>
-      <c r="K94" s="30"/>
+      <c r="K94" s="32"/>
     </row>
     <row r="95" spans="1:11">
-      <c r="A95" s="30"/>
+      <c r="A95" s="32"/>
       <c r="B95" s="38"/>
-      <c r="C95" s="30"/>
-      <c r="D95" s="30"/>
-      <c r="E95" s="30"/>
-      <c r="F95" s="30"/>
-      <c r="G95" s="30"/>
-      <c r="H95" s="30"/>
-      <c r="I95" s="30"/>
+      <c r="C95" s="32"/>
+      <c r="D95" s="32"/>
+      <c r="E95" s="32"/>
+      <c r="F95" s="32"/>
+      <c r="G95" s="32"/>
+      <c r="H95" s="32"/>
+      <c r="I95" s="32"/>
       <c r="J95" s="38"/>
-      <c r="K95" s="30"/>
+      <c r="K95" s="32"/>
     </row>
     <row r="96" spans="1:11">
-      <c r="A96" s="30"/>
+      <c r="A96" s="32"/>
       <c r="B96" s="38"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="30"/>
-      <c r="E96" s="30"/>
-      <c r="F96" s="30"/>
-      <c r="G96" s="30"/>
-      <c r="H96" s="30"/>
-      <c r="I96" s="30"/>
+      <c r="C96" s="32"/>
+      <c r="D96" s="32"/>
+      <c r="E96" s="32"/>
+      <c r="F96" s="32"/>
+      <c r="G96" s="32"/>
+      <c r="H96" s="32"/>
+      <c r="I96" s="32"/>
       <c r="J96" s="38"/>
-      <c r="K96" s="30"/>
+      <c r="K96" s="32"/>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="30"/>
+      <c r="A97" s="32"/>
       <c r="B97" s="38"/>
-      <c r="C97" s="30"/>
-      <c r="D97" s="30"/>
-      <c r="E97" s="30"/>
-      <c r="F97" s="30"/>
-      <c r="G97" s="30"/>
-      <c r="H97" s="30"/>
-      <c r="I97" s="30"/>
+      <c r="C97" s="32"/>
+      <c r="D97" s="32"/>
+      <c r="E97" s="32"/>
+      <c r="F97" s="32"/>
+      <c r="G97" s="32"/>
+      <c r="H97" s="32"/>
+      <c r="I97" s="32"/>
       <c r="J97" s="38"/>
-      <c r="K97" s="30"/>
+      <c r="K97" s="32"/>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="30"/>
+      <c r="A98" s="32"/>
       <c r="B98" s="38"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="30"/>
-      <c r="E98" s="30"/>
-      <c r="F98" s="30"/>
-      <c r="G98" s="30"/>
-      <c r="H98" s="30"/>
-      <c r="I98" s="30"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="32"/>
+      <c r="G98" s="32"/>
+      <c r="H98" s="32"/>
+      <c r="I98" s="32"/>
       <c r="J98" s="38"/>
-      <c r="K98" s="30"/>
+      <c r="K98" s="32"/>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" s="30"/>
+      <c r="A99" s="32"/>
       <c r="B99" s="38"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="30"/>
-      <c r="E99" s="30"/>
-      <c r="F99" s="30"/>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="30"/>
+      <c r="C99" s="32"/>
+      <c r="D99" s="32"/>
+      <c r="E99" s="32"/>
+      <c r="F99" s="32"/>
+      <c r="G99" s="32"/>
+      <c r="H99" s="32"/>
+      <c r="I99" s="32"/>
       <c r="J99" s="38"/>
-      <c r="K99" s="30"/>
+      <c r="K99" s="32"/>
     </row>
     <row r="100" spans="1:11">
-      <c r="A100" s="30"/>
+      <c r="A100" s="32"/>
       <c r="B100" s="38"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="30"/>
-      <c r="E100" s="30"/>
-      <c r="F100" s="30"/>
-      <c r="G100" s="30"/>
-      <c r="H100" s="30"/>
-      <c r="I100" s="30"/>
+      <c r="C100" s="32"/>
+      <c r="D100" s="32"/>
+      <c r="E100" s="32"/>
+      <c r="F100" s="32"/>
+      <c r="G100" s="32"/>
+      <c r="H100" s="32"/>
+      <c r="I100" s="32"/>
       <c r="J100" s="38"/>
-      <c r="K100" s="30"/>
+      <c r="K100" s="32"/>
     </row>
     <row r="101" spans="1:11">
-      <c r="A101" s="30"/>
+      <c r="A101" s="32"/>
       <c r="B101" s="38"/>
-      <c r="C101" s="30"/>
-      <c r="D101" s="30"/>
-      <c r="E101" s="30"/>
-      <c r="F101" s="30"/>
-      <c r="G101" s="30"/>
-      <c r="H101" s="30"/>
-      <c r="I101" s="30"/>
+      <c r="C101" s="32"/>
+      <c r="D101" s="32"/>
+      <c r="E101" s="32"/>
+      <c r="F101" s="32"/>
+      <c r="G101" s="32"/>
+      <c r="H101" s="32"/>
+      <c r="I101" s="32"/>
       <c r="J101" s="38"/>
-      <c r="K101" s="30"/>
+      <c r="K101" s="32"/>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="27"/>
@@ -3864,550 +3873,550 @@
       <c r="K104" s="28"/>
     </row>
     <row r="105" spans="1:11">
-      <c r="A105" s="30"/>
+      <c r="A105" s="32"/>
       <c r="B105" s="38"/>
-      <c r="C105" s="30"/>
-      <c r="D105" s="30"/>
-      <c r="E105" s="30"/>
-      <c r="F105" s="30"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="30"/>
-      <c r="I105" s="30"/>
+      <c r="C105" s="32"/>
+      <c r="D105" s="32"/>
+      <c r="E105" s="32"/>
+      <c r="F105" s="32"/>
+      <c r="G105" s="32"/>
+      <c r="H105" s="32"/>
+      <c r="I105" s="32"/>
       <c r="J105" s="38"/>
-      <c r="K105" s="30"/>
+      <c r="K105" s="32"/>
     </row>
     <row r="106" spans="1:11">
-      <c r="A106" s="30"/>
+      <c r="A106" s="32"/>
       <c r="B106" s="38"/>
-      <c r="C106" s="30"/>
-      <c r="D106" s="30"/>
-      <c r="E106" s="30"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
-      <c r="H106" s="30"/>
-      <c r="I106" s="30"/>
+      <c r="C106" s="32"/>
+      <c r="D106" s="32"/>
+      <c r="E106" s="32"/>
+      <c r="F106" s="32"/>
+      <c r="G106" s="32"/>
+      <c r="H106" s="32"/>
+      <c r="I106" s="32"/>
       <c r="J106" s="38"/>
-      <c r="K106" s="30"/>
+      <c r="K106" s="32"/>
     </row>
     <row r="107" spans="1:11">
-      <c r="A107" s="30"/>
+      <c r="A107" s="32"/>
       <c r="B107" s="38"/>
-      <c r="C107" s="30"/>
-      <c r="D107" s="30"/>
-      <c r="E107" s="30"/>
-      <c r="F107" s="30"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="30"/>
-      <c r="I107" s="30"/>
+      <c r="C107" s="32"/>
+      <c r="D107" s="32"/>
+      <c r="E107" s="32"/>
+      <c r="F107" s="32"/>
+      <c r="G107" s="32"/>
+      <c r="H107" s="32"/>
+      <c r="I107" s="32"/>
       <c r="J107" s="38"/>
-      <c r="K107" s="30"/>
+      <c r="K107" s="32"/>
     </row>
     <row r="108" spans="1:11">
-      <c r="A108" s="30"/>
+      <c r="A108" s="32"/>
       <c r="B108" s="38"/>
-      <c r="C108" s="30"/>
-      <c r="D108" s="30"/>
-      <c r="E108" s="30"/>
-      <c r="F108" s="30"/>
-      <c r="G108" s="30"/>
-      <c r="H108" s="30"/>
-      <c r="I108" s="30"/>
+      <c r="C108" s="32"/>
+      <c r="D108" s="32"/>
+      <c r="E108" s="32"/>
+      <c r="F108" s="32"/>
+      <c r="G108" s="32"/>
+      <c r="H108" s="32"/>
+      <c r="I108" s="32"/>
       <c r="J108" s="38"/>
-      <c r="K108" s="30"/>
+      <c r="K108" s="32"/>
     </row>
     <row r="109" spans="1:11">
-      <c r="A109" s="30"/>
+      <c r="A109" s="32"/>
       <c r="B109" s="38"/>
-      <c r="C109" s="30"/>
-      <c r="D109" s="30"/>
-      <c r="E109" s="30"/>
-      <c r="F109" s="30"/>
-      <c r="G109" s="30"/>
-      <c r="H109" s="30"/>
-      <c r="I109" s="30"/>
+      <c r="C109" s="32"/>
+      <c r="D109" s="32"/>
+      <c r="E109" s="32"/>
+      <c r="F109" s="32"/>
+      <c r="G109" s="32"/>
+      <c r="H109" s="32"/>
+      <c r="I109" s="32"/>
       <c r="J109" s="38"/>
-      <c r="K109" s="30"/>
+      <c r="K109" s="32"/>
     </row>
     <row r="110" spans="1:11">
-      <c r="A110" s="30"/>
+      <c r="A110" s="32"/>
       <c r="B110" s="38"/>
-      <c r="C110" s="30"/>
-      <c r="D110" s="30"/>
-      <c r="E110" s="30"/>
-      <c r="F110" s="30"/>
-      <c r="G110" s="30"/>
-      <c r="H110" s="30"/>
-      <c r="I110" s="30"/>
+      <c r="C110" s="32"/>
+      <c r="D110" s="32"/>
+      <c r="E110" s="32"/>
+      <c r="F110" s="32"/>
+      <c r="G110" s="32"/>
+      <c r="H110" s="32"/>
+      <c r="I110" s="32"/>
       <c r="J110" s="38"/>
-      <c r="K110" s="30"/>
+      <c r="K110" s="32"/>
     </row>
     <row r="111" spans="1:11">
-      <c r="A111" s="30"/>
+      <c r="A111" s="32"/>
       <c r="B111" s="38"/>
-      <c r="C111" s="30"/>
-      <c r="D111" s="30"/>
-      <c r="E111" s="30"/>
-      <c r="F111" s="30"/>
-      <c r="G111" s="30"/>
-      <c r="H111" s="30"/>
-      <c r="I111" s="30"/>
+      <c r="C111" s="32"/>
+      <c r="D111" s="32"/>
+      <c r="E111" s="32"/>
+      <c r="F111" s="32"/>
+      <c r="G111" s="32"/>
+      <c r="H111" s="32"/>
+      <c r="I111" s="32"/>
       <c r="J111" s="38"/>
-      <c r="K111" s="30"/>
+      <c r="K111" s="32"/>
     </row>
     <row r="112" spans="1:11">
-      <c r="A112" s="30"/>
+      <c r="A112" s="32"/>
       <c r="B112" s="38"/>
-      <c r="C112" s="30"/>
-      <c r="D112" s="30"/>
-      <c r="E112" s="30"/>
-      <c r="F112" s="30"/>
-      <c r="G112" s="30"/>
-      <c r="H112" s="30"/>
-      <c r="I112" s="30"/>
+      <c r="C112" s="32"/>
+      <c r="D112" s="32"/>
+      <c r="E112" s="32"/>
+      <c r="F112" s="32"/>
+      <c r="G112" s="32"/>
+      <c r="H112" s="32"/>
+      <c r="I112" s="32"/>
       <c r="J112" s="38"/>
-      <c r="K112" s="30"/>
+      <c r="K112" s="32"/>
     </row>
     <row r="113" spans="1:11">
-      <c r="A113" s="30"/>
+      <c r="A113" s="32"/>
       <c r="B113" s="38"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
-      <c r="G113" s="30"/>
-      <c r="H113" s="30"/>
-      <c r="I113" s="30"/>
+      <c r="C113" s="32"/>
+      <c r="D113" s="32"/>
+      <c r="E113" s="32"/>
+      <c r="F113" s="32"/>
+      <c r="G113" s="32"/>
+      <c r="H113" s="32"/>
+      <c r="I113" s="32"/>
       <c r="J113" s="38"/>
-      <c r="K113" s="30"/>
+      <c r="K113" s="32"/>
     </row>
     <row r="114" spans="1:11">
-      <c r="A114" s="30"/>
+      <c r="A114" s="32"/>
       <c r="B114" s="38"/>
-      <c r="C114" s="30"/>
-      <c r="D114" s="30"/>
-      <c r="E114" s="30"/>
-      <c r="F114" s="30"/>
-      <c r="G114" s="30"/>
-      <c r="H114" s="30"/>
-      <c r="I114" s="30"/>
+      <c r="C114" s="32"/>
+      <c r="D114" s="32"/>
+      <c r="E114" s="32"/>
+      <c r="F114" s="32"/>
+      <c r="G114" s="32"/>
+      <c r="H114" s="32"/>
+      <c r="I114" s="32"/>
       <c r="J114" s="38"/>
-      <c r="K114" s="30"/>
+      <c r="K114" s="32"/>
     </row>
     <row r="115" spans="1:11">
-      <c r="A115" s="30"/>
+      <c r="A115" s="32"/>
       <c r="B115" s="38"/>
-      <c r="C115" s="30"/>
-      <c r="D115" s="30"/>
-      <c r="E115" s="30"/>
-      <c r="F115" s="30"/>
-      <c r="G115" s="30"/>
-      <c r="H115" s="30"/>
-      <c r="I115" s="30"/>
+      <c r="C115" s="32"/>
+      <c r="D115" s="32"/>
+      <c r="E115" s="32"/>
+      <c r="F115" s="32"/>
+      <c r="G115" s="32"/>
+      <c r="H115" s="32"/>
+      <c r="I115" s="32"/>
       <c r="J115" s="38"/>
-      <c r="K115" s="30"/>
+      <c r="K115" s="32"/>
     </row>
     <row r="116" spans="1:11">
-      <c r="A116" s="30"/>
+      <c r="A116" s="32"/>
       <c r="B116" s="38"/>
-      <c r="C116" s="30"/>
-      <c r="D116" s="30"/>
-      <c r="E116" s="30"/>
-      <c r="F116" s="30"/>
-      <c r="G116" s="30"/>
-      <c r="H116" s="30"/>
-      <c r="I116" s="30"/>
+      <c r="C116" s="32"/>
+      <c r="D116" s="32"/>
+      <c r="E116" s="32"/>
+      <c r="F116" s="32"/>
+      <c r="G116" s="32"/>
+      <c r="H116" s="32"/>
+      <c r="I116" s="32"/>
       <c r="J116" s="38"/>
-      <c r="K116" s="30"/>
+      <c r="K116" s="32"/>
     </row>
     <row r="117" spans="1:11">
-      <c r="A117" s="30"/>
+      <c r="A117" s="32"/>
       <c r="B117" s="38"/>
-      <c r="C117" s="30"/>
-      <c r="D117" s="30"/>
-      <c r="E117" s="30"/>
-      <c r="F117" s="30"/>
-      <c r="G117" s="30"/>
-      <c r="H117" s="30"/>
-      <c r="I117" s="30"/>
+      <c r="C117" s="32"/>
+      <c r="D117" s="32"/>
+      <c r="E117" s="32"/>
+      <c r="F117" s="32"/>
+      <c r="G117" s="32"/>
+      <c r="H117" s="32"/>
+      <c r="I117" s="32"/>
       <c r="J117" s="38"/>
-      <c r="K117" s="30"/>
+      <c r="K117" s="32"/>
     </row>
     <row r="118" spans="1:11">
-      <c r="A118" s="30"/>
+      <c r="A118" s="32"/>
       <c r="B118" s="38"/>
-      <c r="C118" s="30"/>
-      <c r="D118" s="30"/>
-      <c r="E118" s="30"/>
-      <c r="F118" s="30"/>
-      <c r="G118" s="30"/>
-      <c r="H118" s="30"/>
-      <c r="I118" s="30"/>
+      <c r="C118" s="32"/>
+      <c r="D118" s="32"/>
+      <c r="E118" s="32"/>
+      <c r="F118" s="32"/>
+      <c r="G118" s="32"/>
+      <c r="H118" s="32"/>
+      <c r="I118" s="32"/>
       <c r="J118" s="38"/>
-      <c r="K118" s="30"/>
+      <c r="K118" s="32"/>
     </row>
     <row r="119" spans="1:11">
-      <c r="A119" s="30"/>
+      <c r="A119" s="32"/>
       <c r="B119" s="38"/>
-      <c r="C119" s="30"/>
-      <c r="D119" s="30"/>
-      <c r="E119" s="30"/>
-      <c r="F119" s="30"/>
-      <c r="G119" s="30"/>
-      <c r="H119" s="30"/>
-      <c r="I119" s="30"/>
+      <c r="C119" s="32"/>
+      <c r="D119" s="32"/>
+      <c r="E119" s="32"/>
+      <c r="F119" s="32"/>
+      <c r="G119" s="32"/>
+      <c r="H119" s="32"/>
+      <c r="I119" s="32"/>
       <c r="J119" s="38"/>
-      <c r="K119" s="30"/>
+      <c r="K119" s="32"/>
     </row>
     <row r="120" spans="1:11">
-      <c r="A120" s="30"/>
+      <c r="A120" s="32"/>
       <c r="B120" s="38"/>
-      <c r="C120" s="30"/>
-      <c r="D120" s="30"/>
-      <c r="E120" s="30"/>
-      <c r="F120" s="30"/>
-      <c r="G120" s="30"/>
-      <c r="H120" s="30"/>
-      <c r="I120" s="30"/>
+      <c r="C120" s="32"/>
+      <c r="D120" s="32"/>
+      <c r="E120" s="32"/>
+      <c r="F120" s="32"/>
+      <c r="G120" s="32"/>
+      <c r="H120" s="32"/>
+      <c r="I120" s="32"/>
       <c r="J120" s="38"/>
-      <c r="K120" s="30"/>
+      <c r="K120" s="32"/>
     </row>
     <row r="121" spans="1:11">
-      <c r="A121" s="30"/>
+      <c r="A121" s="32"/>
       <c r="B121" s="38"/>
-      <c r="C121" s="30"/>
-      <c r="D121" s="30"/>
-      <c r="E121" s="30"/>
-      <c r="F121" s="30"/>
-      <c r="G121" s="30"/>
-      <c r="H121" s="30"/>
-      <c r="I121" s="30"/>
+      <c r="C121" s="32"/>
+      <c r="D121" s="32"/>
+      <c r="E121" s="32"/>
+      <c r="F121" s="32"/>
+      <c r="G121" s="32"/>
+      <c r="H121" s="32"/>
+      <c r="I121" s="32"/>
       <c r="J121" s="38"/>
-      <c r="K121" s="30"/>
+      <c r="K121" s="32"/>
     </row>
     <row r="122" spans="1:11">
-      <c r="A122" s="30"/>
+      <c r="A122" s="32"/>
       <c r="B122" s="38"/>
-      <c r="C122" s="30"/>
-      <c r="D122" s="30"/>
-      <c r="E122" s="30"/>
-      <c r="F122" s="30"/>
-      <c r="G122" s="30"/>
-      <c r="H122" s="30"/>
-      <c r="I122" s="30"/>
+      <c r="C122" s="32"/>
+      <c r="D122" s="32"/>
+      <c r="E122" s="32"/>
+      <c r="F122" s="32"/>
+      <c r="G122" s="32"/>
+      <c r="H122" s="32"/>
+      <c r="I122" s="32"/>
       <c r="J122" s="38"/>
-      <c r="K122" s="30"/>
+      <c r="K122" s="32"/>
     </row>
     <row r="123" spans="1:11">
-      <c r="A123" s="30"/>
+      <c r="A123" s="32"/>
       <c r="B123" s="38"/>
-      <c r="C123" s="30"/>
-      <c r="D123" s="30"/>
-      <c r="E123" s="30"/>
-      <c r="F123" s="30"/>
-      <c r="G123" s="30"/>
-      <c r="H123" s="30"/>
-      <c r="I123" s="30"/>
+      <c r="C123" s="32"/>
+      <c r="D123" s="32"/>
+      <c r="E123" s="32"/>
+      <c r="F123" s="32"/>
+      <c r="G123" s="32"/>
+      <c r="H123" s="32"/>
+      <c r="I123" s="32"/>
       <c r="J123" s="38"/>
-      <c r="K123" s="30"/>
+      <c r="K123" s="32"/>
     </row>
     <row r="124" spans="1:11">
-      <c r="A124" s="30"/>
+      <c r="A124" s="32"/>
       <c r="B124" s="38"/>
-      <c r="C124" s="30"/>
-      <c r="D124" s="30"/>
-      <c r="E124" s="30"/>
-      <c r="F124" s="30"/>
-      <c r="G124" s="30"/>
-      <c r="H124" s="30"/>
-      <c r="I124" s="30"/>
+      <c r="C124" s="32"/>
+      <c r="D124" s="32"/>
+      <c r="E124" s="32"/>
+      <c r="F124" s="32"/>
+      <c r="G124" s="32"/>
+      <c r="H124" s="32"/>
+      <c r="I124" s="32"/>
       <c r="J124" s="38"/>
-      <c r="K124" s="30"/>
+      <c r="K124" s="32"/>
     </row>
     <row r="125" spans="1:11">
-      <c r="A125" s="30"/>
+      <c r="A125" s="32"/>
       <c r="B125" s="38"/>
-      <c r="C125" s="30"/>
-      <c r="D125" s="30"/>
-      <c r="E125" s="30"/>
-      <c r="F125" s="30"/>
-      <c r="G125" s="30"/>
-      <c r="H125" s="30"/>
-      <c r="I125" s="30"/>
+      <c r="C125" s="32"/>
+      <c r="D125" s="32"/>
+      <c r="E125" s="32"/>
+      <c r="F125" s="32"/>
+      <c r="G125" s="32"/>
+      <c r="H125" s="32"/>
+      <c r="I125" s="32"/>
       <c r="J125" s="38"/>
-      <c r="K125" s="30"/>
+      <c r="K125" s="32"/>
     </row>
     <row r="126" spans="1:11">
-      <c r="A126" s="30"/>
+      <c r="A126" s="32"/>
       <c r="B126" s="38"/>
-      <c r="C126" s="30"/>
-      <c r="D126" s="30"/>
-      <c r="E126" s="30"/>
-      <c r="F126" s="30"/>
-      <c r="G126" s="30"/>
-      <c r="H126" s="30"/>
-      <c r="I126" s="30"/>
+      <c r="C126" s="32"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="32"/>
+      <c r="I126" s="32"/>
       <c r="J126" s="38"/>
-      <c r="K126" s="30"/>
+      <c r="K126" s="32"/>
     </row>
     <row r="127" spans="1:11">
-      <c r="A127" s="30"/>
+      <c r="A127" s="32"/>
       <c r="B127" s="38"/>
-      <c r="C127" s="30"/>
-      <c r="D127" s="30"/>
-      <c r="E127" s="30"/>
-      <c r="F127" s="30"/>
-      <c r="G127" s="30"/>
-      <c r="H127" s="30"/>
-      <c r="I127" s="30"/>
+      <c r="C127" s="32"/>
+      <c r="D127" s="32"/>
+      <c r="E127" s="32"/>
+      <c r="F127" s="32"/>
+      <c r="G127" s="32"/>
+      <c r="H127" s="32"/>
+      <c r="I127" s="32"/>
       <c r="J127" s="38"/>
-      <c r="K127" s="30"/>
+      <c r="K127" s="32"/>
     </row>
     <row r="128" spans="1:11">
-      <c r="A128" s="30"/>
+      <c r="A128" s="32"/>
       <c r="B128" s="38"/>
-      <c r="C128" s="30"/>
-      <c r="D128" s="30"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="30"/>
-      <c r="G128" s="30"/>
-      <c r="H128" s="30"/>
-      <c r="I128" s="30"/>
+      <c r="C128" s="32"/>
+      <c r="D128" s="32"/>
+      <c r="E128" s="32"/>
+      <c r="F128" s="32"/>
+      <c r="G128" s="32"/>
+      <c r="H128" s="32"/>
+      <c r="I128" s="32"/>
       <c r="J128" s="38"/>
-      <c r="K128" s="30"/>
+      <c r="K128" s="32"/>
     </row>
     <row r="129" spans="1:11">
-      <c r="A129" s="30"/>
+      <c r="A129" s="32"/>
       <c r="B129" s="38"/>
-      <c r="C129" s="30"/>
-      <c r="D129" s="30"/>
-      <c r="E129" s="30"/>
-      <c r="F129" s="30"/>
-      <c r="G129" s="30"/>
-      <c r="H129" s="30"/>
-      <c r="I129" s="30"/>
+      <c r="C129" s="32"/>
+      <c r="D129" s="32"/>
+      <c r="E129" s="32"/>
+      <c r="F129" s="32"/>
+      <c r="G129" s="32"/>
+      <c r="H129" s="32"/>
+      <c r="I129" s="32"/>
       <c r="J129" s="38"/>
-      <c r="K129" s="30"/>
+      <c r="K129" s="32"/>
     </row>
     <row r="130" spans="1:11">
-      <c r="A130" s="30"/>
+      <c r="A130" s="32"/>
       <c r="B130" s="38"/>
-      <c r="C130" s="30"/>
-      <c r="D130" s="30"/>
-      <c r="E130" s="30"/>
-      <c r="F130" s="30"/>
-      <c r="G130" s="30"/>
-      <c r="H130" s="30"/>
-      <c r="I130" s="30"/>
+      <c r="C130" s="32"/>
+      <c r="D130" s="32"/>
+      <c r="E130" s="32"/>
+      <c r="F130" s="32"/>
+      <c r="G130" s="32"/>
+      <c r="H130" s="32"/>
+      <c r="I130" s="32"/>
       <c r="J130" s="38"/>
-      <c r="K130" s="30"/>
+      <c r="K130" s="32"/>
     </row>
     <row r="131" spans="1:11">
-      <c r="A131" s="30"/>
+      <c r="A131" s="32"/>
       <c r="B131" s="38"/>
-      <c r="C131" s="30"/>
-      <c r="D131" s="30"/>
-      <c r="E131" s="30"/>
-      <c r="F131" s="30"/>
-      <c r="G131" s="30"/>
-      <c r="H131" s="30"/>
-      <c r="I131" s="30"/>
+      <c r="C131" s="32"/>
+      <c r="D131" s="32"/>
+      <c r="E131" s="32"/>
+      <c r="F131" s="32"/>
+      <c r="G131" s="32"/>
+      <c r="H131" s="32"/>
+      <c r="I131" s="32"/>
       <c r="J131" s="38"/>
-      <c r="K131" s="30"/>
+      <c r="K131" s="32"/>
     </row>
     <row r="132" spans="1:11">
-      <c r="A132" s="30"/>
+      <c r="A132" s="32"/>
       <c r="B132" s="38"/>
-      <c r="C132" s="30"/>
-      <c r="D132" s="30"/>
-      <c r="E132" s="30"/>
-      <c r="F132" s="30"/>
-      <c r="G132" s="30"/>
-      <c r="H132" s="30"/>
-      <c r="I132" s="30"/>
+      <c r="C132" s="32"/>
+      <c r="D132" s="32"/>
+      <c r="E132" s="32"/>
+      <c r="F132" s="32"/>
+      <c r="G132" s="32"/>
+      <c r="H132" s="32"/>
+      <c r="I132" s="32"/>
       <c r="J132" s="38"/>
-      <c r="K132" s="30"/>
+      <c r="K132" s="32"/>
     </row>
     <row r="133" spans="1:11">
-      <c r="A133" s="30"/>
+      <c r="A133" s="32"/>
       <c r="B133" s="38"/>
-      <c r="C133" s="30"/>
-      <c r="D133" s="30"/>
-      <c r="E133" s="30"/>
-      <c r="F133" s="30"/>
-      <c r="G133" s="30"/>
-      <c r="H133" s="30"/>
-      <c r="I133" s="30"/>
+      <c r="C133" s="32"/>
+      <c r="D133" s="32"/>
+      <c r="E133" s="32"/>
+      <c r="F133" s="32"/>
+      <c r="G133" s="32"/>
+      <c r="H133" s="32"/>
+      <c r="I133" s="32"/>
       <c r="J133" s="38"/>
-      <c r="K133" s="30"/>
+      <c r="K133" s="32"/>
     </row>
     <row r="134" spans="1:11">
-      <c r="A134" s="30"/>
+      <c r="A134" s="32"/>
       <c r="B134" s="38"/>
-      <c r="C134" s="30"/>
-      <c r="D134" s="30"/>
-      <c r="E134" s="30"/>
-      <c r="F134" s="30"/>
-      <c r="G134" s="30"/>
-      <c r="H134" s="30"/>
-      <c r="I134" s="30"/>
+      <c r="C134" s="32"/>
+      <c r="D134" s="32"/>
+      <c r="E134" s="32"/>
+      <c r="F134" s="32"/>
+      <c r="G134" s="32"/>
+      <c r="H134" s="32"/>
+      <c r="I134" s="32"/>
       <c r="J134" s="38"/>
-      <c r="K134" s="30"/>
+      <c r="K134" s="32"/>
     </row>
     <row r="135" spans="1:11">
-      <c r="A135" s="30"/>
+      <c r="A135" s="32"/>
       <c r="B135" s="38"/>
-      <c r="C135" s="30"/>
-      <c r="D135" s="30"/>
-      <c r="E135" s="30"/>
-      <c r="F135" s="30"/>
-      <c r="G135" s="30"/>
-      <c r="H135" s="30"/>
-      <c r="I135" s="30"/>
+      <c r="C135" s="32"/>
+      <c r="D135" s="32"/>
+      <c r="E135" s="32"/>
+      <c r="F135" s="32"/>
+      <c r="G135" s="32"/>
+      <c r="H135" s="32"/>
+      <c r="I135" s="32"/>
       <c r="J135" s="38"/>
-      <c r="K135" s="30"/>
+      <c r="K135" s="32"/>
     </row>
     <row r="136" spans="1:11">
-      <c r="A136" s="30"/>
+      <c r="A136" s="32"/>
       <c r="B136" s="38"/>
-      <c r="C136" s="30"/>
-      <c r="D136" s="30"/>
-      <c r="E136" s="30"/>
-      <c r="F136" s="30"/>
-      <c r="G136" s="30"/>
-      <c r="H136" s="30"/>
-      <c r="I136" s="30"/>
+      <c r="C136" s="32"/>
+      <c r="D136" s="32"/>
+      <c r="E136" s="32"/>
+      <c r="F136" s="32"/>
+      <c r="G136" s="32"/>
+      <c r="H136" s="32"/>
+      <c r="I136" s="32"/>
       <c r="J136" s="38"/>
-      <c r="K136" s="30"/>
+      <c r="K136" s="32"/>
     </row>
     <row r="137" spans="1:11">
-      <c r="A137" s="30"/>
+      <c r="A137" s="32"/>
       <c r="B137" s="38"/>
-      <c r="C137" s="30"/>
-      <c r="D137" s="30"/>
-      <c r="E137" s="30"/>
-      <c r="F137" s="30"/>
-      <c r="G137" s="30"/>
-      <c r="H137" s="30"/>
-      <c r="I137" s="30"/>
+      <c r="C137" s="32"/>
+      <c r="D137" s="32"/>
+      <c r="E137" s="32"/>
+      <c r="F137" s="32"/>
+      <c r="G137" s="32"/>
+      <c r="H137" s="32"/>
+      <c r="I137" s="32"/>
       <c r="J137" s="38"/>
-      <c r="K137" s="30"/>
+      <c r="K137" s="32"/>
     </row>
     <row r="138" spans="1:11">
-      <c r="A138" s="30"/>
+      <c r="A138" s="32"/>
       <c r="B138" s="38"/>
-      <c r="C138" s="30"/>
-      <c r="D138" s="30"/>
-      <c r="E138" s="30"/>
-      <c r="F138" s="30"/>
-      <c r="G138" s="30"/>
-      <c r="H138" s="30"/>
-      <c r="I138" s="30"/>
+      <c r="C138" s="32"/>
+      <c r="D138" s="32"/>
+      <c r="E138" s="32"/>
+      <c r="F138" s="32"/>
+      <c r="G138" s="32"/>
+      <c r="H138" s="32"/>
+      <c r="I138" s="32"/>
       <c r="J138" s="38"/>
-      <c r="K138" s="30"/>
+      <c r="K138" s="32"/>
     </row>
     <row r="139" spans="1:11">
-      <c r="A139" s="30"/>
+      <c r="A139" s="32"/>
       <c r="B139" s="38"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="30"/>
-      <c r="E139" s="30"/>
-      <c r="F139" s="30"/>
-      <c r="G139" s="30"/>
-      <c r="H139" s="30"/>
-      <c r="I139" s="30"/>
+      <c r="C139" s="32"/>
+      <c r="D139" s="32"/>
+      <c r="E139" s="32"/>
+      <c r="F139" s="32"/>
+      <c r="G139" s="32"/>
+      <c r="H139" s="32"/>
+      <c r="I139" s="32"/>
       <c r="J139" s="38"/>
-      <c r="K139" s="30"/>
+      <c r="K139" s="32"/>
     </row>
     <row r="140" spans="1:11">
-      <c r="A140" s="30"/>
+      <c r="A140" s="32"/>
       <c r="B140" s="38"/>
-      <c r="C140" s="30"/>
-      <c r="D140" s="30"/>
-      <c r="E140" s="30"/>
-      <c r="F140" s="30"/>
-      <c r="G140" s="30"/>
-      <c r="H140" s="30"/>
-      <c r="I140" s="30"/>
+      <c r="C140" s="32"/>
+      <c r="D140" s="32"/>
+      <c r="E140" s="32"/>
+      <c r="F140" s="32"/>
+      <c r="G140" s="32"/>
+      <c r="H140" s="32"/>
+      <c r="I140" s="32"/>
       <c r="J140" s="38"/>
-      <c r="K140" s="30"/>
+      <c r="K140" s="32"/>
     </row>
     <row r="141" spans="1:11">
-      <c r="A141" s="30"/>
+      <c r="A141" s="32"/>
       <c r="B141" s="38"/>
-      <c r="C141" s="30"/>
-      <c r="D141" s="30"/>
-      <c r="E141" s="30"/>
-      <c r="F141" s="30"/>
-      <c r="G141" s="30"/>
-      <c r="H141" s="30"/>
-      <c r="I141" s="30"/>
+      <c r="C141" s="32"/>
+      <c r="D141" s="32"/>
+      <c r="E141" s="32"/>
+      <c r="F141" s="32"/>
+      <c r="G141" s="32"/>
+      <c r="H141" s="32"/>
+      <c r="I141" s="32"/>
       <c r="J141" s="38"/>
-      <c r="K141" s="30"/>
+      <c r="K141" s="32"/>
     </row>
     <row r="142" spans="1:11">
-      <c r="A142" s="30"/>
+      <c r="A142" s="32"/>
       <c r="B142" s="38"/>
-      <c r="C142" s="30"/>
-      <c r="D142" s="30"/>
-      <c r="E142" s="30"/>
-      <c r="F142" s="30"/>
-      <c r="G142" s="30"/>
-      <c r="H142" s="30"/>
-      <c r="I142" s="30"/>
+      <c r="C142" s="32"/>
+      <c r="D142" s="32"/>
+      <c r="E142" s="32"/>
+      <c r="F142" s="32"/>
+      <c r="G142" s="32"/>
+      <c r="H142" s="32"/>
+      <c r="I142" s="32"/>
       <c r="J142" s="38"/>
-      <c r="K142" s="30"/>
+      <c r="K142" s="32"/>
     </row>
     <row r="143" spans="1:11">
-      <c r="A143" s="30"/>
+      <c r="A143" s="32"/>
       <c r="B143" s="38"/>
-      <c r="C143" s="30"/>
-      <c r="D143" s="30"/>
-      <c r="E143" s="30"/>
-      <c r="F143" s="30"/>
-      <c r="G143" s="30"/>
-      <c r="H143" s="30"/>
-      <c r="I143" s="30"/>
+      <c r="C143" s="32"/>
+      <c r="D143" s="32"/>
+      <c r="E143" s="32"/>
+      <c r="F143" s="32"/>
+      <c r="G143" s="32"/>
+      <c r="H143" s="32"/>
+      <c r="I143" s="32"/>
       <c r="J143" s="38"/>
-      <c r="K143" s="30"/>
+      <c r="K143" s="32"/>
     </row>
     <row r="144" spans="1:11">
-      <c r="A144" s="30"/>
+      <c r="A144" s="32"/>
       <c r="B144" s="38"/>
-      <c r="C144" s="30"/>
-      <c r="D144" s="30"/>
-      <c r="E144" s="30"/>
-      <c r="F144" s="30"/>
-      <c r="G144" s="30"/>
-      <c r="H144" s="30"/>
-      <c r="I144" s="30"/>
+      <c r="C144" s="32"/>
+      <c r="D144" s="32"/>
+      <c r="E144" s="32"/>
+      <c r="F144" s="32"/>
+      <c r="G144" s="32"/>
+      <c r="H144" s="32"/>
+      <c r="I144" s="32"/>
       <c r="J144" s="38"/>
-      <c r="K144" s="30"/>
+      <c r="K144" s="32"/>
     </row>
     <row r="145" spans="1:11">
-      <c r="A145" s="30"/>
+      <c r="A145" s="32"/>
       <c r="B145" s="38"/>
-      <c r="C145" s="30"/>
-      <c r="D145" s="30"/>
-      <c r="E145" s="30"/>
-      <c r="F145" s="30"/>
-      <c r="G145" s="30"/>
-      <c r="H145" s="30"/>
-      <c r="I145" s="30"/>
+      <c r="C145" s="32"/>
+      <c r="D145" s="32"/>
+      <c r="E145" s="32"/>
+      <c r="F145" s="32"/>
+      <c r="G145" s="32"/>
+      <c r="H145" s="32"/>
+      <c r="I145" s="32"/>
       <c r="J145" s="38"/>
-      <c r="K145" s="30"/>
+      <c r="K145" s="32"/>
     </row>
     <row r="146" spans="1:11">
-      <c r="A146" s="30"/>
+      <c r="A146" s="32"/>
       <c r="B146" s="38"/>
-      <c r="C146" s="30"/>
-      <c r="D146" s="30"/>
-      <c r="E146" s="30"/>
-      <c r="F146" s="30"/>
-      <c r="G146" s="30"/>
-      <c r="H146" s="30"/>
-      <c r="I146" s="30"/>
+      <c r="C146" s="32"/>
+      <c r="D146" s="32"/>
+      <c r="E146" s="32"/>
+      <c r="F146" s="32"/>
+      <c r="G146" s="32"/>
+      <c r="H146" s="32"/>
+      <c r="I146" s="32"/>
       <c r="J146" s="38"/>
-      <c r="K146" s="30"/>
+      <c r="K146" s="32"/>
     </row>
   </sheetData>
   <sortState ref="A2:K107">
@@ -4463,868 +4472,868 @@
       <c r="C2" s="28"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
-      <c r="F2" s="32"/>
+      <c r="F2" s="30"/>
       <c r="G2" s="28"/>
       <c r="H2" s="28"/>
-      <c r="I2" s="34"/>
+      <c r="I2" s="31"/>
     </row>
     <row r="3" ht="17.55" spans="1:9">
-      <c r="A3" s="30"/>
-      <c r="B3" s="31"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="35"/>
+      <c r="A3" s="32"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="34"/>
     </row>
     <row r="4" ht="17.55" spans="1:9">
-      <c r="A4" s="30"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="35"/>
+      <c r="A4" s="32"/>
+      <c r="B4" s="33"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="34"/>
     </row>
     <row r="5" ht="17.55" spans="1:9">
-      <c r="A5" s="30"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="35"/>
+      <c r="A5" s="32"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" ht="17.55" spans="1:9">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="35"/>
+      <c r="A6" s="32"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" ht="17.55" spans="1:9">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="35"/>
+      <c r="A7" s="32"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="34"/>
     </row>
     <row r="8" ht="17.55" spans="1:9">
-      <c r="A8" s="30"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="35"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" ht="17.55" spans="1:9">
-      <c r="A9" s="30"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="35"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="34"/>
     </row>
     <row r="10" ht="17.55" spans="1:9">
-      <c r="A10" s="30"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="35"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="34"/>
     </row>
     <row r="11" ht="17.55" spans="1:9">
-      <c r="A11" s="30"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="35"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="34"/>
     </row>
     <row r="12" ht="17.55" spans="1:9">
-      <c r="A12" s="30"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="30"/>
-      <c r="H12" s="30"/>
-      <c r="I12" s="35"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="34"/>
     </row>
     <row r="13" ht="17.55" spans="1:9">
-      <c r="A13" s="30"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="30"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="35"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="34"/>
     </row>
     <row r="14" ht="17.55" spans="1:9">
-      <c r="A14" s="30"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="35"/>
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="34"/>
     </row>
     <row r="15" ht="17.55" spans="1:9">
-      <c r="A15" s="30"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="35"/>
+      <c r="A15" s="32"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="34"/>
     </row>
     <row r="16" ht="17.55" spans="1:9">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="35"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="33"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="34"/>
     </row>
     <row r="17" ht="17.55" spans="1:9">
-      <c r="A17" s="30"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="35"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="34"/>
     </row>
     <row r="18" ht="17.55" spans="1:9">
-      <c r="A18" s="30"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="35"/>
+      <c r="A18" s="32"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="34"/>
     </row>
     <row r="19" ht="17.55" spans="1:9">
-      <c r="A19" s="30"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="35"/>
+      <c r="A19" s="32"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="34"/>
     </row>
     <row r="20" ht="17.55" spans="1:9">
-      <c r="A20" s="30"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="35"/>
+      <c r="A20" s="32"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="34"/>
     </row>
     <row r="21" ht="17.55" spans="1:9">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="35"/>
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="34"/>
     </row>
     <row r="22" ht="17.55" spans="1:9">
-      <c r="A22" s="30"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="35"/>
+      <c r="A22" s="32"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="34"/>
     </row>
     <row r="23" ht="17.55" spans="1:9">
-      <c r="A23" s="30"/>
-      <c r="B23" s="31"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="35"/>
+      <c r="A23" s="32"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+      <c r="I23" s="34"/>
     </row>
     <row r="24" ht="17.55" spans="1:9">
-      <c r="A24" s="30"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="35"/>
+      <c r="A24" s="32"/>
+      <c r="B24" s="33"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="34"/>
     </row>
     <row r="25" ht="17.55" spans="1:9">
-      <c r="A25" s="30"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="35"/>
+      <c r="A25" s="32"/>
+      <c r="B25" s="33"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="34"/>
     </row>
     <row r="26" ht="17.55" spans="1:9">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="35"/>
+      <c r="A26" s="32"/>
+      <c r="B26" s="33"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="34"/>
     </row>
     <row r="27" ht="17.55" spans="1:9">
-      <c r="A27" s="30"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="35"/>
+      <c r="A27" s="32"/>
+      <c r="B27" s="33"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="34"/>
     </row>
     <row r="28" ht="17.55" spans="1:9">
-      <c r="A28" s="30"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="35"/>
+      <c r="A28" s="32"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="34"/>
     </row>
     <row r="29" ht="17.55" spans="1:9">
-      <c r="A29" s="30"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="35"/>
+      <c r="A29" s="32"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="34"/>
     </row>
     <row r="30" ht="17.55" spans="1:9">
-      <c r="A30" s="30"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="35"/>
+      <c r="A30" s="32"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="32"/>
+      <c r="G30" s="32"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="34"/>
     </row>
     <row r="31" ht="17.55" spans="1:9">
-      <c r="A31" s="30"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="35"/>
+      <c r="A31" s="32"/>
+      <c r="B31" s="33"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="34"/>
     </row>
     <row r="32" ht="17.55" spans="1:9">
-      <c r="A32" s="30"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="35"/>
+      <c r="A32" s="32"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="34"/>
     </row>
     <row r="33" ht="17.55" spans="1:9">
-      <c r="A33" s="30"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
-      <c r="E33" s="30"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="30"/>
-      <c r="H33" s="30"/>
-      <c r="I33" s="35"/>
+      <c r="A33" s="32"/>
+      <c r="B33" s="33"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="34"/>
     </row>
     <row r="34" ht="17.55" spans="1:9">
-      <c r="A34" s="30"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
-      <c r="I34" s="35"/>
+      <c r="A34" s="32"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="34"/>
     </row>
     <row r="35" ht="17.55" spans="1:9">
-      <c r="A35" s="30"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="35"/>
+      <c r="A35" s="32"/>
+      <c r="B35" s="33"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="34"/>
     </row>
     <row r="36" ht="17.55" spans="1:9">
-      <c r="A36" s="30"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="35"/>
+      <c r="A36" s="32"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="32"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="34"/>
     </row>
     <row r="37" ht="17.55" spans="1:9">
-      <c r="A37" s="30"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="35"/>
+      <c r="A37" s="32"/>
+      <c r="B37" s="33"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32"/>
+      <c r="F37" s="32"/>
+      <c r="G37" s="32"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="34"/>
     </row>
     <row r="38" ht="17.55" spans="1:9">
-      <c r="A38" s="30"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="35"/>
+      <c r="A38" s="32"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="34"/>
     </row>
     <row r="39" ht="17.55" spans="1:9">
-      <c r="A39" s="30"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="35"/>
+      <c r="A39" s="32"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="34"/>
     </row>
     <row r="40" ht="17.55" spans="1:9">
-      <c r="A40" s="30"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="35"/>
+      <c r="A40" s="32"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="34"/>
     </row>
     <row r="41" ht="17.55" spans="1:9">
-      <c r="A41" s="30"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="35"/>
+      <c r="A41" s="32"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="34"/>
     </row>
     <row r="42" ht="17.55" spans="1:9">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="30"/>
-      <c r="D42" s="30"/>
-      <c r="E42" s="30"/>
-      <c r="F42" s="30"/>
-      <c r="G42" s="30"/>
-      <c r="H42" s="30"/>
-      <c r="I42" s="35"/>
+      <c r="A42" s="32"/>
+      <c r="B42" s="33"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="34"/>
     </row>
     <row r="43" ht="17.55" spans="1:9">
-      <c r="A43" s="30"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="35"/>
+      <c r="A43" s="32"/>
+      <c r="B43" s="33"/>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32"/>
+      <c r="F43" s="32"/>
+      <c r="G43" s="32"/>
+      <c r="H43" s="32"/>
+      <c r="I43" s="34"/>
     </row>
     <row r="44" ht="17.55" spans="1:9">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="30"/>
-      <c r="D44" s="30"/>
-      <c r="E44" s="30"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="30"/>
-      <c r="I44" s="35"/>
+      <c r="A44" s="32"/>
+      <c r="B44" s="33"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="35"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="34"/>
     </row>
     <row r="45" ht="17.55" spans="1:9">
-      <c r="A45" s="30"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="30"/>
-      <c r="D45" s="30"/>
-      <c r="E45" s="30"/>
-      <c r="F45" s="30"/>
-      <c r="G45" s="30"/>
-      <c r="H45" s="30"/>
-      <c r="I45" s="35"/>
+      <c r="A45" s="32"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32"/>
+      <c r="F45" s="32"/>
+      <c r="G45" s="32"/>
+      <c r="H45" s="32"/>
+      <c r="I45" s="34"/>
     </row>
     <row r="46" ht="17.55" spans="1:9">
-      <c r="A46" s="30"/>
-      <c r="B46" s="31"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="35"/>
+      <c r="A46" s="32"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="34"/>
     </row>
     <row r="47" ht="17.55" spans="1:9">
-      <c r="A47" s="30"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="35"/>
+      <c r="A47" s="32"/>
+      <c r="B47" s="33"/>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="32"/>
+      <c r="I47" s="34"/>
     </row>
     <row r="48" ht="17.55" spans="1:9">
-      <c r="A48" s="30"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="35"/>
+      <c r="A48" s="32"/>
+      <c r="B48" s="33"/>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32"/>
+      <c r="F48" s="32"/>
+      <c r="G48" s="32"/>
+      <c r="H48" s="32"/>
+      <c r="I48" s="34"/>
     </row>
     <row r="49" ht="17.55" spans="1:9">
-      <c r="A49" s="30"/>
-      <c r="B49" s="31"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="35"/>
+      <c r="A49" s="32"/>
+      <c r="B49" s="33"/>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="34"/>
     </row>
     <row r="50" ht="17.55" spans="1:9">
-      <c r="A50" s="30"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="30"/>
-      <c r="D50" s="30"/>
-      <c r="E50" s="30"/>
-      <c r="F50" s="30"/>
-      <c r="G50" s="30"/>
-      <c r="H50" s="30"/>
-      <c r="I50" s="35"/>
+      <c r="A50" s="32"/>
+      <c r="B50" s="33"/>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="34"/>
     </row>
     <row r="51" ht="17.55" spans="1:9">
-      <c r="A51" s="30"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="30"/>
-      <c r="E51" s="30"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="30"/>
-      <c r="H51" s="30"/>
-      <c r="I51" s="35"/>
+      <c r="A51" s="32"/>
+      <c r="B51" s="33"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="34"/>
     </row>
     <row r="52" ht="17.55" spans="1:9">
-      <c r="A52" s="30"/>
-      <c r="B52" s="31"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="35"/>
+      <c r="A52" s="32"/>
+      <c r="B52" s="33"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="34"/>
     </row>
     <row r="53" ht="17.55" spans="1:9">
-      <c r="A53" s="30"/>
-      <c r="B53" s="31"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="30"/>
-      <c r="I53" s="35"/>
+      <c r="A53" s="32"/>
+      <c r="B53" s="33"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32"/>
+      <c r="F53" s="32"/>
+      <c r="G53" s="32"/>
+      <c r="H53" s="32"/>
+      <c r="I53" s="34"/>
     </row>
     <row r="54" ht="17.55" spans="1:9">
-      <c r="A54" s="30"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="35"/>
+      <c r="A54" s="32"/>
+      <c r="B54" s="33"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="34"/>
     </row>
     <row r="55" ht="17.55" spans="1:9">
-      <c r="A55" s="30"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="35"/>
+      <c r="A55" s="32"/>
+      <c r="B55" s="33"/>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="34"/>
     </row>
     <row r="56" ht="17.55" spans="1:9">
-      <c r="A56" s="30"/>
-      <c r="B56" s="31"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="30"/>
-      <c r="G56" s="30"/>
-      <c r="H56" s="30"/>
-      <c r="I56" s="35"/>
+      <c r="A56" s="32"/>
+      <c r="B56" s="33"/>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="34"/>
     </row>
     <row r="57" ht="17.55" spans="1:9">
-      <c r="A57" s="30"/>
-      <c r="B57" s="31"/>
-      <c r="C57" s="30"/>
-      <c r="D57" s="30"/>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-      <c r="G57" s="30"/>
-      <c r="H57" s="30"/>
-      <c r="I57" s="35"/>
+      <c r="A57" s="32"/>
+      <c r="B57" s="33"/>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="34"/>
     </row>
     <row r="58" ht="17.55" spans="1:9">
-      <c r="A58" s="30"/>
-      <c r="B58" s="31"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="35"/>
+      <c r="A58" s="32"/>
+      <c r="B58" s="33"/>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="34"/>
     </row>
     <row r="59" ht="17.55" spans="1:9">
-      <c r="A59" s="30"/>
-      <c r="B59" s="31"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="30"/>
-      <c r="I59" s="35"/>
+      <c r="A59" s="32"/>
+      <c r="B59" s="33"/>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="34"/>
     </row>
     <row r="60" ht="17.55" spans="1:9">
-      <c r="A60" s="30"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="35"/>
+      <c r="A60" s="32"/>
+      <c r="B60" s="33"/>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32"/>
+      <c r="F60" s="32"/>
+      <c r="G60" s="32"/>
+      <c r="H60" s="32"/>
+      <c r="I60" s="34"/>
     </row>
     <row r="61" ht="17.55" spans="1:9">
-      <c r="A61" s="30"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="35"/>
+      <c r="A61" s="32"/>
+      <c r="B61" s="33"/>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32"/>
+      <c r="F61" s="32"/>
+      <c r="G61" s="32"/>
+      <c r="H61" s="32"/>
+      <c r="I61" s="34"/>
     </row>
     <row r="62" ht="17.55" spans="1:9">
-      <c r="A62" s="30"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="30"/>
-      <c r="H62" s="30"/>
-      <c r="I62" s="35"/>
+      <c r="A62" s="32"/>
+      <c r="B62" s="33"/>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32"/>
+      <c r="F62" s="32"/>
+      <c r="G62" s="32"/>
+      <c r="H62" s="32"/>
+      <c r="I62" s="34"/>
     </row>
     <row r="63" ht="17.55" spans="1:9">
-      <c r="A63" s="30"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="30"/>
-      <c r="E63" s="30"/>
-      <c r="F63" s="30"/>
-      <c r="G63" s="30"/>
-      <c r="H63" s="30"/>
-      <c r="I63" s="35"/>
+      <c r="A63" s="32"/>
+      <c r="B63" s="33"/>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="32"/>
+      <c r="G63" s="32"/>
+      <c r="H63" s="32"/>
+      <c r="I63" s="34"/>
     </row>
     <row r="64" ht="17.55" spans="1:9">
-      <c r="A64" s="30"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="35"/>
+      <c r="A64" s="32"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="34"/>
     </row>
     <row r="65" ht="17.55" spans="1:9">
-      <c r="A65" s="30"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="30"/>
-      <c r="D65" s="30"/>
-      <c r="E65" s="30"/>
-      <c r="F65" s="30"/>
-      <c r="G65" s="30"/>
-      <c r="H65" s="30"/>
-      <c r="I65" s="35"/>
+      <c r="A65" s="32"/>
+      <c r="B65" s="33"/>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32"/>
+      <c r="F65" s="32"/>
+      <c r="G65" s="32"/>
+      <c r="H65" s="32"/>
+      <c r="I65" s="34"/>
     </row>
     <row r="66" ht="17.55" spans="1:9">
-      <c r="A66" s="30"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="30"/>
-      <c r="D66" s="30"/>
-      <c r="E66" s="30"/>
-      <c r="F66" s="30"/>
-      <c r="G66" s="30"/>
-      <c r="H66" s="30"/>
-      <c r="I66" s="35"/>
+      <c r="A66" s="32"/>
+      <c r="B66" s="33"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="32"/>
+      <c r="I66" s="34"/>
     </row>
     <row r="67" ht="17.55" spans="1:9">
-      <c r="A67" s="30"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="35"/>
+      <c r="A67" s="32"/>
+      <c r="B67" s="33"/>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32"/>
+      <c r="F67" s="32"/>
+      <c r="G67" s="32"/>
+      <c r="H67" s="32"/>
+      <c r="I67" s="34"/>
     </row>
     <row r="68" ht="17.55" spans="1:9">
-      <c r="A68" s="30"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="35"/>
+      <c r="A68" s="32"/>
+      <c r="B68" s="33"/>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32"/>
+      <c r="F68" s="32"/>
+      <c r="G68" s="32"/>
+      <c r="H68" s="32"/>
+      <c r="I68" s="34"/>
     </row>
     <row r="69" ht="17.55" spans="1:9">
-      <c r="A69" s="30"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="30"/>
-      <c r="D69" s="30"/>
-      <c r="E69" s="30"/>
-      <c r="F69" s="30"/>
-      <c r="G69" s="30"/>
-      <c r="H69" s="30"/>
-      <c r="I69" s="35"/>
+      <c r="A69" s="32"/>
+      <c r="B69" s="33"/>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32"/>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="34"/>
     </row>
     <row r="70" ht="17.55" spans="1:9">
-      <c r="A70" s="30"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="35"/>
+      <c r="A70" s="32"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32"/>
+      <c r="F70" s="32"/>
+      <c r="G70" s="32"/>
+      <c r="H70" s="32"/>
+      <c r="I70" s="34"/>
     </row>
     <row r="71" ht="17.55" spans="1:9">
-      <c r="A71" s="30"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="35"/>
+      <c r="A71" s="32"/>
+      <c r="B71" s="33"/>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32"/>
+      <c r="F71" s="32"/>
+      <c r="G71" s="32"/>
+      <c r="H71" s="32"/>
+      <c r="I71" s="34"/>
     </row>
     <row r="72" ht="17.55" spans="1:9">
-      <c r="A72" s="30"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="35"/>
+      <c r="A72" s="32"/>
+      <c r="B72" s="33"/>
+      <c r="C72" s="32"/>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="34"/>
     </row>
     <row r="73" ht="17.55" spans="1:9">
-      <c r="A73" s="30"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="30"/>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="35"/>
+      <c r="A73" s="32"/>
+      <c r="B73" s="33"/>
+      <c r="C73" s="32"/>
+      <c r="D73" s="32"/>
+      <c r="E73" s="32"/>
+      <c r="F73" s="32"/>
+      <c r="G73" s="32"/>
+      <c r="H73" s="32"/>
+      <c r="I73" s="34"/>
     </row>
     <row r="74" ht="17.55" spans="1:9">
-      <c r="A74" s="30"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="35"/>
+      <c r="A74" s="32"/>
+      <c r="B74" s="33"/>
+      <c r="C74" s="32"/>
+      <c r="D74" s="32"/>
+      <c r="E74" s="32"/>
+      <c r="F74" s="32"/>
+      <c r="G74" s="32"/>
+      <c r="H74" s="32"/>
+      <c r="I74" s="34"/>
     </row>
     <row r="75" ht="17.55" spans="1:9">
-      <c r="A75" s="30"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="35"/>
+      <c r="A75" s="32"/>
+      <c r="B75" s="33"/>
+      <c r="C75" s="32"/>
+      <c r="D75" s="32"/>
+      <c r="E75" s="32"/>
+      <c r="F75" s="32"/>
+      <c r="G75" s="32"/>
+      <c r="H75" s="32"/>
+      <c r="I75" s="34"/>
     </row>
     <row r="76" ht="17.55" spans="1:9">
-      <c r="A76" s="30"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="35"/>
+      <c r="A76" s="32"/>
+      <c r="B76" s="33"/>
+      <c r="C76" s="32"/>
+      <c r="D76" s="32"/>
+      <c r="E76" s="32"/>
+      <c r="F76" s="32"/>
+      <c r="G76" s="32"/>
+      <c r="H76" s="32"/>
+      <c r="I76" s="34"/>
     </row>
     <row r="77" ht="17.55" spans="1:9">
-      <c r="A77" s="30"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="35"/>
+      <c r="A77" s="32"/>
+      <c r="B77" s="33"/>
+      <c r="C77" s="32"/>
+      <c r="D77" s="32"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="32"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="34"/>
     </row>
     <row r="78" ht="17.55" spans="1:9">
-      <c r="A78" s="30"/>
-      <c r="B78" s="31"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="35"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="33"/>
+      <c r="C78" s="32"/>
+      <c r="D78" s="32"/>
+      <c r="E78" s="32"/>
+      <c r="F78" s="32"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="34"/>
     </row>
     <row r="79" ht="17.55" spans="1:9">
-      <c r="A79" s="30"/>
-      <c r="B79" s="31"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="35"/>
+      <c r="A79" s="32"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="32"/>
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" ht="17.55" spans="1:9">
-      <c r="A80" s="30"/>
-      <c r="B80" s="31"/>
-      <c r="C80" s="30"/>
-      <c r="D80" s="30"/>
-      <c r="E80" s="30"/>
-      <c r="F80" s="30"/>
-      <c r="G80" s="30"/>
-      <c r="H80" s="30"/>
-      <c r="I80" s="35"/>
+      <c r="A80" s="32"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="32"/>
+      <c r="D80" s="32"/>
+      <c r="E80" s="32"/>
+      <c r="F80" s="32"/>
+      <c r="G80" s="32"/>
+      <c r="H80" s="32"/>
+      <c r="I80" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7175,11 +7184,14 @@
       <c r="Q1" s="15" t="s">
         <v>21</v>
       </c>
+      <c r="R1" s="15" t="s">
+        <v>22</v>
+      </c>
       <c r="DK1" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" ht="24" spans="1:20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" ht="24" spans="1:115">
       <c r="A2" s="16" t="e" cm="1">
         <f t="array" ref="A2">_xlfn.LET(_xlpm.col,INDEX(配送员履约明细表!A3:Z5000,,MATCH(A1,配送员履约明细表!2:2,0)),_xlpm.unique_col,_xlfn.UNIQUE(_xlpm.col),IF(_xlpm.unique_col=0,"",_xlpm.unique_col))</f>
         <v>#N/A</v>
@@ -7213,7 +7225,7 @@
         <v>缺勤</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K2" s="15">
         <f>SUMIF(F:F,"&lt;0")</f>
@@ -7224,7 +7236,7 @@
         <v/>
       </c>
       <c r="N2" s="15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O2" s="15" t="e" cm="1">
         <f t="array" ref="O2:O300">IF(COUNTIF(F2:F300,0)=0,"",_xlfn._xlws.FILTER(A2:A300,F2:F300=0))</f>
@@ -7234,15 +7246,18 @@
         <f t="array" ref="P2:P200">SUMIFS(配送员履约明细表!W2:W5000,配送员履约明细表!J2:J5000,O2:O200)</f>
         <v>0</v>
       </c>
-      <c r="Q2" s="21">
+      <c r="Q2" s="15" cm="1">
+        <f t="array" ref="Q2:Q200">P2:P200*盘点表!B2</f>
+        <v>0</v>
+      </c>
+      <c r="R2" s="21">
         <f ca="1">TODAY()</f>
-        <v>45849</v>
-      </c>
-      <c r="R2" s="19"/>
+        <v>45983</v>
+      </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
     </row>
-    <row r="3" ht="24" spans="2:16">
+    <row r="3" ht="24" spans="1:115">
       <c r="B3" s="15" t="str">
         <v>0</v>
       </c>
@@ -7274,8 +7289,11 @@
       <c r="P3" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" s="15" customFormat="1" spans="1:16">
+      <c r="Q3" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" s="15" customFormat="1" spans="1:115">
       <c r="A4" s="16"/>
       <c r="B4" s="15" t="str">
         <v>0</v>
@@ -7309,8 +7327,11 @@
       <c r="P4" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:16">
+      <c r="Q4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:115">
       <c r="B5" s="15" t="str">
         <v>0</v>
       </c>
@@ -7341,8 +7362,11 @@
       <c r="P5" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:16">
+      <c r="Q5" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:115">
       <c r="B6" s="15" t="str">
         <v>0</v>
       </c>
@@ -7373,8 +7397,11 @@
       <c r="P6" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:16">
+      <c r="Q6" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:115">
       <c r="B7" s="15" t="str">
         <v>0</v>
       </c>
@@ -7405,8 +7432,11 @@
       <c r="P7" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:16">
+      <c r="Q7" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:115">
       <c r="B8" s="15" t="str">
         <v>0</v>
       </c>
@@ -7437,8 +7467,11 @@
       <c r="P8" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:16">
+      <c r="Q8" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:115">
       <c r="B9" s="15" t="str">
         <v>0</v>
       </c>
@@ -7469,8 +7502,11 @@
       <c r="P9" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="2:16">
+      <c r="Q9" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:115">
       <c r="B10" s="15" t="str">
         <v>0</v>
       </c>
@@ -7501,8 +7537,11 @@
       <c r="P10" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="2:16">
+      <c r="Q10" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:115">
       <c r="B11" s="15" t="str">
         <v>0</v>
       </c>
@@ -7533,8 +7572,11 @@
       <c r="P11" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="2:16">
+      <c r="Q11" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:115">
       <c r="B12" s="15" t="str">
         <v>0</v>
       </c>
@@ -7565,8 +7607,11 @@
       <c r="P12" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="2:16">
+      <c r="Q12" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:115">
       <c r="B13" s="15" t="str">
         <v>0</v>
       </c>
@@ -7597,8 +7642,11 @@
       <c r="P13" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:16">
+      <c r="Q13" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:115">
       <c r="B14" s="15" t="str">
         <v>0</v>
       </c>
@@ -7629,8 +7677,11 @@
       <c r="P14" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:16">
+      <c r="Q14" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:115">
       <c r="B15" s="15" t="str">
         <v>0</v>
       </c>
@@ -7661,8 +7712,11 @@
       <c r="P15" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="2:16">
+      <c r="Q15" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:115">
       <c r="B16" s="15" t="str">
         <v>0</v>
       </c>
@@ -7693,8 +7747,11 @@
       <c r="P16" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:16">
+      <c r="Q16" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
       <c r="B17" s="15" t="str">
         <v>0</v>
       </c>
@@ -7725,8 +7782,11 @@
       <c r="P17" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:16">
+      <c r="Q17" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17">
       <c r="B18" s="15" t="str">
         <v>0</v>
       </c>
@@ -7757,8 +7817,11 @@
       <c r="P18" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:16">
+      <c r="Q18" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
       <c r="B19" s="15" t="str">
         <v>0</v>
       </c>
@@ -7789,8 +7852,11 @@
       <c r="P19" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="2:16">
+      <c r="Q19" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17">
       <c r="B20" s="15" t="str">
         <v>0</v>
       </c>
@@ -7821,8 +7887,11 @@
       <c r="P20" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:16">
+      <c r="Q20" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
       <c r="B21" s="15" t="str">
         <v>0</v>
       </c>
@@ -7853,8 +7922,11 @@
       <c r="P21" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="2:16">
+      <c r="Q21" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
       <c r="B22" s="15" t="str">
         <v>0</v>
       </c>
@@ -7885,8 +7957,11 @@
       <c r="P22" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:16">
+      <c r="Q22" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
       <c r="B23" s="15" t="str">
         <v>0</v>
       </c>
@@ -7917,8 +7992,11 @@
       <c r="P23" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="2:16">
+      <c r="Q23" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="15" t="str">
         <v>0</v>
       </c>
@@ -7949,8 +8027,11 @@
       <c r="P24" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:16">
+      <c r="Q24" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="15" t="str">
         <v>0</v>
       </c>
@@ -7981,8 +8062,11 @@
       <c r="P25" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="2:16">
+      <c r="Q25" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="15" t="str">
         <v>0</v>
       </c>
@@ -8013,8 +8097,11 @@
       <c r="P26" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="2:16">
+      <c r="Q26" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
       <c r="B27" s="15" t="str">
         <v>0</v>
       </c>
@@ -8045,8 +8132,11 @@
       <c r="P27" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="2:16">
+      <c r="Q27" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
       <c r="B28" s="15" t="str">
         <v>0</v>
       </c>
@@ -8077,8 +8167,11 @@
       <c r="P28" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:16">
+      <c r="Q28" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
       <c r="B29" s="15" t="str">
         <v>0</v>
       </c>
@@ -8109,8 +8202,11 @@
       <c r="P29" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:16">
+      <c r="Q29" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17">
       <c r="B30" s="15" t="str">
         <v>0</v>
       </c>
@@ -8141,8 +8237,11 @@
       <c r="P30" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="2:16">
+      <c r="Q30" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17">
       <c r="B31" s="15" t="str">
         <v>0</v>
       </c>
@@ -8173,8 +8272,11 @@
       <c r="P31" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="2:16">
+      <c r="Q31" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17">
       <c r="B32" s="15" t="str">
         <v>0</v>
       </c>
@@ -8205,8 +8307,11 @@
       <c r="P32" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:16">
+      <c r="Q32" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
       <c r="B33" s="15" t="str">
         <v>0</v>
       </c>
@@ -8237,8 +8342,11 @@
       <c r="P33" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="2:16">
+      <c r="Q33" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="15" t="str">
         <v>0</v>
       </c>
@@ -8269,8 +8377,11 @@
       <c r="P34" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16">
+      <c r="Q34" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="15" t="str">
         <v>0</v>
       </c>
@@ -8301,8 +8412,11 @@
       <c r="P35" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="2:16">
+      <c r="Q35" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="15" t="str">
         <v>0</v>
       </c>
@@ -8333,8 +8447,11 @@
       <c r="P36" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="2:16">
+      <c r="Q36" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17">
       <c r="B37" s="15" t="str">
         <v>0</v>
       </c>
@@ -8365,8 +8482,11 @@
       <c r="P37" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:16">
+      <c r="Q37" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17">
       <c r="B38" s="15" t="str">
         <v>0</v>
       </c>
@@ -8397,8 +8517,11 @@
       <c r="P38" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="2:16">
+      <c r="Q38" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17">
       <c r="B39" s="15" t="str">
         <v>0</v>
       </c>
@@ -8429,8 +8552,11 @@
       <c r="P39" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="2:16">
+      <c r="Q39" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
       <c r="B40" s="15" t="str">
         <v>0</v>
       </c>
@@ -8461,8 +8587,11 @@
       <c r="P40" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="2:16">
+      <c r="Q40" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17">
       <c r="B41" s="15" t="str">
         <v>0</v>
       </c>
@@ -8493,8 +8622,11 @@
       <c r="P41" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:16">
+      <c r="Q41" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17">
       <c r="B42" s="15" t="str">
         <v>0</v>
       </c>
@@ -8525,8 +8657,11 @@
       <c r="P42" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16">
+      <c r="Q42" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17">
       <c r="B43" s="15" t="str">
         <v>0</v>
       </c>
@@ -8557,8 +8692,11 @@
       <c r="P43" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16">
+      <c r="Q43" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17">
       <c r="B44" s="15" t="str">
         <v>0</v>
       </c>
@@ -8589,8 +8727,11 @@
       <c r="P44" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16">
+      <c r="Q44" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
       <c r="B45" s="15" t="str">
         <v>0</v>
       </c>
@@ -8621,8 +8762,11 @@
       <c r="P45" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16">
+      <c r="Q45" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17">
       <c r="B46" s="15" t="str">
         <v>0</v>
       </c>
@@ -8653,8 +8797,11 @@
       <c r="P46" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16">
+      <c r="Q46" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
       <c r="B47" s="15" t="str">
         <v>0</v>
       </c>
@@ -8685,8 +8832,11 @@
       <c r="P47" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:16">
+      <c r="Q47" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="15" t="str">
         <v>0</v>
       </c>
@@ -8717,8 +8867,11 @@
       <c r="P48" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:16">
+      <c r="Q48" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17">
       <c r="B49" s="15" t="str">
         <v>0</v>
       </c>
@@ -8749,8 +8902,11 @@
       <c r="P49" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:16">
+      <c r="Q49" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17">
       <c r="B50" s="15" t="str">
         <v>0</v>
       </c>
@@ -8781,8 +8937,11 @@
       <c r="P50" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="2:16">
+      <c r="Q50" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
       <c r="B51" s="15" t="str">
         <v>0</v>
       </c>
@@ -8813,8 +8972,11 @@
       <c r="P51" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="2:16">
+      <c r="Q51" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17">
       <c r="B52" s="15" t="str">
         <v>0</v>
       </c>
@@ -8845,8 +9007,11 @@
       <c r="P52" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="2:16">
+      <c r="Q52" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17">
       <c r="B53" s="15" t="str">
         <v>0</v>
       </c>
@@ -8877,8 +9042,11 @@
       <c r="P53" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="2:16">
+      <c r="Q53" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
       <c r="B54" s="15" t="str">
         <v>0</v>
       </c>
@@ -8909,8 +9077,11 @@
       <c r="P54" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="2:16">
+      <c r="Q54" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17">
       <c r="B55" s="15" t="str">
         <v>0</v>
       </c>
@@ -8941,8 +9112,11 @@
       <c r="P55" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="56" spans="2:16">
+      <c r="Q55" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17">
       <c r="B56" s="15" t="str">
         <v>0</v>
       </c>
@@ -8973,8 +9147,11 @@
       <c r="P56" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" spans="2:16">
+      <c r="Q56" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17">
       <c r="B57" s="15" t="str">
         <v>0</v>
       </c>
@@ -9005,8 +9182,11 @@
       <c r="P57" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="2:16">
+      <c r="Q57" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17">
       <c r="B58" s="15" t="str">
         <v>0</v>
       </c>
@@ -9037,8 +9217,11 @@
       <c r="P58" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="2:16">
+      <c r="Q58" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17">
       <c r="B59" s="15" t="str">
         <v>0</v>
       </c>
@@ -9069,8 +9252,11 @@
       <c r="P59" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="2:16">
+      <c r="Q59" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17">
       <c r="B60" s="15" t="str">
         <v>0</v>
       </c>
@@ -9101,8 +9287,11 @@
       <c r="P60" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="2:16">
+      <c r="Q60" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17">
       <c r="B61" s="15" t="str">
         <v>0</v>
       </c>
@@ -9133,8 +9322,11 @@
       <c r="P61" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="2:16">
+      <c r="Q61" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17">
       <c r="B62" s="15" t="str">
         <v>0</v>
       </c>
@@ -9165,8 +9357,11 @@
       <c r="P62" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="2:16">
+      <c r="Q62" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
       <c r="B63" s="15" t="str">
         <v>0</v>
       </c>
@@ -9197,8 +9392,11 @@
       <c r="P63" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="2:16">
+      <c r="Q63" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17">
       <c r="B64" s="15" t="str">
         <v>0</v>
       </c>
@@ -9229,8 +9427,11 @@
       <c r="P64" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16">
+      <c r="Q64" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17">
       <c r="B65" s="15" t="str">
         <v>0</v>
       </c>
@@ -9261,8 +9462,11 @@
       <c r="P65" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16">
+      <c r="Q65" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17">
       <c r="B66" s="15" t="str">
         <v>0</v>
       </c>
@@ -9293,8 +9497,11 @@
       <c r="P66" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:16">
+      <c r="Q66" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17">
       <c r="B67" s="15" t="str">
         <v>0</v>
       </c>
@@ -9325,8 +9532,11 @@
       <c r="P67" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="68" spans="2:16">
+      <c r="Q67" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17">
       <c r="B68" s="15" t="str">
         <v>0</v>
       </c>
@@ -9357,8 +9567,11 @@
       <c r="P68" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16">
+      <c r="Q68" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
       <c r="B69" s="15" t="str">
         <v>0</v>
       </c>
@@ -9389,8 +9602,11 @@
       <c r="P69" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16">
+      <c r="Q69" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17">
       <c r="B70" s="15" t="str">
         <v>0</v>
       </c>
@@ -9421,8 +9637,11 @@
       <c r="P70" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16">
+      <c r="Q70" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17">
       <c r="B71" s="15" t="str">
         <v>0</v>
       </c>
@@ -9453,8 +9672,11 @@
       <c r="P71" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16">
+      <c r="Q71" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17">
       <c r="B72" s="15" t="str">
         <v>0</v>
       </c>
@@ -9485,8 +9707,11 @@
       <c r="P72" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:16">
+      <c r="Q72" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
       <c r="B73" s="15" t="str">
         <v>0</v>
       </c>
@@ -9517,8 +9742,11 @@
       <c r="P73" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16">
+      <c r="Q73" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
       <c r="B74" s="15" t="str">
         <v>0</v>
       </c>
@@ -9549,8 +9777,11 @@
       <c r="P74" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16">
+      <c r="Q74" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17">
       <c r="B75" s="15" t="str">
         <v>0</v>
       </c>
@@ -9581,8 +9812,11 @@
       <c r="P75" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16">
+      <c r="Q75" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17">
       <c r="B76" s="15" t="str">
         <v>0</v>
       </c>
@@ -9613,8 +9847,11 @@
       <c r="P76" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:16">
+      <c r="Q76" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17">
       <c r="B77" s="15" t="str">
         <v>0</v>
       </c>
@@ -9645,8 +9882,11 @@
       <c r="P77" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="78" spans="2:16">
+      <c r="Q77" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17">
       <c r="B78" s="15" t="str">
         <v>0</v>
       </c>
@@ -9677,8 +9917,11 @@
       <c r="P78" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16">
+      <c r="Q78" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17">
       <c r="B79" s="15" t="str">
         <v>0</v>
       </c>
@@ -9709,8 +9952,11 @@
       <c r="P79" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="2:16">
+      <c r="Q79" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17">
       <c r="B80" s="15" t="str">
         <v>0</v>
       </c>
@@ -9741,8 +9987,11 @@
       <c r="P80" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="81" spans="2:16">
+      <c r="Q80" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17">
       <c r="B81" s="15" t="str">
         <v>0</v>
       </c>
@@ -9773,8 +10022,11 @@
       <c r="P81" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="82" spans="2:16">
+      <c r="Q81" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17">
       <c r="B82" s="15" t="str">
         <v>0</v>
       </c>
@@ -9805,8 +10057,11 @@
       <c r="P82" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="2:16">
+      <c r="Q82" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17">
       <c r="B83" s="15" t="str">
         <v>0</v>
       </c>
@@ -9837,8 +10092,11 @@
       <c r="P83" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="2:16">
+      <c r="Q83" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17">
       <c r="B84" s="15" t="str">
         <v>0</v>
       </c>
@@ -9869,8 +10127,11 @@
       <c r="P84" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="2:16">
+      <c r="Q84" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17">
       <c r="B85" s="15" t="str">
         <v>0</v>
       </c>
@@ -9901,8 +10162,11 @@
       <c r="P85" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="2:16">
+      <c r="Q85" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17">
       <c r="B86" s="15" t="str">
         <v>0</v>
       </c>
@@ -9933,8 +10197,11 @@
       <c r="P86" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="2:16">
+      <c r="Q86" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17">
       <c r="B87" s="15" t="str">
         <v>0</v>
       </c>
@@ -9965,8 +10232,11 @@
       <c r="P87" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="2:16">
+      <c r="Q87" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17">
       <c r="B88" s="15" t="str">
         <v>0</v>
       </c>
@@ -9997,8 +10267,11 @@
       <c r="P88" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="2:16">
+      <c r="Q88" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17">
       <c r="B89" s="15" t="str">
         <v>0</v>
       </c>
@@ -10029,8 +10302,11 @@
       <c r="P89" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="2:16">
+      <c r="Q89" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17">
       <c r="B90" s="15" t="str">
         <v>0</v>
       </c>
@@ -10061,8 +10337,11 @@
       <c r="P90" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="2:16">
+      <c r="Q90" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17">
       <c r="B91" s="15" t="str">
         <v>0</v>
       </c>
@@ -10093,8 +10372,11 @@
       <c r="P91" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="2:16">
+      <c r="Q91" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:17">
       <c r="B92" s="15" t="str">
         <v>0</v>
       </c>
@@ -10125,8 +10407,11 @@
       <c r="P92" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="2:16">
+      <c r="Q92" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17">
       <c r="B93" s="15" t="str">
         <v>0</v>
       </c>
@@ -10157,8 +10442,11 @@
       <c r="P93" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="2:16">
+      <c r="Q93" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17">
       <c r="B94" s="15" t="str">
         <v>0</v>
       </c>
@@ -10189,8 +10477,11 @@
       <c r="P94" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="2:16">
+      <c r="Q94" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17">
       <c r="B95" s="15" t="str">
         <v>0</v>
       </c>
@@ -10221,8 +10512,11 @@
       <c r="P95" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="2:16">
+      <c r="Q95" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17">
       <c r="B96" s="15" t="str">
         <v>0</v>
       </c>
@@ -10253,8 +10547,11 @@
       <c r="P96" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="2:16">
+      <c r="Q96" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17">
       <c r="B97" s="15" t="str">
         <v>0</v>
       </c>
@@ -10285,8 +10582,11 @@
       <c r="P97" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="2:16">
+      <c r="Q97" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17">
       <c r="B98" s="15" t="str">
         <v>0</v>
       </c>
@@ -10317,8 +10617,11 @@
       <c r="P98" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="2:16">
+      <c r="Q98" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17">
       <c r="B99" s="15" t="str">
         <v>0</v>
       </c>
@@ -10349,8 +10652,11 @@
       <c r="P99" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="2:16">
+      <c r="Q99" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17">
       <c r="B100" s="15" t="str">
         <v>0</v>
       </c>
@@ -10381,8 +10687,11 @@
       <c r="P100" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="2:16">
+      <c r="Q100" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
       <c r="B101" s="15" t="str">
         <v>0</v>
       </c>
@@ -10413,8 +10722,11 @@
       <c r="P101" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="2:16">
+      <c r="Q101" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17">
       <c r="B102" s="15" t="str">
         <v>0</v>
       </c>
@@ -10445,8 +10757,11 @@
       <c r="P102" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="103" spans="2:16">
+      <c r="Q102" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17">
       <c r="B103" s="15" t="str">
         <v>0</v>
       </c>
@@ -10477,8 +10792,11 @@
       <c r="P103" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="2:16">
+      <c r="Q103" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17">
       <c r="B104" s="15" t="str">
         <v>0</v>
       </c>
@@ -10509,8 +10827,11 @@
       <c r="P104" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="2:16">
+      <c r="Q104" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17">
       <c r="B105" s="15" t="str">
         <v>0</v>
       </c>
@@ -10541,8 +10862,11 @@
       <c r="P105" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="106" spans="2:16">
+      <c r="Q105" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17">
       <c r="B106" s="15" t="str">
         <v>0</v>
       </c>
@@ -10573,8 +10897,11 @@
       <c r="P106" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="107" spans="2:16">
+      <c r="Q106" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17">
       <c r="B107" s="15" t="str">
         <v>0</v>
       </c>
@@ -10605,8 +10932,11 @@
       <c r="P107" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="108" spans="2:16">
+      <c r="Q107" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17">
       <c r="B108" s="15" t="str">
         <v>0</v>
       </c>
@@ -10637,8 +10967,11 @@
       <c r="P108" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="109" spans="2:16">
+      <c r="Q108" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17">
       <c r="B109" s="15" t="str">
         <v>0</v>
       </c>
@@ -10669,8 +11002,11 @@
       <c r="P109" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="110" spans="2:16">
+      <c r="Q109" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
       <c r="B110" s="15" t="str">
         <v>0</v>
       </c>
@@ -10701,8 +11037,11 @@
       <c r="P110" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="111" spans="2:16">
+      <c r="Q110" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17">
       <c r="B111" s="15" t="str">
         <v>0</v>
       </c>
@@ -10733,8 +11072,11 @@
       <c r="P111" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="112" spans="2:16">
+      <c r="Q111" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17">
       <c r="B112" s="15" t="str">
         <v>0</v>
       </c>
@@ -10765,8 +11107,11 @@
       <c r="P112" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="113" spans="2:16">
+      <c r="Q112" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17">
       <c r="B113" s="15" t="str">
         <v>0</v>
       </c>
@@ -10797,8 +11142,11 @@
       <c r="P113" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="114" spans="2:16">
+      <c r="Q113" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17">
       <c r="B114" s="15" t="str">
         <v>0</v>
       </c>
@@ -10829,8 +11177,11 @@
       <c r="P114" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="115" spans="2:16">
+      <c r="Q114" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17">
       <c r="B115" s="15" t="str">
         <v>0</v>
       </c>
@@ -10861,8 +11212,11 @@
       <c r="P115" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="116" spans="2:16">
+      <c r="Q115" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17">
       <c r="B116" s="15" t="str">
         <v>0</v>
       </c>
@@ -10893,8 +11247,11 @@
       <c r="P116" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="117" spans="2:16">
+      <c r="Q116" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17">
       <c r="B117" s="15" t="str">
         <v>0</v>
       </c>
@@ -10925,8 +11282,11 @@
       <c r="P117" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="2:16">
+      <c r="Q117" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17">
       <c r="B118" s="15" t="str">
         <v>0</v>
       </c>
@@ -10957,8 +11317,11 @@
       <c r="P118" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="119" spans="2:16">
+      <c r="Q118" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17">
       <c r="B119" s="15" t="str">
         <v>0</v>
       </c>
@@ -10989,8 +11352,11 @@
       <c r="P119" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="120" spans="2:16">
+      <c r="Q119" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17">
       <c r="B120" s="15" t="str">
         <v>0</v>
       </c>
@@ -11021,8 +11387,11 @@
       <c r="P120" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="121" spans="2:16">
+      <c r="Q120" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17">
       <c r="B121" s="15" t="str">
         <v>0</v>
       </c>
@@ -11053,8 +11422,11 @@
       <c r="P121" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="122" spans="2:16">
+      <c r="Q121" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17">
       <c r="B122" s="15" t="str">
         <v>0</v>
       </c>
@@ -11085,8 +11457,11 @@
       <c r="P122" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="123" spans="2:16">
+      <c r="Q122" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17">
       <c r="B123" s="15" t="str">
         <v>0</v>
       </c>
@@ -11117,8 +11492,11 @@
       <c r="P123" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="124" spans="2:16">
+      <c r="Q123" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17">
       <c r="B124" s="15" t="str">
         <v>0</v>
       </c>
@@ -11149,8 +11527,11 @@
       <c r="P124" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="125" spans="2:16">
+      <c r="Q124" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17">
       <c r="B125" s="15" t="str">
         <v>0</v>
       </c>
@@ -11181,8 +11562,11 @@
       <c r="P125" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="126" spans="2:16">
+      <c r="Q125" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17">
       <c r="B126" s="15" t="str">
         <v>0</v>
       </c>
@@ -11213,8 +11597,11 @@
       <c r="P126" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="127" spans="2:16">
+      <c r="Q126" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17">
       <c r="B127" s="15" t="str">
         <v>0</v>
       </c>
@@ -11245,8 +11632,11 @@
       <c r="P127" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="128" spans="2:16">
+      <c r="Q127" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17">
       <c r="B128" s="15" t="str">
         <v>0</v>
       </c>
@@ -11277,8 +11667,11 @@
       <c r="P128" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="129" spans="2:16">
+      <c r="Q128" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17">
       <c r="B129" s="15" t="str">
         <v>0</v>
       </c>
@@ -11309,8 +11702,11 @@
       <c r="P129" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="130" spans="2:16">
+      <c r="Q129" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17">
       <c r="B130" s="15" t="str">
         <v>0</v>
       </c>
@@ -11341,8 +11737,11 @@
       <c r="P130" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="131" spans="2:16">
+      <c r="Q130" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17">
       <c r="B131" s="15" t="str">
         <v>0</v>
       </c>
@@ -11373,8 +11772,11 @@
       <c r="P131" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="132" spans="2:16">
+      <c r="Q131" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17">
       <c r="B132" s="15" t="str">
         <v>0</v>
       </c>
@@ -11405,8 +11807,11 @@
       <c r="P132" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="133" spans="2:16">
+      <c r="Q132" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17">
       <c r="B133" s="15" t="str">
         <v>0</v>
       </c>
@@ -11437,8 +11842,11 @@
       <c r="P133" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="134" spans="2:16">
+      <c r="Q133" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17">
       <c r="B134" s="15" t="str">
         <v>0</v>
       </c>
@@ -11469,8 +11877,11 @@
       <c r="P134" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="135" spans="2:16">
+      <c r="Q134" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17">
       <c r="B135" s="15" t="str">
         <v>0</v>
       </c>
@@ -11501,8 +11912,11 @@
       <c r="P135" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="136" spans="2:16">
+      <c r="Q135" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17">
       <c r="B136" s="15" t="str">
         <v>0</v>
       </c>
@@ -11533,8 +11947,11 @@
       <c r="P136" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="137" spans="2:16">
+      <c r="Q136" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17">
       <c r="B137" s="15" t="str">
         <v>0</v>
       </c>
@@ -11565,8 +11982,11 @@
       <c r="P137" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="138" spans="2:16">
+      <c r="Q137" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17">
       <c r="B138" s="15" t="str">
         <v>0</v>
       </c>
@@ -11597,8 +12017,11 @@
       <c r="P138" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="139" spans="2:16">
+      <c r="Q138" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17">
       <c r="B139" s="15" t="str">
         <v>0</v>
       </c>
@@ -11629,8 +12052,11 @@
       <c r="P139" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="140" spans="2:16">
+      <c r="Q139" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17">
       <c r="B140" s="15" t="str">
         <v>0</v>
       </c>
@@ -11661,8 +12087,11 @@
       <c r="P140" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="141" spans="2:16">
+      <c r="Q140" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17">
       <c r="B141" s="15" t="str">
         <v>0</v>
       </c>
@@ -11693,8 +12122,11 @@
       <c r="P141" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="142" spans="2:16">
+      <c r="Q141" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17">
       <c r="B142" s="15" t="str">
         <v>0</v>
       </c>
@@ -11725,8 +12157,11 @@
       <c r="P142" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="143" spans="2:16">
+      <c r="Q142" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17">
       <c r="B143" s="15" t="str">
         <v>0</v>
       </c>
@@ -11757,8 +12192,11 @@
       <c r="P143" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="2:16">
+      <c r="Q143" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17">
       <c r="B144" s="15" t="str">
         <v>0</v>
       </c>
@@ -11789,8 +12227,11 @@
       <c r="P144" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="145" spans="2:16">
+      <c r="Q144" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17">
       <c r="B145" s="15" t="str">
         <v>0</v>
       </c>
@@ -11821,8 +12262,11 @@
       <c r="P145" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="146" spans="2:16">
+      <c r="Q145" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:17">
       <c r="B146" s="15" t="str">
         <v>0</v>
       </c>
@@ -11853,8 +12297,11 @@
       <c r="P146" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="147" spans="2:16">
+      <c r="Q146" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17">
       <c r="B147" s="15" t="str">
         <v>0</v>
       </c>
@@ -11885,8 +12332,11 @@
       <c r="P147" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="148" spans="2:16">
+      <c r="Q147" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17">
       <c r="B148" s="15" t="str">
         <v>0</v>
       </c>
@@ -11917,8 +12367,11 @@
       <c r="P148" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="149" spans="2:16">
+      <c r="Q148" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17">
       <c r="B149" s="15" t="str">
         <v>0</v>
       </c>
@@ -11949,8 +12402,11 @@
       <c r="P149" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="150" spans="2:16">
+      <c r="Q149" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:17">
       <c r="B150" s="15" t="str">
         <v>0</v>
       </c>
@@ -11981,8 +12437,11 @@
       <c r="P150" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="151" spans="2:16">
+      <c r="Q150" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17">
       <c r="B151" s="15" t="str">
         <v>0</v>
       </c>
@@ -12013,8 +12472,11 @@
       <c r="P151" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="152" spans="2:16">
+      <c r="Q151" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17">
       <c r="B152" s="15" t="str">
         <v>0</v>
       </c>
@@ -12045,8 +12507,11 @@
       <c r="P152" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="153" spans="2:16">
+      <c r="Q152" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17">
       <c r="B153" s="15" t="str">
         <v>0</v>
       </c>
@@ -12077,8 +12542,11 @@
       <c r="P153" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="154" spans="2:16">
+      <c r="Q153" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17">
       <c r="B154" s="15" t="str">
         <v>0</v>
       </c>
@@ -12109,8 +12577,11 @@
       <c r="P154" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="155" spans="2:16">
+      <c r="Q154" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17">
       <c r="B155" s="15" t="str">
         <v>0</v>
       </c>
@@ -12141,8 +12612,11 @@
       <c r="P155" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="156" spans="2:16">
+      <c r="Q155" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:17">
       <c r="B156" s="15" t="str">
         <v>0</v>
       </c>
@@ -12173,8 +12647,11 @@
       <c r="P156" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="157" spans="2:16">
+      <c r="Q156" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17">
       <c r="B157" s="15" t="str">
         <v>0</v>
       </c>
@@ -12205,8 +12682,11 @@
       <c r="P157" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="158" spans="2:16">
+      <c r="Q157" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17">
       <c r="B158" s="15" t="str">
         <v>0</v>
       </c>
@@ -12237,8 +12717,11 @@
       <c r="P158" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="159" spans="2:16">
+      <c r="Q158" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17">
       <c r="B159" s="15" t="str">
         <v>0</v>
       </c>
@@ -12269,8 +12752,11 @@
       <c r="P159" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="160" spans="2:16">
+      <c r="Q159" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17">
       <c r="B160" s="15" t="str">
         <v>0</v>
       </c>
@@ -12301,8 +12787,11 @@
       <c r="P160" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="161" spans="2:16">
+      <c r="Q160" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:17">
       <c r="B161" s="15" t="str">
         <v>0</v>
       </c>
@@ -12333,8 +12822,11 @@
       <c r="P161" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="162" spans="2:16">
+      <c r="Q161" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:17">
       <c r="B162" s="15" t="str">
         <v>0</v>
       </c>
@@ -12365,8 +12857,11 @@
       <c r="P162" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="163" spans="2:16">
+      <c r="Q162" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="2:17">
       <c r="B163" s="15" t="str">
         <v>0</v>
       </c>
@@ -12397,8 +12892,11 @@
       <c r="P163" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="164" spans="2:16">
+      <c r="Q163" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="2:17">
       <c r="B164" s="15" t="str">
         <v>0</v>
       </c>
@@ -12429,8 +12927,11 @@
       <c r="P164" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="165" spans="2:16">
+      <c r="Q164" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="2:17">
       <c r="B165" s="15" t="str">
         <v>0</v>
       </c>
@@ -12461,8 +12962,11 @@
       <c r="P165" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="166" spans="2:16">
+      <c r="Q165" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="2:17">
       <c r="B166" s="15" t="str">
         <v>0</v>
       </c>
@@ -12493,8 +12997,11 @@
       <c r="P166" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="167" spans="2:16">
+      <c r="Q166" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="2:17">
       <c r="B167" s="15" t="str">
         <v>0</v>
       </c>
@@ -12525,8 +13032,11 @@
       <c r="P167" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="168" spans="2:16">
+      <c r="Q167" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="2:17">
       <c r="B168" s="15" t="str">
         <v>0</v>
       </c>
@@ -12557,8 +13067,11 @@
       <c r="P168" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="169" spans="2:16">
+      <c r="Q168" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="2:17">
       <c r="B169" s="15" t="str">
         <v>0</v>
       </c>
@@ -12589,8 +13102,11 @@
       <c r="P169" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="170" spans="2:16">
+      <c r="Q169" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="2:17">
       <c r="B170" s="15" t="str">
         <v>0</v>
       </c>
@@ -12621,8 +13137,11 @@
       <c r="P170" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="171" spans="2:16">
+      <c r="Q170" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="2:17">
       <c r="B171" s="15" t="str">
         <v>0</v>
       </c>
@@ -12653,8 +13172,11 @@
       <c r="P171" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="172" spans="2:16">
+      <c r="Q171" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="2:17">
       <c r="B172" s="15" t="str">
         <v>0</v>
       </c>
@@ -12685,8 +13207,11 @@
       <c r="P172" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="173" spans="2:16">
+      <c r="Q172" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="2:17">
       <c r="B173" s="15" t="str">
         <v>0</v>
       </c>
@@ -12717,8 +13242,11 @@
       <c r="P173" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="174" spans="2:16">
+      <c r="Q173" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="2:17">
       <c r="B174" s="15" t="str">
         <v>0</v>
       </c>
@@ -12749,8 +13277,11 @@
       <c r="P174" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="175" spans="2:16">
+      <c r="Q174" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="2:17">
       <c r="B175" s="15" t="str">
         <v>0</v>
       </c>
@@ -12781,8 +13312,11 @@
       <c r="P175" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="176" spans="2:16">
+      <c r="Q175" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="2:17">
       <c r="B176" s="15" t="str">
         <v>0</v>
       </c>
@@ -12813,8 +13347,11 @@
       <c r="P176" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="177" spans="2:16">
+      <c r="Q176" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="2:17">
       <c r="B177" s="15" t="str">
         <v>0</v>
       </c>
@@ -12845,8 +13382,11 @@
       <c r="P177" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="178" spans="2:16">
+      <c r="Q177" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="2:17">
       <c r="B178" s="15" t="str">
         <v>0</v>
       </c>
@@ -12877,8 +13417,11 @@
       <c r="P178" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="179" spans="2:16">
+      <c r="Q178" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="2:17">
       <c r="B179" s="15" t="str">
         <v>0</v>
       </c>
@@ -12909,8 +13452,11 @@
       <c r="P179" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="180" spans="2:16">
+      <c r="Q179" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="2:17">
       <c r="B180" s="15" t="str">
         <v>0</v>
       </c>
@@ -12941,8 +13487,11 @@
       <c r="P180" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="181" spans="2:16">
+      <c r="Q180" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:17">
       <c r="B181" s="15" t="str">
         <v>0</v>
       </c>
@@ -12973,8 +13522,11 @@
       <c r="P181" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="182" spans="2:16">
+      <c r="Q181" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="2:17">
       <c r="B182" s="15" t="str">
         <v>0</v>
       </c>
@@ -13005,8 +13557,11 @@
       <c r="P182" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="183" spans="2:16">
+      <c r="Q182" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="2:17">
       <c r="B183" s="15" t="str">
         <v>0</v>
       </c>
@@ -13037,8 +13592,11 @@
       <c r="P183" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="184" spans="2:16">
+      <c r="Q183" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="2:17">
       <c r="B184" s="15" t="str">
         <v>0</v>
       </c>
@@ -13069,8 +13627,11 @@
       <c r="P184" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="185" spans="2:16">
+      <c r="Q184" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="2:17">
       <c r="B185" s="15" t="str">
         <v>0</v>
       </c>
@@ -13101,8 +13662,11 @@
       <c r="P185" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="186" spans="2:16">
+      <c r="Q185" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="2:17">
       <c r="B186" s="15" t="str">
         <v>0</v>
       </c>
@@ -13133,8 +13697,11 @@
       <c r="P186" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="187" spans="2:16">
+      <c r="Q186" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="2:17">
       <c r="B187" s="15" t="str">
         <v>0</v>
       </c>
@@ -13165,8 +13732,11 @@
       <c r="P187" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="188" spans="2:16">
+      <c r="Q187" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:17">
       <c r="B188" s="15" t="str">
         <v>0</v>
       </c>
@@ -13197,8 +13767,11 @@
       <c r="P188" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="189" spans="2:16">
+      <c r="Q188" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="2:17">
       <c r="B189" s="15" t="str">
         <v>0</v>
       </c>
@@ -13229,8 +13802,11 @@
       <c r="P189" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="190" spans="2:16">
+      <c r="Q189" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="2:17">
       <c r="B190" s="15" t="str">
         <v>0</v>
       </c>
@@ -13261,8 +13837,11 @@
       <c r="P190" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="191" spans="2:16">
+      <c r="Q190" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="2:17">
       <c r="B191" s="15" t="str">
         <v>0</v>
       </c>
@@ -13293,8 +13872,11 @@
       <c r="P191" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="192" spans="2:16">
+      <c r="Q191" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="2:17">
       <c r="B192" s="15" t="str">
         <v>0</v>
       </c>
@@ -13325,8 +13907,11 @@
       <c r="P192" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="193" spans="2:16">
+      <c r="Q192" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="2:17">
       <c r="B193" s="15" t="str">
         <v>0</v>
       </c>
@@ -13357,8 +13942,11 @@
       <c r="P193" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="194" spans="2:16">
+      <c r="Q193" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="2:17">
       <c r="B194" s="15" t="str">
         <v>0</v>
       </c>
@@ -13389,8 +13977,11 @@
       <c r="P194" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="195" spans="2:16">
+      <c r="Q194" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="2:17">
       <c r="B195" s="15" t="str">
         <v>0</v>
       </c>
@@ -13421,8 +14012,11 @@
       <c r="P195" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="196" spans="2:16">
+      <c r="Q195" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="2:17">
       <c r="B196" s="15" t="str">
         <v>0</v>
       </c>
@@ -13453,8 +14047,11 @@
       <c r="P196" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="197" spans="2:16">
+      <c r="Q196" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="2:17">
       <c r="B197" s="15" t="str">
         <v>0</v>
       </c>
@@ -13485,8 +14082,11 @@
       <c r="P197" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="198" spans="2:16">
+      <c r="Q197" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="2:17">
       <c r="B198" s="15" t="str">
         <v>0</v>
       </c>
@@ -13517,8 +14117,11 @@
       <c r="P198" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="199" spans="2:16">
+      <c r="Q198" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="2:17">
       <c r="B199" s="15" t="str">
         <v>0</v>
       </c>
@@ -13549,8 +14152,11 @@
       <c r="P199" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="200" spans="2:16">
+      <c r="Q199" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="2:17">
       <c r="B200" s="15" t="str">
         <v>0</v>
       </c>
@@ -13581,8 +14187,11 @@
       <c r="P200" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="201" spans="2:15">
+      <c r="Q200" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="2:17">
       <c r="B201" s="15" t="str">
         <v>0</v>
       </c>
@@ -13611,7 +14220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:15">
+    <row r="202" spans="2:17">
       <c r="B202" s="15" t="str">
         <v>0</v>
       </c>
@@ -13640,7 +14249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="2:15">
+    <row r="203" spans="2:17">
       <c r="B203" s="15" t="str">
         <v>0</v>
       </c>
@@ -13669,7 +14278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="2:15">
+    <row r="204" spans="2:17">
       <c r="B204" s="15" t="str">
         <v>0</v>
       </c>
@@ -13698,7 +14307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="2:15">
+    <row r="205" spans="2:17">
       <c r="B205" s="15" t="str">
         <v>0</v>
       </c>
@@ -13727,7 +14336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="2:15">
+    <row r="206" spans="2:17">
       <c r="B206" s="15" t="str">
         <v>0</v>
       </c>
@@ -13756,7 +14365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="2:15">
+    <row r="207" spans="2:17">
       <c r="B207" s="15" t="str">
         <v>0</v>
       </c>
@@ -13785,7 +14394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="2:15">
+    <row r="208" spans="2:17">
       <c r="B208" s="15" t="str">
         <v>0</v>
       </c>
@@ -16498,199 +17107,224 @@
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
-  <sheetFormatPr defaultColWidth="52" defaultRowHeight="16.8"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultColWidth="52" defaultRowHeight="43.2"/>
   <cols>
-    <col min="1" max="1" width="23.7857142857143" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.0714285714286" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7857142857143" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85714285714286" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.9285714285714" style="1" customWidth="1"/>
-    <col min="7" max="8" width="12.7142857142857" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="18.2857142857143" style="1" customWidth="1"/>
-    <col min="11" max="11" width="5.57142857142857" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.2857142857143" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1428571428571" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33.2857142857143" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.3571428571429" style="1" customWidth="1"/>
+    <col min="5" max="5" width="31.0714285714286" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5714285714286" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.2142857142857" style="1" customWidth="1"/>
+    <col min="10" max="10" width="19.7857142857143" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7857142857143" style="1" customWidth="1"/>
     <col min="12" max="16384" width="52" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" spans="1:6">
+    <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3" t="str">
+        <f ca="1">TEXT(TODAY(),"yyyy年m月")</f>
+        <v>2025年11月</v>
+      </c>
+      <c r="F1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="3">
+        <f>J14</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3">
+        <f>H8</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="4">
+        <f>I9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="7"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="6" t="str">
-        <f ca="1">TEXT(TODAY(),"yyyy年m月")</f>
-        <v>2025年7月</v>
-      </c>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" ht="28.8" spans="1:6">
-      <c r="A2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2" s="5"/>
-    </row>
-    <row r="3" ht="28.8" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <f>B3-D3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="40" spans="7:10">
-      <c r="G4" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="14"/>
-    </row>
-    <row r="5" ht="40" spans="7:10">
-      <c r="G5" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="11" t="s">
+      <c r="I5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="9">
+        <v>500</v>
+      </c>
+      <c r="J6" s="9">
+        <f>H6/I6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="E7" s="11"/>
+      <c r="G7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="9">
+        <v>1000</v>
+      </c>
+      <c r="J7" s="9">
+        <f>H7/I7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="E8" s="11"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9">
+        <f>SUM(H6:H7)</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9">
+        <f>SUM(J6:J7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13">
+        <f>J14-H8</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="13"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="E10" s="11"/>
+      <c r="G10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="7"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="G11" s="9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" ht="40" spans="5:10">
-      <c r="E6" s="12"/>
-      <c r="G6" s="11" t="s">
+      <c r="H11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="11">
+      <c r="J11" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="G12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="10"/>
+      <c r="I12" s="9">
         <v>500</v>
       </c>
-      <c r="J6" s="11">
-        <f>H6/I6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="40" spans="5:10">
-      <c r="E7" s="12"/>
-      <c r="G7" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="11">
+      <c r="J12" s="9">
+        <f>H12*I12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="G13" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="10"/>
+      <c r="I13" s="9">
         <v>1000</v>
       </c>
-      <c r="J7" s="11">
-        <f>H7/I7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="40" spans="5:11">
-      <c r="E8" s="12"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11">
-        <f>SUM(H6:H7)</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11">
-        <f>SUM(J6:J7)</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <f>4904+719</f>
-        <v>5623</v>
-      </c>
-    </row>
-    <row r="9" ht="40" spans="5:5">
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" ht="40" spans="5:10">
-      <c r="E10" s="12"/>
-      <c r="G10" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="14"/>
-    </row>
-    <row r="11" ht="40" spans="7:10">
-      <c r="G11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="12" ht="40" spans="7:10">
-      <c r="G12" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="11">
-        <v>500</v>
-      </c>
-      <c r="J12" s="11">
-        <f>H12*I12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="40" spans="7:10">
-      <c r="G13" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="11">
-        <v>1000</v>
-      </c>
-      <c r="J13" s="11">
+      <c r="J13" s="9">
         <f>H13*I13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="40" spans="7:10">
-      <c r="G14" s="11"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11">
+    <row r="14" spans="1:10">
+      <c r="G14" s="9"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9">
         <f>SUM(J12:J13)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <sheetProtection sheet="1" objects="1"/>
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
     <mergeCell ref="G10:J10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hema/3-单袋比.xlsx
+++ b/hema/3-单袋比.xlsx
@@ -243,7 +243,7 @@
     <t>签收单</t>
   </si>
   <si>
-    <t>刘强新</t>
+    <t>请输入名字</t>
   </si>
   <si>
     <t>校准</t>
@@ -1970,44 +1970,26 @@
       <c r="A5" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="53" t="e">
-        <f>DGET(代码!$A$1:$H$300,B$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C5" s="53" t="e">
-        <f>DGET(代码!$A$1:$H$300,C$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D5" s="53" t="e">
-        <f>DGET(代码!$A$1:$H$300,D$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="E5" s="53" t="e">
-        <f>DGET(代码!$A$1:$H$300,E$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="F5" s="61" t="e">
-        <f>DGET(代码!$A$1:$H$300,F$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="G5" s="59" t="e">
-        <f>DGET(代码!$A$1:$H$300,G$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H5" s="53" t="e">
-        <f>DGET(代码!$A$1:$H$300,H$4,$A$4:$A$5)</f>
-        <v>#VALUE!</v>
-      </c>
+      <c r="B5" s="53" t="e" cm="1">
+        <f t="array" ref="B5">_xlfn._xlws.FILTER(代码!$B$2:$H$300,代码!$A$2:$A$300=$A5,"")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="53"/>
       <c r="J5" s="44" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="62" t="e">
         <f>(B5+D5+F5)/B2+N("（需补数量+确认数量+当日申请）/单袋比")</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
       <c r="L5" s="46" t="e">
         <f>(B5+D5)/(C5+E5)</f>
-        <v>#VALUE!</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="6" s="42" customFormat="1" spans="1:12">

--- a/hema/3-单袋比.xlsx
+++ b/hema/3-单袋比.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="16760" activeTab="1"/>
+    <workbookView windowHeight="17100" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="盘点表" sheetId="2" r:id="rId1"/>
@@ -192,9 +192,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>购物袋差异</t>
+  </si>
+  <si>
+    <t>1.0以下</t>
+  </si>
+  <si>
+    <t>1.0～1.29</t>
+  </si>
+  <si>
+    <t>1.3以上</t>
   </si>
   <si>
     <t>单袋比</t>
@@ -1880,7 +1889,7 @@
     <row r="1" spans="1:12">
       <c r="A1" s="47">
         <f ca="1">TODAY()</f>
-        <v>45983</v>
+        <v>46009</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -1892,16 +1901,25 @@
       <c r="G1" s="48"/>
       <c r="H1" s="48"/>
       <c r="I1" s="50"/>
+      <c r="J1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="44" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="51" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="52">
         <v>1.3</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" s="53">
         <f>代码!K1</f>
@@ -1909,17 +1927,29 @@
       </c>
       <c r="E2" s="53"/>
       <c r="F2" s="54" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G2" s="55">
         <f>代码!K2</f>
         <v>0</v>
       </c>
       <c r="H2" s="55"/>
+      <c r="J2" s="44">
+        <f>COUNTIF(G8:G300,"&lt;1.0")</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="44">
+        <f>COUNTIFS(G8:G300,"&gt;=1.0",G8:G300,"&lt;=1.29")</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="44">
+        <f>COUNTIF(G8:G300,"&gt;1.3")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" s="41" customFormat="1" ht="51.2" spans="1:12">
       <c r="A3" s="56" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3" s="56"/>
       <c r="C3" s="56"/>
@@ -1932,43 +1962,43 @@
     </row>
     <row r="4" s="41" customFormat="1" ht="58" spans="1:12">
       <c r="A4" s="57" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" s="57" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G4" s="59" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="57" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I4" s="44"/>
       <c r="J4" s="44" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K4" s="46" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L4" s="46" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" s="42" customFormat="1" spans="1:12">
       <c r="A5" s="60" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" s="53" t="e" cm="1">
         <f t="array" ref="B5">_xlfn._xlws.FILTER(代码!$B$2:$H$300,代码!$A$2:$A$300=$A5,"")</f>
@@ -1981,7 +2011,7 @@
       <c r="G5" s="59"/>
       <c r="H5" s="53"/>
       <c r="J5" s="44" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K5" s="62" t="e">
         <f>(B5+D5+F5)/B2+N("（需补数量+确认数量+当日申请）/单袋比")</f>
@@ -7122,32 +7152,32 @@
   <sheetData>
     <row r="1" ht="47" spans="1:115">
       <c r="A1" s="18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F1" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G1" s="20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I1" s="20"/>
       <c r="J1" s="20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K1" s="15">
         <f>SUMIF(F:F,"&gt;1")</f>
@@ -7155,22 +7185,22 @@
       </c>
       <c r="L1" s="19"/>
       <c r="M1" s="15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O1" s="15" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R1" s="15" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" ht="24" spans="1:115">
@@ -7207,7 +7237,7 @@
         <v>缺勤</v>
       </c>
       <c r="J2" s="17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K2" s="15">
         <f>SUMIF(F:F,"&lt;0")</f>
@@ -7218,7 +7248,7 @@
         <v/>
       </c>
       <c r="N2" s="15" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="O2" s="15" t="e" cm="1">
         <f t="array" ref="O2:O300">IF(COUNTIF(F2:F300,0)=0,"",_xlfn._xlws.FILTER(A2:A300,F2:F300=0))</f>
@@ -7234,7 +7264,7 @@
       </c>
       <c r="R2" s="21">
         <f ca="1">TODAY()</f>
-        <v>45983</v>
+        <v>46009</v>
       </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
@@ -17108,48 +17138,48 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="str">
         <f ca="1">TEXT(TODAY(),"yyyy年m月")</f>
-        <v>2025年11月</v>
+        <v>2025年12月</v>
       </c>
       <c r="F1" s="3"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <f>J14</f>
         <v>0</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" s="3">
         <f>H8</f>
         <v>0</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F3" s="4">
         <f>I9</f>
@@ -17164,7 +17194,7 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
@@ -17174,23 +17204,23 @@
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="9">
@@ -17204,7 +17234,7 @@
     <row r="7" spans="1:10">
       <c r="E7" s="11"/>
       <c r="G7" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="9">
@@ -17232,7 +17262,7 @@
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="13">
@@ -17244,7 +17274,7 @@
     <row r="10" spans="1:10">
       <c r="E10" s="11"/>
       <c r="G10" s="14" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -17252,21 +17282,21 @@
     </row>
     <row r="11" spans="1:10">
       <c r="G11" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="G12" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H12" s="10"/>
       <c r="I12" s="9">
@@ -17279,7 +17309,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="G13" s="9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H13" s="10"/>
       <c r="I13" s="9">

--- a/hema/3-单袋比.xlsx
+++ b/hema/3-单袋比.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17100" activeTab="1"/>
+    <workbookView windowHeight="15560" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="盘点表" sheetId="2" r:id="rId1"/>
@@ -200,10 +200,10 @@
     <t>1.0以下</t>
   </si>
   <si>
-    <t>1.0～1.29</t>
+    <t>1.0～1.19</t>
   </si>
   <si>
-    <t>1.3以上</t>
+    <t>1.2以上</t>
   </si>
   <si>
     <t>单袋比</t>
@@ -1873,23 +1873,24 @@
   <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="36.5" defaultRowHeight="28.8"/>
   <cols>
-    <col min="1" max="1" width="13.2142857142857" style="44" customWidth="1"/>
+    <col min="1" max="1" width="21.1428571428571" style="44" customWidth="1"/>
     <col min="2" max="2" width="15.7142857142857" style="44" customWidth="1"/>
     <col min="3" max="3" width="17.1428571428571" style="44" customWidth="1"/>
     <col min="4" max="5" width="12.1428571428571" style="44" customWidth="1"/>
-    <col min="6" max="6" width="19.2142857142857" style="45" customWidth="1"/>
+    <col min="6" max="6" width="17.1428571428571" style="45" customWidth="1"/>
     <col min="7" max="7" width="21.1428571428571" style="46" customWidth="1"/>
     <col min="8" max="8" width="15.7142857142857" style="44" customWidth="1"/>
     <col min="9" max="9" width="13.1607142857143" style="44" customWidth="1"/>
-    <col min="10" max="10" width="17.1428571428571" style="44" customWidth="1"/>
-    <col min="11" max="12" width="15.7142857142857" style="44" customWidth="1"/>
+    <col min="10" max="10" width="15.7142857142857" style="44" customWidth="1"/>
+    <col min="11" max="11" width="19" style="44" customWidth="1"/>
+    <col min="12" max="12" width="15.7142857142857" style="44" customWidth="1"/>
     <col min="13" max="16384" width="36.5" style="44"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="47">
         <f ca="1">TODAY()</f>
-        <v>46009</v>
+        <v>46032</v>
       </c>
       <c r="B1" s="47"/>
       <c r="C1" s="47"/>
@@ -1916,7 +1917,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="52">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>5</v>
@@ -1939,11 +1940,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="44">
-        <f>COUNTIFS(G8:G300,"&gt;=1.0",G8:G300,"&lt;=1.29")</f>
+        <f>COUNTIFS(G8:G300,"&gt;=1.0",G8:G300,"&lt;=1.19")</f>
         <v>0</v>
       </c>
       <c r="L2" s="44">
-        <f>COUNTIF(G8:G300,"&gt;1.3")</f>
+        <f>COUNTIF(G8:G300,"&gt;1.2")</f>
         <v>0</v>
       </c>
     </row>
@@ -7264,7 +7265,7 @@
       </c>
       <c r="R2" s="21">
         <f ca="1">TODAY()</f>
-        <v>46009</v>
+        <v>46032</v>
       </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
@@ -17145,7 +17146,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="str">
         <f ca="1">TEXT(TODAY(),"yyyy年m月")</f>
-        <v>2025年12月</v>
+        <v>2026年1月</v>
       </c>
       <c r="F1" s="3"/>
     </row>

--- a/hema/3-单袋比.xlsx
+++ b/hema/3-单袋比.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="15560" activeTab="1"/>
+    <workbookView windowWidth="32000" windowHeight="17120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="盘点表" sheetId="2" r:id="rId1"/>
@@ -337,7 +337,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="13">
+  <numFmts count="12">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
@@ -348,9 +348,8 @@
     <numFmt numFmtId="179" formatCode="0_ "/>
     <numFmt numFmtId="180" formatCode="0.00_ "/>
     <numFmt numFmtId="181" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
-    <numFmt numFmtId="182" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="183" formatCode="&quot;需&quot;&quot;补&quot;\:???0;[Red]&quot;超&quot;&quot;标&quot;\:???0"/>
-    <numFmt numFmtId="184" formatCode="0&quot;单&quot;"/>
+    <numFmt numFmtId="182" formatCode="&quot;需&quot;&quot;补&quot;\:???0;[Red]&quot;超&quot;&quot;标&quot;\:???0"/>
+    <numFmt numFmtId="183" formatCode="0&quot;单&quot;"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -1187,7 +1186,7 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="62">
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1275,58 +1274,40 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="182" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="58" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1347,7 +1328,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1363,7 +1344,7 @@
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1383,7 +1364,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1399,7 +1380,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1411,11 +1392,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0" hidden="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="184" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="183" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1423,7 +1404,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="183" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1873,374 +1854,374 @@
   <dimension ref="A1:L62"/>
   <sheetFormatPr defaultColWidth="36.5" defaultRowHeight="28.8"/>
   <cols>
-    <col min="1" max="1" width="21.1428571428571" style="44" customWidth="1"/>
-    <col min="2" max="2" width="15.7142857142857" style="44" customWidth="1"/>
-    <col min="3" max="3" width="17.1428571428571" style="44" customWidth="1"/>
-    <col min="4" max="5" width="12.1428571428571" style="44" customWidth="1"/>
-    <col min="6" max="6" width="17.1428571428571" style="45" customWidth="1"/>
-    <col min="7" max="7" width="21.1428571428571" style="46" customWidth="1"/>
-    <col min="8" max="8" width="15.7142857142857" style="44" customWidth="1"/>
-    <col min="9" max="9" width="13.1607142857143" style="44" customWidth="1"/>
-    <col min="10" max="10" width="15.7142857142857" style="44" customWidth="1"/>
-    <col min="11" max="11" width="19" style="44" customWidth="1"/>
-    <col min="12" max="12" width="15.7142857142857" style="44" customWidth="1"/>
-    <col min="13" max="16384" width="36.5" style="44"/>
+    <col min="1" max="1" width="21.1428571428571" style="38" customWidth="1"/>
+    <col min="2" max="2" width="15.7142857142857" style="38" customWidth="1"/>
+    <col min="3" max="3" width="17.1428571428571" style="38" customWidth="1"/>
+    <col min="4" max="5" width="12.1428571428571" style="38" customWidth="1"/>
+    <col min="6" max="6" width="17.1428571428571" style="39" customWidth="1"/>
+    <col min="7" max="7" width="21.1428571428571" style="40" customWidth="1"/>
+    <col min="8" max="8" width="15.7142857142857" style="38" customWidth="1"/>
+    <col min="9" max="9" width="13.1607142857143" style="38" customWidth="1"/>
+    <col min="10" max="10" width="15.7142857142857" style="38" customWidth="1"/>
+    <col min="11" max="11" width="19" style="38" customWidth="1"/>
+    <col min="12" max="12" width="15.7142857142857" style="38" customWidth="1"/>
+    <col min="13" max="16384" width="36.5" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="47">
+      <c r="A1" s="41">
         <f ca="1">TODAY()</f>
-        <v>46032</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="49"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="44" t="s">
+        <v>46067</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="43"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="44" t="s">
+      <c r="K1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="38" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="52">
+      <c r="B2" s="46">
         <v>1.2</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="53">
+      <c r="D2" s="47">
         <f>代码!K1</f>
         <v>0</v>
       </c>
-      <c r="E2" s="53"/>
-      <c r="F2" s="54" t="s">
+      <c r="E2" s="47"/>
+      <c r="F2" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="55">
+      <c r="G2" s="49">
         <f>代码!K2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="55"/>
-      <c r="J2" s="44">
+      <c r="H2" s="49"/>
+      <c r="J2" s="38">
         <f>COUNTIF(G8:G300,"&lt;1.0")</f>
         <v>0</v>
       </c>
-      <c r="K2" s="44">
+      <c r="K2" s="38">
         <f>COUNTIFS(G8:G300,"&gt;=1.0",G8:G300,"&lt;=1.19")</f>
         <v>0</v>
       </c>
-      <c r="L2" s="44">
+      <c r="L2" s="38">
         <f>COUNTIF(G8:G300,"&gt;1.2")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="41" customFormat="1" ht="51.2" spans="1:12">
-      <c r="A3" s="56" t="s">
+    <row r="3" s="35" customFormat="1" ht="51.2" spans="1:12">
+      <c r="A3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="44"/>
-    </row>
-    <row r="4" s="41" customFormat="1" ht="58" spans="1:12">
-      <c r="A4" s="57" t="s">
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="38"/>
+    </row>
+    <row r="4" s="35" customFormat="1" ht="58" spans="1:12">
+      <c r="A4" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="57" t="s">
+      <c r="D4" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="57" t="s">
+      <c r="E4" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="57" t="s">
+      <c r="H4" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44" t="s">
+      <c r="I4" s="38"/>
+      <c r="J4" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="L4" s="46" t="s">
+      <c r="L4" s="40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" s="42" customFormat="1" spans="1:12">
-      <c r="A5" s="60" t="s">
+    <row r="5" s="36" customFormat="1" spans="1:12">
+      <c r="A5" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="53" t="e" cm="1">
+      <c r="B5" s="47" t="e" cm="1">
         <f t="array" ref="B5">_xlfn._xlws.FILTER(代码!$B$2:$H$300,代码!$A$2:$A$300=$A5,"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="61"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="53"/>
-      <c r="J5" s="44" t="s">
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="47"/>
+      <c r="J5" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="62" t="e">
+      <c r="K5" s="56" t="e">
         <f>(B5+D5+F5)/B2+N("（需补数量+确认数量+当日申请）/单袋比")</f>
         <v>#N/A</v>
       </c>
-      <c r="L5" s="46" t="e">
+      <c r="L5" s="40" t="e">
         <f>(B5+D5)/(C5+E5)</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" s="42" customFormat="1" spans="1:12">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-    </row>
-    <row r="7" s="43" customFormat="1" ht="66" customHeight="1" spans="1:12">
-      <c r="A7" s="63" t="str" cm="1">
+    <row r="6" s="36" customFormat="1" spans="1:12">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+    </row>
+    <row r="7" s="37" customFormat="1" ht="66" customHeight="1" spans="1:12">
+      <c r="A7" s="57" t="str" cm="1">
         <f t="array" ref="A7:H7">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(代码!A1:H300,代码!F1:F300&lt;&gt;0),6,-1)</f>
         <v>配送员名字</v>
       </c>
-      <c r="B7" s="63" t="str">
+      <c r="B7" s="57" t="str">
         <v>确认申领商品数量</v>
       </c>
-      <c r="C7" s="63" t="str">
+      <c r="C7" s="57" t="str">
         <v>o2o签收单量</v>
       </c>
-      <c r="D7" s="63" t="str">
+      <c r="D7" s="57" t="str">
         <v>今日
 已申请</v>
       </c>
-      <c r="E7" s="63" t="str">
+      <c r="E7" s="57" t="str">
         <v>今日
 配送单</v>
       </c>
-      <c r="F7" s="64" t="str">
+      <c r="F7" s="58" t="str">
         <v>需要
 申请数量</v>
       </c>
-      <c r="G7" s="65" t="str">
+      <c r="G7" s="59" t="str">
         <v>目前
 单袋比</v>
       </c>
-      <c r="H7" s="63" t="str">
+      <c r="H7" s="57" t="str">
         <v>当前状态</v>
       </c>
-      <c r="I7" s="66"/>
-      <c r="J7" s="67" t="str" cm="1">
+      <c r="I7" s="60"/>
+      <c r="J7" s="61" t="str" cm="1">
         <f t="array" ref="J7:L7">_xlfn._xlws.SORT(_xlfn._xlws.FILTER(代码!O1:Q200,代码!P1:P200&lt;&gt;0),2,-1)</f>
         <v>挂零人员</v>
       </c>
-      <c r="K7" s="43" t="str">
+      <c r="K7" s="37" t="str">
         <v>计费单量</v>
       </c>
-      <c r="L7" s="43" t="str">
+      <c r="L7" s="37" t="str">
         <v>须补数量</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="I8" s="43"/>
+      <c r="I8" s="37"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="I9" s="43"/>
+      <c r="I9" s="37"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="I10" s="43"/>
+      <c r="I10" s="37"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="I11" s="43"/>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="I12" s="43"/>
+      <c r="I12" s="37"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="I13" s="43"/>
+      <c r="I13" s="37"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="I14" s="43"/>
+      <c r="I14" s="37"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="I15" s="43"/>
+      <c r="I15" s="37"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="I16" s="43"/>
+      <c r="I16" s="37"/>
     </row>
     <row r="17" spans="9:9">
-      <c r="I17" s="43"/>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="9:9">
-      <c r="I18" s="43"/>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="9:9">
-      <c r="I19" s="43"/>
+      <c r="I19" s="37"/>
     </row>
     <row r="20" spans="9:9">
-      <c r="I20" s="43"/>
+      <c r="I20" s="37"/>
     </row>
     <row r="21" spans="9:9">
-      <c r="I21" s="43"/>
+      <c r="I21" s="37"/>
     </row>
     <row r="22" spans="9:9">
-      <c r="I22" s="43"/>
+      <c r="I22" s="37"/>
     </row>
     <row r="23" spans="9:9">
-      <c r="I23" s="43"/>
+      <c r="I23" s="37"/>
     </row>
     <row r="24" spans="9:9">
-      <c r="I24" s="43"/>
+      <c r="I24" s="37"/>
     </row>
     <row r="25" spans="9:9">
-      <c r="I25" s="43"/>
+      <c r="I25" s="37"/>
     </row>
     <row r="26" spans="9:9">
-      <c r="I26" s="43"/>
+      <c r="I26" s="37"/>
     </row>
     <row r="27" spans="9:9">
-      <c r="I27" s="43"/>
+      <c r="I27" s="37"/>
     </row>
     <row r="28" spans="9:9">
-      <c r="I28" s="43"/>
+      <c r="I28" s="37"/>
     </row>
     <row r="29" spans="9:9">
-      <c r="I29" s="43"/>
+      <c r="I29" s="37"/>
     </row>
     <row r="30" spans="9:9">
-      <c r="I30" s="43"/>
+      <c r="I30" s="37"/>
     </row>
     <row r="31" spans="9:9">
-      <c r="I31" s="43"/>
+      <c r="I31" s="37"/>
     </row>
     <row r="32" spans="9:9">
-      <c r="I32" s="43"/>
+      <c r="I32" s="37"/>
     </row>
     <row r="33" spans="9:9">
-      <c r="I33" s="43"/>
+      <c r="I33" s="37"/>
     </row>
     <row r="34" spans="9:9">
-      <c r="I34" s="43"/>
+      <c r="I34" s="37"/>
     </row>
     <row r="35" spans="9:9">
-      <c r="I35" s="43"/>
+      <c r="I35" s="37"/>
     </row>
     <row r="36" spans="9:9">
-      <c r="I36" s="43"/>
+      <c r="I36" s="37"/>
     </row>
     <row r="37" spans="9:9">
-      <c r="I37" s="43"/>
+      <c r="I37" s="37"/>
     </row>
     <row r="38" spans="9:9">
-      <c r="I38" s="43"/>
+      <c r="I38" s="37"/>
     </row>
     <row r="39" spans="9:9">
-      <c r="I39" s="43"/>
+      <c r="I39" s="37"/>
     </row>
     <row r="40" spans="9:9">
-      <c r="I40" s="43"/>
+      <c r="I40" s="37"/>
     </row>
     <row r="41" spans="9:9">
-      <c r="I41" s="43"/>
+      <c r="I41" s="37"/>
     </row>
     <row r="42" spans="9:9">
-      <c r="I42" s="43"/>
+      <c r="I42" s="37"/>
     </row>
     <row r="43" spans="9:9">
-      <c r="I43" s="43"/>
+      <c r="I43" s="37"/>
     </row>
     <row r="44" spans="9:9">
-      <c r="I44" s="43"/>
+      <c r="I44" s="37"/>
     </row>
     <row r="45" spans="9:9">
-      <c r="I45" s="43"/>
+      <c r="I45" s="37"/>
     </row>
     <row r="46" spans="9:9">
-      <c r="I46" s="43"/>
+      <c r="I46" s="37"/>
     </row>
     <row r="47" spans="9:9">
-      <c r="I47" s="43"/>
+      <c r="I47" s="37"/>
     </row>
     <row r="48" spans="9:9">
-      <c r="I48" s="43"/>
+      <c r="I48" s="37"/>
     </row>
     <row r="49" spans="9:9">
-      <c r="I49" s="43"/>
+      <c r="I49" s="37"/>
     </row>
     <row r="50" spans="9:9">
-      <c r="I50" s="43"/>
+      <c r="I50" s="37"/>
     </row>
     <row r="51" spans="9:9">
-      <c r="I51" s="43"/>
+      <c r="I51" s="37"/>
     </row>
     <row r="52" spans="9:9">
-      <c r="I52" s="43"/>
+      <c r="I52" s="37"/>
     </row>
     <row r="53" spans="9:9">
-      <c r="I53" s="43"/>
+      <c r="I53" s="37"/>
     </row>
     <row r="54" spans="9:9">
-      <c r="I54" s="43"/>
+      <c r="I54" s="37"/>
     </row>
     <row r="55" spans="9:9">
-      <c r="I55" s="43"/>
+      <c r="I55" s="37"/>
     </row>
     <row r="56" spans="9:9">
-      <c r="I56" s="43"/>
+      <c r="I56" s="37"/>
     </row>
     <row r="57" spans="9:9">
-      <c r="I57" s="43"/>
+      <c r="I57" s="37"/>
     </row>
     <row r="58" spans="9:9">
-      <c r="I58" s="43"/>
+      <c r="I58" s="37"/>
     </row>
     <row r="59" spans="9:9">
-      <c r="I59" s="43"/>
+      <c r="I59" s="37"/>
     </row>
     <row r="60" spans="9:9">
-      <c r="I60" s="43"/>
+      <c r="I60" s="37"/>
     </row>
     <row r="61" spans="9:9">
-      <c r="I61" s="43"/>
+      <c r="I61" s="37"/>
     </row>
     <row r="62" spans="9:9">
-      <c r="I62" s="43"/>
+      <c r="I62" s="37"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1"/>
@@ -2357,45 +2338,45 @@
   <dimension ref="A1:AZ1"/>
   <sheetFormatPr defaultColWidth="8.35714285714286" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="2" width="9.57142857142857" style="40" customWidth="1"/>
-    <col min="3" max="3" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="4" max="4" width="16.2142857142857" style="40" customWidth="1"/>
-    <col min="5" max="5" width="22.9285714285714" style="40" customWidth="1"/>
-    <col min="6" max="7" width="36.3571428571429" style="40" customWidth="1"/>
-    <col min="8" max="8" width="33.2857142857143" style="40" customWidth="1"/>
-    <col min="9" max="9" width="20.0714285714286" style="40" customWidth="1"/>
-    <col min="10" max="10" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="11" max="12" width="14" style="40" customWidth="1"/>
-    <col min="13" max="13" width="22.7857142857143" style="40" customWidth="1"/>
-    <col min="14" max="14" width="16.2142857142857" style="40" customWidth="1"/>
-    <col min="15" max="15" width="22.7857142857143" style="40" customWidth="1"/>
-    <col min="16" max="16" width="9.57142857142857" style="40" customWidth="1"/>
-    <col min="17" max="17" width="14" style="40" customWidth="1"/>
-    <col min="18" max="18" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="19" max="20" width="9.57142857142857" style="40" customWidth="1"/>
-    <col min="21" max="21" width="16.2142857142857" style="40" customWidth="1"/>
-    <col min="22" max="22" width="18.4285714285714" style="40" customWidth="1"/>
-    <col min="23" max="23" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="24" max="24" width="9.57142857142857" style="40" customWidth="1"/>
-    <col min="25" max="28" width="16.2142857142857" style="40" customWidth="1"/>
-    <col min="29" max="30" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="31" max="33" width="12.7857142857143" style="40" customWidth="1"/>
-    <col min="34" max="35" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="36" max="37" width="12.7857142857143" style="40" customWidth="1"/>
-    <col min="38" max="38" width="16.2142857142857" style="40" customWidth="1"/>
-    <col min="39" max="39" width="18.4285714285714" style="40" customWidth="1"/>
-    <col min="40" max="40" width="16.7142857142857" style="40" customWidth="1"/>
-    <col min="41" max="41" width="18.9285714285714" style="40" customWidth="1"/>
-    <col min="42" max="42" width="9.57142857142857" style="40" customWidth="1"/>
-    <col min="43" max="43" width="11.7142857142857" style="40" customWidth="1"/>
-    <col min="44" max="44" width="12.7142857142857" style="40" customWidth="1"/>
-    <col min="45" max="47" width="12.6428571428571" style="40" customWidth="1"/>
-    <col min="48" max="48" width="18.4285714285714" style="40" customWidth="1"/>
-    <col min="49" max="49" width="16.2142857142857" style="40" customWidth="1"/>
-    <col min="50" max="50" width="17.1428571428571" style="40" customWidth="1"/>
-    <col min="51" max="51" width="17.0714285714286" style="40" customWidth="1"/>
-    <col min="52" max="52" width="9.57142857142857" style="40" customWidth="1"/>
-    <col min="53" max="16384" width="8.35714285714286" style="40"/>
+    <col min="1" max="2" width="9.57142857142857" style="34" customWidth="1"/>
+    <col min="3" max="3" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="4" max="4" width="16.2142857142857" style="34" customWidth="1"/>
+    <col min="5" max="5" width="22.9285714285714" style="34" customWidth="1"/>
+    <col min="6" max="7" width="36.3571428571429" style="34" customWidth="1"/>
+    <col min="8" max="8" width="33.2857142857143" style="34" customWidth="1"/>
+    <col min="9" max="9" width="20.0714285714286" style="34" customWidth="1"/>
+    <col min="10" max="10" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="11" max="12" width="14" style="34" customWidth="1"/>
+    <col min="13" max="13" width="22.7857142857143" style="34" customWidth="1"/>
+    <col min="14" max="14" width="16.2142857142857" style="34" customWidth="1"/>
+    <col min="15" max="15" width="22.7857142857143" style="34" customWidth="1"/>
+    <col min="16" max="16" width="9.57142857142857" style="34" customWidth="1"/>
+    <col min="17" max="17" width="14" style="34" customWidth="1"/>
+    <col min="18" max="18" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="19" max="20" width="9.57142857142857" style="34" customWidth="1"/>
+    <col min="21" max="21" width="16.2142857142857" style="34" customWidth="1"/>
+    <col min="22" max="22" width="18.4285714285714" style="34" customWidth="1"/>
+    <col min="23" max="23" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="24" max="24" width="9.57142857142857" style="34" customWidth="1"/>
+    <col min="25" max="28" width="16.2142857142857" style="34" customWidth="1"/>
+    <col min="29" max="30" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="31" max="33" width="12.7857142857143" style="34" customWidth="1"/>
+    <col min="34" max="35" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="36" max="37" width="12.7857142857143" style="34" customWidth="1"/>
+    <col min="38" max="38" width="16.2142857142857" style="34" customWidth="1"/>
+    <col min="39" max="39" width="18.4285714285714" style="34" customWidth="1"/>
+    <col min="40" max="40" width="16.7142857142857" style="34" customWidth="1"/>
+    <col min="41" max="41" width="18.9285714285714" style="34" customWidth="1"/>
+    <col min="42" max="42" width="9.57142857142857" style="34" customWidth="1"/>
+    <col min="43" max="43" width="11.7142857142857" style="34" customWidth="1"/>
+    <col min="44" max="44" width="12.7142857142857" style="34" customWidth="1"/>
+    <col min="45" max="47" width="12.6428571428571" style="34" customWidth="1"/>
+    <col min="48" max="48" width="18.4285714285714" style="34" customWidth="1"/>
+    <col min="49" max="49" width="16.2142857142857" style="34" customWidth="1"/>
+    <col min="50" max="50" width="17.1428571428571" style="34" customWidth="1"/>
+    <col min="51" max="51" width="17.0714285714286" style="34" customWidth="1"/>
+    <col min="52" max="52" width="9.57142857142857" style="34" customWidth="1"/>
+    <col min="53" max="16384" width="8.35714285714286" style="34"/>
   </cols>
   <sheetData/>
   <sortState ref="A3:AZ66">
@@ -2420,87 +2401,87 @@
   <dimension ref="A1048515:A1048576"/>
   <sheetFormatPr defaultColWidth="8.33035714285714" defaultRowHeight="16.8"/>
   <cols>
-    <col min="1" max="2" width="9.5" style="40" customWidth="1"/>
-    <col min="3" max="3" width="18.8303571428571" style="40" customWidth="1"/>
-    <col min="4" max="4" width="9.33035714285714" style="40" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="40" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="40" customWidth="1"/>
-    <col min="7" max="7" width="11.8303571428571" style="40" customWidth="1"/>
-    <col min="8" max="8" width="7.16071428571429" style="40" customWidth="1"/>
-    <col min="9" max="9" width="16.3303571428571" style="40" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="40" customWidth="1"/>
-    <col min="11" max="11" width="23" style="40" customWidth="1"/>
-    <col min="12" max="12" width="9.5" style="40" customWidth="1"/>
-    <col min="13" max="13" width="8" style="40" customWidth="1"/>
-    <col min="14" max="14" width="9.5" style="40" customWidth="1"/>
-    <col min="15" max="15" width="18.5" style="40" customWidth="1"/>
-    <col min="16" max="16" width="12.8303571428571" style="40" customWidth="1"/>
-    <col min="17" max="17" width="12" style="40" customWidth="1"/>
-    <col min="18" max="16384" width="8.33035714285714" style="40"/>
+    <col min="1" max="2" width="9.5" style="34" customWidth="1"/>
+    <col min="3" max="3" width="18.8303571428571" style="34" customWidth="1"/>
+    <col min="4" max="4" width="9.33035714285714" style="34" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="34" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="34" customWidth="1"/>
+    <col min="7" max="7" width="11.8303571428571" style="34" customWidth="1"/>
+    <col min="8" max="8" width="7.16071428571429" style="34" customWidth="1"/>
+    <col min="9" max="9" width="16.3303571428571" style="34" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="34" customWidth="1"/>
+    <col min="11" max="11" width="23" style="34" customWidth="1"/>
+    <col min="12" max="12" width="9.5" style="34" customWidth="1"/>
+    <col min="13" max="13" width="8" style="34" customWidth="1"/>
+    <col min="14" max="14" width="9.5" style="34" customWidth="1"/>
+    <col min="15" max="15" width="18.5" style="34" customWidth="1"/>
+    <col min="16" max="16" width="12.8303571428571" style="34" customWidth="1"/>
+    <col min="17" max="17" width="12" style="34" customWidth="1"/>
+    <col min="18" max="16384" width="8.33035714285714" style="34"/>
   </cols>
   <sheetData>
-    <row r="1048515" s="39" customFormat="1"/>
-    <row r="1048516" s="39" customFormat="1"/>
-    <row r="1048517" s="39" customFormat="1"/>
-    <row r="1048518" s="39" customFormat="1"/>
-    <row r="1048519" s="39" customFormat="1"/>
-    <row r="1048520" s="39" customFormat="1"/>
-    <row r="1048521" s="39" customFormat="1"/>
-    <row r="1048522" s="39" customFormat="1"/>
-    <row r="1048523" s="39" customFormat="1"/>
-    <row r="1048524" s="39" customFormat="1"/>
-    <row r="1048525" s="39" customFormat="1"/>
-    <row r="1048526" s="39" customFormat="1"/>
-    <row r="1048527" s="39" customFormat="1"/>
-    <row r="1048528" s="39" customFormat="1"/>
-    <row r="1048529" s="39" customFormat="1"/>
-    <row r="1048530" s="39" customFormat="1"/>
-    <row r="1048531" s="39" customFormat="1"/>
-    <row r="1048532" s="39" customFormat="1"/>
-    <row r="1048533" s="39" customFormat="1"/>
-    <row r="1048534" s="39" customFormat="1"/>
-    <row r="1048535" s="39" customFormat="1"/>
-    <row r="1048536" s="39" customFormat="1"/>
-    <row r="1048537" s="39" customFormat="1"/>
-    <row r="1048538" s="39" customFormat="1"/>
-    <row r="1048539" s="39" customFormat="1"/>
-    <row r="1048540" s="39" customFormat="1"/>
-    <row r="1048541" s="39" customFormat="1"/>
-    <row r="1048542" s="39" customFormat="1"/>
-    <row r="1048543" s="39" customFormat="1"/>
-    <row r="1048544" s="39" customFormat="1"/>
-    <row r="1048545" s="39" customFormat="1"/>
-    <row r="1048546" s="39" customFormat="1"/>
-    <row r="1048547" s="39" customFormat="1"/>
-    <row r="1048548" s="39" customFormat="1"/>
-    <row r="1048549" s="39" customFormat="1"/>
-    <row r="1048550" s="39" customFormat="1"/>
-    <row r="1048551" s="39" customFormat="1"/>
-    <row r="1048552" s="39" customFormat="1"/>
-    <row r="1048553" s="39" customFormat="1"/>
-    <row r="1048554" s="39" customFormat="1"/>
-    <row r="1048555" s="39" customFormat="1"/>
-    <row r="1048556" s="39" customFormat="1"/>
-    <row r="1048557" s="39" customFormat="1"/>
-    <row r="1048558" s="39" customFormat="1"/>
-    <row r="1048559" s="39" customFormat="1"/>
-    <row r="1048560" s="39" customFormat="1"/>
-    <row r="1048561" s="39" customFormat="1"/>
-    <row r="1048562" s="39" customFormat="1"/>
-    <row r="1048563" s="39" customFormat="1"/>
-    <row r="1048564" s="39" customFormat="1"/>
-    <row r="1048565" s="39" customFormat="1"/>
-    <row r="1048566" s="39" customFormat="1"/>
-    <row r="1048567" s="39" customFormat="1"/>
-    <row r="1048568" s="39" customFormat="1"/>
-    <row r="1048569" s="39" customFormat="1"/>
-    <row r="1048570" s="39" customFormat="1"/>
-    <row r="1048571" s="39" customFormat="1"/>
-    <row r="1048572" s="39" customFormat="1"/>
-    <row r="1048573" s="39" customFormat="1"/>
-    <row r="1048574" s="39" customFormat="1"/>
-    <row r="1048575" s="39" customFormat="1"/>
-    <row r="1048576" s="39" customFormat="1"/>
+    <row r="1048515" s="25" customFormat="1"/>
+    <row r="1048516" s="25" customFormat="1"/>
+    <row r="1048517" s="25" customFormat="1"/>
+    <row r="1048518" s="25" customFormat="1"/>
+    <row r="1048519" s="25" customFormat="1"/>
+    <row r="1048520" s="25" customFormat="1"/>
+    <row r="1048521" s="25" customFormat="1"/>
+    <row r="1048522" s="25" customFormat="1"/>
+    <row r="1048523" s="25" customFormat="1"/>
+    <row r="1048524" s="25" customFormat="1"/>
+    <row r="1048525" s="25" customFormat="1"/>
+    <row r="1048526" s="25" customFormat="1"/>
+    <row r="1048527" s="25" customFormat="1"/>
+    <row r="1048528" s="25" customFormat="1"/>
+    <row r="1048529" s="25" customFormat="1"/>
+    <row r="1048530" s="25" customFormat="1"/>
+    <row r="1048531" s="25" customFormat="1"/>
+    <row r="1048532" s="25" customFormat="1"/>
+    <row r="1048533" s="25" customFormat="1"/>
+    <row r="1048534" s="25" customFormat="1"/>
+    <row r="1048535" s="25" customFormat="1"/>
+    <row r="1048536" s="25" customFormat="1"/>
+    <row r="1048537" s="25" customFormat="1"/>
+    <row r="1048538" s="25" customFormat="1"/>
+    <row r="1048539" s="25" customFormat="1"/>
+    <row r="1048540" s="25" customFormat="1"/>
+    <row r="1048541" s="25" customFormat="1"/>
+    <row r="1048542" s="25" customFormat="1"/>
+    <row r="1048543" s="25" customFormat="1"/>
+    <row r="1048544" s="25" customFormat="1"/>
+    <row r="1048545" s="25" customFormat="1"/>
+    <row r="1048546" s="25" customFormat="1"/>
+    <row r="1048547" s="25" customFormat="1"/>
+    <row r="1048548" s="25" customFormat="1"/>
+    <row r="1048549" s="25" customFormat="1"/>
+    <row r="1048550" s="25" customFormat="1"/>
+    <row r="1048551" s="25" customFormat="1"/>
+    <row r="1048552" s="25" customFormat="1"/>
+    <row r="1048553" s="25" customFormat="1"/>
+    <row r="1048554" s="25" customFormat="1"/>
+    <row r="1048555" s="25" customFormat="1"/>
+    <row r="1048556" s="25" customFormat="1"/>
+    <row r="1048557" s="25" customFormat="1"/>
+    <row r="1048558" s="25" customFormat="1"/>
+    <row r="1048559" s="25" customFormat="1"/>
+    <row r="1048560" s="25" customFormat="1"/>
+    <row r="1048561" s="25" customFormat="1"/>
+    <row r="1048562" s="25" customFormat="1"/>
+    <row r="1048563" s="25" customFormat="1"/>
+    <row r="1048564" s="25" customFormat="1"/>
+    <row r="1048565" s="25" customFormat="1"/>
+    <row r="1048566" s="25" customFormat="1"/>
+    <row r="1048567" s="25" customFormat="1"/>
+    <row r="1048568" s="25" customFormat="1"/>
+    <row r="1048569" s="25" customFormat="1"/>
+    <row r="1048570" s="25" customFormat="1"/>
+    <row r="1048571" s="25" customFormat="1"/>
+    <row r="1048572" s="25" customFormat="1"/>
+    <row r="1048573" s="25" customFormat="1"/>
+    <row r="1048574" s="25" customFormat="1"/>
+    <row r="1048575" s="25" customFormat="1"/>
+    <row r="1048576" s="25" customFormat="1"/>
   </sheetData>
   <sortState ref="A2:Q79">
     <sortCondition ref="P77" descending="1"/>
@@ -2519,1917 +2500,1917 @@
   <dimension ref="A1:K146"/>
   <sheetFormatPr defaultColWidth="110.714285714286" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="40.8928571428571" style="36" customWidth="1"/>
-    <col min="2" max="2" width="19.2142857142857" style="36" customWidth="1"/>
-    <col min="3" max="3" width="17.5" style="36" customWidth="1"/>
-    <col min="4" max="4" width="11.6071428571429" style="36" customWidth="1"/>
-    <col min="5" max="5" width="13.75" style="36" customWidth="1"/>
-    <col min="6" max="6" width="36.9642857142857" style="36" customWidth="1"/>
-    <col min="7" max="7" width="15.0714285714286" style="36" customWidth="1"/>
-    <col min="8" max="8" width="7.32142857142857" style="36" customWidth="1"/>
-    <col min="9" max="9" width="9.46428571428571" style="36" customWidth="1"/>
-    <col min="10" max="10" width="19.2142857142857" style="36" customWidth="1"/>
-    <col min="11" max="11" width="7.32142857142857" style="36" customWidth="1"/>
-    <col min="12" max="16384" width="110.714285714286" style="36" customWidth="1"/>
+    <col min="1" max="1" width="40.8928571428571" style="33" customWidth="1"/>
+    <col min="2" max="2" width="19.2142857142857" style="33" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="33" customWidth="1"/>
+    <col min="4" max="4" width="11.6071428571429" style="33" customWidth="1"/>
+    <col min="5" max="5" width="13.75" style="33" customWidth="1"/>
+    <col min="6" max="6" width="36.9642857142857" style="33" customWidth="1"/>
+    <col min="7" max="7" width="15.0714285714286" style="33" customWidth="1"/>
+    <col min="8" max="8" width="7.32142857142857" style="33" customWidth="1"/>
+    <col min="9" max="9" width="9.46428571428571" style="33" customWidth="1"/>
+    <col min="10" max="10" width="19.2142857142857" style="33" customWidth="1"/>
+    <col min="11" max="11" width="7.32142857142857" style="33" customWidth="1"/>
+    <col min="12" max="16384" width="110.714285714286" style="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="27"/>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="28"/>
-      <c r="B2" s="37"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="28"/>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="32"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="32"/>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="32"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="38"/>
-      <c r="K4" s="32"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="32"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="32"/>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="32"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="38"/>
-      <c r="K6" s="32"/>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="32"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="32"/>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="32"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="32"/>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="32"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="32"/>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="32"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="32"/>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="32"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="38"/>
-      <c r="K11" s="32"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="32"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="38"/>
-      <c r="K12" s="32"/>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="32"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="32"/>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="32"/>
-      <c r="B14" s="38"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="38"/>
-      <c r="K14" s="32"/>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="32"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="38"/>
-      <c r="K15" s="32"/>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="32"/>
-      <c r="B16" s="38"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="32"/>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="32"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="32"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="32"/>
-      <c r="B18" s="38"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="32"/>
-      <c r="B19" s="38"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="32"/>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="32"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="32"/>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="32"/>
-      <c r="B21" s="38"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="32"/>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="32"/>
-      <c r="B22" s="38"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="32"/>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="32"/>
-      <c r="B23" s="38"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="32"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="32"/>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="32"/>
-      <c r="B24" s="38"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="32"/>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="32"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="32"/>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="32"/>
-      <c r="B26" s="38"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="32"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="32"/>
-      <c r="B27" s="38"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="32"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="32"/>
-      <c r="B28" s="38"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="32"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="32"/>
-      <c r="B29" s="38"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="32"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="32"/>
-      <c r="B30" s="38"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="32"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="32"/>
-      <c r="B31" s="38"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="32"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="32"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="32"/>
-      <c r="B32" s="38"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="32"/>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" s="32"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="38"/>
-      <c r="K33" s="32"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="32"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="32"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="32"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="32"/>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="32"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="32"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="32"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="32"/>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="32"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="32"/>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="32"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="32"/>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="32"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="32"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="32"/>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="32"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="32"/>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="32"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="38"/>
-      <c r="K42" s="32"/>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="32"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="32"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="32"/>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="32"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="32"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="32"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="32"/>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="32"/>
-      <c r="B45" s="38"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="32"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="32"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="32"/>
-      <c r="B46" s="38"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="32"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="32"/>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="32"/>
-      <c r="B47" s="38"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="32"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="32"/>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="32"/>
-      <c r="B48" s="38"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="32"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="32"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="32"/>
-      <c r="B49" s="38"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="32"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="32"/>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="32"/>
-      <c r="B50" s="38"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="32"/>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="32"/>
-      <c r="B51" s="38"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="38"/>
-      <c r="K51" s="32"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="32"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="38"/>
-      <c r="K52" s="32"/>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="32"/>
-      <c r="B53" s="38"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="32"/>
-      <c r="J53" s="38"/>
-      <c r="K53" s="32"/>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="32"/>
-      <c r="B54" s="38"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="32"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="32"/>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="32"/>
-      <c r="B55" s="38"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="32"/>
-      <c r="J55" s="38"/>
-      <c r="K55" s="32"/>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="32"/>
-      <c r="B56" s="38"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="32"/>
-      <c r="J56" s="38"/>
-      <c r="K56" s="32"/>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" s="32"/>
-      <c r="B57" s="38"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="38"/>
-      <c r="K57" s="32"/>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" s="32"/>
-      <c r="B58" s="38"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="32"/>
-      <c r="J58" s="38"/>
-      <c r="K58" s="32"/>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" s="32"/>
-      <c r="B59" s="38"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="32"/>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" s="32"/>
-      <c r="B60" s="38"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="32"/>
-      <c r="J60" s="38"/>
-      <c r="K60" s="32"/>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" s="32"/>
-      <c r="B61" s="38"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="32"/>
-      <c r="J61" s="38"/>
-      <c r="K61" s="32"/>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="A62" s="32"/>
-      <c r="B62" s="38"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="32"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="32"/>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="A63" s="32"/>
-      <c r="B63" s="38"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="32"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="32"/>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" s="32"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="32"/>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" s="32"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="32"/>
-      <c r="J65" s="38"/>
-      <c r="K65" s="32"/>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="A66" s="32"/>
-      <c r="B66" s="38"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="32"/>
-      <c r="J66" s="38"/>
-      <c r="K66" s="32"/>
-    </row>
-    <row r="67" spans="1:11">
-      <c r="A67" s="32"/>
-      <c r="B67" s="38"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="32"/>
-      <c r="J67" s="38"/>
-      <c r="K67" s="32"/>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="A68" s="32"/>
-      <c r="B68" s="38"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="32"/>
-      <c r="J68" s="38"/>
-      <c r="K68" s="32"/>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="A69" s="32"/>
-      <c r="B69" s="38"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="32"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="32"/>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="A70" s="32"/>
-      <c r="B70" s="38"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="32"/>
-      <c r="J70" s="38"/>
-      <c r="K70" s="32"/>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="A71" s="32"/>
-      <c r="B71" s="38"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="32"/>
-      <c r="J71" s="38"/>
-      <c r="K71" s="32"/>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="A72" s="32"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="38"/>
-      <c r="K72" s="32"/>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" s="32"/>
-      <c r="B73" s="38"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="32"/>
-      <c r="J73" s="38"/>
-      <c r="K73" s="32"/>
-    </row>
-    <row r="74" spans="1:11">
-      <c r="A74" s="32"/>
-      <c r="B74" s="38"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="32"/>
-      <c r="J74" s="38"/>
-      <c r="K74" s="32"/>
-    </row>
-    <row r="75" spans="1:11">
-      <c r="A75" s="32"/>
-      <c r="B75" s="38"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="32"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="32"/>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" s="32"/>
-      <c r="B76" s="38"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="32"/>
-      <c r="J76" s="38"/>
-      <c r="K76" s="32"/>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77" s="32"/>
-      <c r="B77" s="38"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="32"/>
-      <c r="J77" s="38"/>
-      <c r="K77" s="32"/>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" s="32"/>
-      <c r="B78" s="38"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="32"/>
-      <c r="J78" s="38"/>
-      <c r="K78" s="32"/>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" s="32"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="38"/>
-      <c r="K79" s="32"/>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="32"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="32"/>
-      <c r="J80" s="38"/>
-      <c r="K80" s="32"/>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="A81" s="32"/>
-      <c r="B81" s="38"/>
-      <c r="C81" s="32"/>
-      <c r="D81" s="32"/>
-      <c r="E81" s="32"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="32"/>
-      <c r="H81" s="32"/>
-      <c r="I81" s="32"/>
-      <c r="J81" s="38"/>
-      <c r="K81" s="32"/>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="32"/>
-      <c r="B82" s="38"/>
-      <c r="C82" s="32"/>
-      <c r="D82" s="32"/>
-      <c r="E82" s="32"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="32"/>
-      <c r="H82" s="32"/>
-      <c r="I82" s="32"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="32"/>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="32"/>
-      <c r="B83" s="38"/>
-      <c r="C83" s="32"/>
-      <c r="D83" s="32"/>
-      <c r="E83" s="32"/>
-      <c r="F83" s="32"/>
-      <c r="G83" s="32"/>
-      <c r="H83" s="32"/>
-      <c r="I83" s="32"/>
-      <c r="J83" s="38"/>
-      <c r="K83" s="32"/>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="32"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="32"/>
-      <c r="D84" s="32"/>
-      <c r="E84" s="32"/>
-      <c r="F84" s="32"/>
-      <c r="G84" s="32"/>
-      <c r="H84" s="32"/>
-      <c r="I84" s="32"/>
-      <c r="J84" s="38"/>
-      <c r="K84" s="32"/>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="32"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="32"/>
-      <c r="D85" s="32"/>
-      <c r="E85" s="32"/>
-      <c r="F85" s="32"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
-      <c r="J85" s="38"/>
-      <c r="K85" s="32"/>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="32"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="32"/>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="38"/>
-      <c r="K86" s="32"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="32"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="32"/>
-      <c r="D87" s="32"/>
-      <c r="E87" s="32"/>
-      <c r="F87" s="32"/>
-      <c r="G87" s="32"/>
-      <c r="H87" s="32"/>
-      <c r="I87" s="32"/>
-      <c r="J87" s="38"/>
-      <c r="K87" s="32"/>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="32"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="32"/>
-      <c r="D88" s="32"/>
-      <c r="E88" s="32"/>
-      <c r="F88" s="32"/>
-      <c r="G88" s="32"/>
-      <c r="H88" s="32"/>
-      <c r="I88" s="32"/>
-      <c r="J88" s="38"/>
-      <c r="K88" s="32"/>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="32"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="32"/>
-      <c r="D89" s="32"/>
-      <c r="E89" s="32"/>
-      <c r="F89" s="32"/>
-      <c r="G89" s="32"/>
-      <c r="H89" s="32"/>
-      <c r="I89" s="32"/>
-      <c r="J89" s="38"/>
-      <c r="K89" s="32"/>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="32"/>
-      <c r="B90" s="38"/>
-      <c r="C90" s="32"/>
-      <c r="D90" s="32"/>
-      <c r="E90" s="32"/>
-      <c r="F90" s="32"/>
-      <c r="G90" s="32"/>
-      <c r="H90" s="32"/>
-      <c r="I90" s="32"/>
-      <c r="J90" s="38"/>
-      <c r="K90" s="32"/>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="32"/>
-      <c r="B91" s="38"/>
-      <c r="C91" s="32"/>
-      <c r="D91" s="32"/>
-      <c r="E91" s="32"/>
-      <c r="F91" s="32"/>
-      <c r="G91" s="32"/>
-      <c r="H91" s="32"/>
-      <c r="I91" s="32"/>
-      <c r="J91" s="38"/>
-      <c r="K91" s="32"/>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="32"/>
-      <c r="B92" s="38"/>
-      <c r="C92" s="32"/>
-      <c r="D92" s="32"/>
-      <c r="E92" s="32"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="32"/>
-      <c r="I92" s="32"/>
-      <c r="J92" s="38"/>
-      <c r="K92" s="32"/>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="32"/>
-      <c r="B93" s="38"/>
-      <c r="C93" s="32"/>
-      <c r="D93" s="32"/>
-      <c r="E93" s="32"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="32"/>
-      <c r="H93" s="32"/>
-      <c r="I93" s="32"/>
-      <c r="J93" s="38"/>
-      <c r="K93" s="32"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="32"/>
-      <c r="B94" s="38"/>
-      <c r="C94" s="32"/>
-      <c r="D94" s="32"/>
-      <c r="E94" s="32"/>
-      <c r="F94" s="32"/>
-      <c r="G94" s="32"/>
-      <c r="H94" s="32"/>
-      <c r="I94" s="32"/>
-      <c r="J94" s="38"/>
-      <c r="K94" s="32"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="32"/>
-      <c r="B95" s="38"/>
-      <c r="C95" s="32"/>
-      <c r="D95" s="32"/>
-      <c r="E95" s="32"/>
-      <c r="F95" s="32"/>
-      <c r="G95" s="32"/>
-      <c r="H95" s="32"/>
-      <c r="I95" s="32"/>
-      <c r="J95" s="38"/>
-      <c r="K95" s="32"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="32"/>
-      <c r="B96" s="38"/>
-      <c r="C96" s="32"/>
-      <c r="D96" s="32"/>
-      <c r="E96" s="32"/>
-      <c r="F96" s="32"/>
-      <c r="G96" s="32"/>
-      <c r="H96" s="32"/>
-      <c r="I96" s="32"/>
-      <c r="J96" s="38"/>
-      <c r="K96" s="32"/>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" s="32"/>
-      <c r="B97" s="38"/>
-      <c r="C97" s="32"/>
-      <c r="D97" s="32"/>
-      <c r="E97" s="32"/>
-      <c r="F97" s="32"/>
-      <c r="G97" s="32"/>
-      <c r="H97" s="32"/>
-      <c r="I97" s="32"/>
-      <c r="J97" s="38"/>
-      <c r="K97" s="32"/>
-    </row>
-    <row r="98" spans="1:11">
-      <c r="A98" s="32"/>
-      <c r="B98" s="38"/>
-      <c r="C98" s="32"/>
-      <c r="D98" s="32"/>
-      <c r="E98" s="32"/>
-      <c r="F98" s="32"/>
-      <c r="G98" s="32"/>
-      <c r="H98" s="32"/>
-      <c r="I98" s="32"/>
-      <c r="J98" s="38"/>
-      <c r="K98" s="32"/>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" s="32"/>
-      <c r="B99" s="38"/>
-      <c r="C99" s="32"/>
-      <c r="D99" s="32"/>
-      <c r="E99" s="32"/>
-      <c r="F99" s="32"/>
-      <c r="G99" s="32"/>
-      <c r="H99" s="32"/>
-      <c r="I99" s="32"/>
-      <c r="J99" s="38"/>
-      <c r="K99" s="32"/>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" s="32"/>
-      <c r="B100" s="38"/>
-      <c r="C100" s="32"/>
-      <c r="D100" s="32"/>
-      <c r="E100" s="32"/>
-      <c r="F100" s="32"/>
-      <c r="G100" s="32"/>
-      <c r="H100" s="32"/>
-      <c r="I100" s="32"/>
-      <c r="J100" s="38"/>
-      <c r="K100" s="32"/>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" s="32"/>
-      <c r="B101" s="38"/>
-      <c r="C101" s="32"/>
-      <c r="D101" s="32"/>
-      <c r="E101" s="32"/>
-      <c r="F101" s="32"/>
-      <c r="G101" s="32"/>
-      <c r="H101" s="32"/>
-      <c r="I101" s="32"/>
-      <c r="J101" s="38"/>
-      <c r="K101" s="32"/>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" s="27"/>
-      <c r="B102" s="27"/>
-      <c r="C102" s="27"/>
-      <c r="D102" s="27"/>
-      <c r="E102" s="27"/>
-      <c r="F102" s="27"/>
-      <c r="G102" s="27"/>
-      <c r="H102" s="27"/>
-      <c r="I102" s="27"/>
-      <c r="J102" s="27"/>
-      <c r="K102" s="27"/>
-    </row>
-    <row r="103" spans="1:11">
-      <c r="A103" s="27"/>
-      <c r="B103" s="27"/>
-      <c r="C103" s="27"/>
-      <c r="D103" s="27"/>
-      <c r="E103" s="27"/>
-      <c r="F103" s="27"/>
-      <c r="G103" s="27"/>
-      <c r="H103" s="27"/>
-      <c r="I103" s="27"/>
-      <c r="J103" s="27"/>
-      <c r="K103" s="27"/>
-    </row>
-    <row r="104" spans="1:11">
-      <c r="A104" s="28"/>
-      <c r="B104" s="37"/>
-      <c r="C104" s="28"/>
-      <c r="D104" s="28"/>
-      <c r="E104" s="28"/>
-      <c r="F104" s="28"/>
-      <c r="G104" s="28"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="28"/>
-      <c r="J104" s="37"/>
-      <c r="K104" s="28"/>
-    </row>
-    <row r="105" spans="1:11">
-      <c r="A105" s="32"/>
-      <c r="B105" s="38"/>
-      <c r="C105" s="32"/>
-      <c r="D105" s="32"/>
-      <c r="E105" s="32"/>
-      <c r="F105" s="32"/>
-      <c r="G105" s="32"/>
-      <c r="H105" s="32"/>
-      <c r="I105" s="32"/>
-      <c r="J105" s="38"/>
-      <c r="K105" s="32"/>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" s="32"/>
-      <c r="B106" s="38"/>
-      <c r="C106" s="32"/>
-      <c r="D106" s="32"/>
-      <c r="E106" s="32"/>
-      <c r="F106" s="32"/>
-      <c r="G106" s="32"/>
-      <c r="H106" s="32"/>
-      <c r="I106" s="32"/>
-      <c r="J106" s="38"/>
-      <c r="K106" s="32"/>
-    </row>
-    <row r="107" spans="1:11">
-      <c r="A107" s="32"/>
-      <c r="B107" s="38"/>
-      <c r="C107" s="32"/>
-      <c r="D107" s="32"/>
-      <c r="E107" s="32"/>
-      <c r="F107" s="32"/>
-      <c r="G107" s="32"/>
-      <c r="H107" s="32"/>
-      <c r="I107" s="32"/>
-      <c r="J107" s="38"/>
-      <c r="K107" s="32"/>
-    </row>
-    <row r="108" spans="1:11">
-      <c r="A108" s="32"/>
-      <c r="B108" s="38"/>
-      <c r="C108" s="32"/>
-      <c r="D108" s="32"/>
-      <c r="E108" s="32"/>
-      <c r="F108" s="32"/>
-      <c r="G108" s="32"/>
-      <c r="H108" s="32"/>
-      <c r="I108" s="32"/>
-      <c r="J108" s="38"/>
-      <c r="K108" s="32"/>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="A109" s="32"/>
-      <c r="B109" s="38"/>
-      <c r="C109" s="32"/>
-      <c r="D109" s="32"/>
-      <c r="E109" s="32"/>
-      <c r="F109" s="32"/>
-      <c r="G109" s="32"/>
-      <c r="H109" s="32"/>
-      <c r="I109" s="32"/>
-      <c r="J109" s="38"/>
-      <c r="K109" s="32"/>
-    </row>
-    <row r="110" spans="1:11">
-      <c r="A110" s="32"/>
-      <c r="B110" s="38"/>
-      <c r="C110" s="32"/>
-      <c r="D110" s="32"/>
-      <c r="E110" s="32"/>
-      <c r="F110" s="32"/>
-      <c r="G110" s="32"/>
-      <c r="H110" s="32"/>
-      <c r="I110" s="32"/>
-      <c r="J110" s="38"/>
-      <c r="K110" s="32"/>
-    </row>
-    <row r="111" spans="1:11">
-      <c r="A111" s="32"/>
-      <c r="B111" s="38"/>
-      <c r="C111" s="32"/>
-      <c r="D111" s="32"/>
-      <c r="E111" s="32"/>
-      <c r="F111" s="32"/>
-      <c r="G111" s="32"/>
-      <c r="H111" s="32"/>
-      <c r="I111" s="32"/>
-      <c r="J111" s="38"/>
-      <c r="K111" s="32"/>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" s="32"/>
-      <c r="B112" s="38"/>
-      <c r="C112" s="32"/>
-      <c r="D112" s="32"/>
-      <c r="E112" s="32"/>
-      <c r="F112" s="32"/>
-      <c r="G112" s="32"/>
-      <c r="H112" s="32"/>
-      <c r="I112" s="32"/>
-      <c r="J112" s="38"/>
-      <c r="K112" s="32"/>
-    </row>
-    <row r="113" spans="1:11">
-      <c r="A113" s="32"/>
-      <c r="B113" s="38"/>
-      <c r="C113" s="32"/>
-      <c r="D113" s="32"/>
-      <c r="E113" s="32"/>
-      <c r="F113" s="32"/>
-      <c r="G113" s="32"/>
-      <c r="H113" s="32"/>
-      <c r="I113" s="32"/>
-      <c r="J113" s="38"/>
-      <c r="K113" s="32"/>
-    </row>
-    <row r="114" spans="1:11">
-      <c r="A114" s="32"/>
-      <c r="B114" s="38"/>
-      <c r="C114" s="32"/>
-      <c r="D114" s="32"/>
-      <c r="E114" s="32"/>
-      <c r="F114" s="32"/>
-      <c r="G114" s="32"/>
-      <c r="H114" s="32"/>
-      <c r="I114" s="32"/>
-      <c r="J114" s="38"/>
-      <c r="K114" s="32"/>
-    </row>
-    <row r="115" spans="1:11">
-      <c r="A115" s="32"/>
-      <c r="B115" s="38"/>
-      <c r="C115" s="32"/>
-      <c r="D115" s="32"/>
-      <c r="E115" s="32"/>
-      <c r="F115" s="32"/>
-      <c r="G115" s="32"/>
-      <c r="H115" s="32"/>
-      <c r="I115" s="32"/>
-      <c r="J115" s="38"/>
-      <c r="K115" s="32"/>
-    </row>
-    <row r="116" spans="1:11">
-      <c r="A116" s="32"/>
-      <c r="B116" s="38"/>
-      <c r="C116" s="32"/>
-      <c r="D116" s="32"/>
-      <c r="E116" s="32"/>
-      <c r="F116" s="32"/>
-      <c r="G116" s="32"/>
-      <c r="H116" s="32"/>
-      <c r="I116" s="32"/>
-      <c r="J116" s="38"/>
-      <c r="K116" s="32"/>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" s="32"/>
-      <c r="B117" s="38"/>
-      <c r="C117" s="32"/>
-      <c r="D117" s="32"/>
-      <c r="E117" s="32"/>
-      <c r="F117" s="32"/>
-      <c r="G117" s="32"/>
-      <c r="H117" s="32"/>
-      <c r="I117" s="32"/>
-      <c r="J117" s="38"/>
-      <c r="K117" s="32"/>
-    </row>
-    <row r="118" spans="1:11">
-      <c r="A118" s="32"/>
-      <c r="B118" s="38"/>
-      <c r="C118" s="32"/>
-      <c r="D118" s="32"/>
-      <c r="E118" s="32"/>
-      <c r="F118" s="32"/>
-      <c r="G118" s="32"/>
-      <c r="H118" s="32"/>
-      <c r="I118" s="32"/>
-      <c r="J118" s="38"/>
-      <c r="K118" s="32"/>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" s="32"/>
-      <c r="B119" s="38"/>
-      <c r="C119" s="32"/>
-      <c r="D119" s="32"/>
-      <c r="E119" s="32"/>
-      <c r="F119" s="32"/>
-      <c r="G119" s="32"/>
-      <c r="H119" s="32"/>
-      <c r="I119" s="32"/>
-      <c r="J119" s="38"/>
-      <c r="K119" s="32"/>
-    </row>
-    <row r="120" spans="1:11">
-      <c r="A120" s="32"/>
-      <c r="B120" s="38"/>
-      <c r="C120" s="32"/>
-      <c r="D120" s="32"/>
-      <c r="E120" s="32"/>
-      <c r="F120" s="32"/>
-      <c r="G120" s="32"/>
-      <c r="H120" s="32"/>
-      <c r="I120" s="32"/>
-      <c r="J120" s="38"/>
-      <c r="K120" s="32"/>
-    </row>
-    <row r="121" spans="1:11">
-      <c r="A121" s="32"/>
-      <c r="B121" s="38"/>
-      <c r="C121" s="32"/>
-      <c r="D121" s="32"/>
-      <c r="E121" s="32"/>
-      <c r="F121" s="32"/>
-      <c r="G121" s="32"/>
-      <c r="H121" s="32"/>
-      <c r="I121" s="32"/>
-      <c r="J121" s="38"/>
-      <c r="K121" s="32"/>
-    </row>
-    <row r="122" spans="1:11">
-      <c r="A122" s="32"/>
-      <c r="B122" s="38"/>
-      <c r="C122" s="32"/>
-      <c r="D122" s="32"/>
-      <c r="E122" s="32"/>
-      <c r="F122" s="32"/>
-      <c r="G122" s="32"/>
-      <c r="H122" s="32"/>
-      <c r="I122" s="32"/>
-      <c r="J122" s="38"/>
-      <c r="K122" s="32"/>
-    </row>
-    <row r="123" spans="1:11">
-      <c r="A123" s="32"/>
-      <c r="B123" s="38"/>
-      <c r="C123" s="32"/>
-      <c r="D123" s="32"/>
-      <c r="E123" s="32"/>
-      <c r="F123" s="32"/>
-      <c r="G123" s="32"/>
-      <c r="H123" s="32"/>
-      <c r="I123" s="32"/>
-      <c r="J123" s="38"/>
-      <c r="K123" s="32"/>
-    </row>
-    <row r="124" spans="1:11">
-      <c r="A124" s="32"/>
-      <c r="B124" s="38"/>
-      <c r="C124" s="32"/>
-      <c r="D124" s="32"/>
-      <c r="E124" s="32"/>
-      <c r="F124" s="32"/>
-      <c r="G124" s="32"/>
-      <c r="H124" s="32"/>
-      <c r="I124" s="32"/>
-      <c r="J124" s="38"/>
-      <c r="K124" s="32"/>
-    </row>
-    <row r="125" spans="1:11">
-      <c r="A125" s="32"/>
-      <c r="B125" s="38"/>
-      <c r="C125" s="32"/>
-      <c r="D125" s="32"/>
-      <c r="E125" s="32"/>
-      <c r="F125" s="32"/>
-      <c r="G125" s="32"/>
-      <c r="H125" s="32"/>
-      <c r="I125" s="32"/>
-      <c r="J125" s="38"/>
-      <c r="K125" s="32"/>
-    </row>
-    <row r="126" spans="1:11">
-      <c r="A126" s="32"/>
-      <c r="B126" s="38"/>
-      <c r="C126" s="32"/>
-      <c r="D126" s="32"/>
-      <c r="E126" s="32"/>
-      <c r="F126" s="32"/>
-      <c r="G126" s="32"/>
-      <c r="H126" s="32"/>
-      <c r="I126" s="32"/>
-      <c r="J126" s="38"/>
-      <c r="K126" s="32"/>
-    </row>
-    <row r="127" spans="1:11">
-      <c r="A127" s="32"/>
-      <c r="B127" s="38"/>
-      <c r="C127" s="32"/>
-      <c r="D127" s="32"/>
-      <c r="E127" s="32"/>
-      <c r="F127" s="32"/>
-      <c r="G127" s="32"/>
-      <c r="H127" s="32"/>
-      <c r="I127" s="32"/>
-      <c r="J127" s="38"/>
-      <c r="K127" s="32"/>
-    </row>
-    <row r="128" spans="1:11">
-      <c r="A128" s="32"/>
-      <c r="B128" s="38"/>
-      <c r="C128" s="32"/>
-      <c r="D128" s="32"/>
-      <c r="E128" s="32"/>
-      <c r="F128" s="32"/>
-      <c r="G128" s="32"/>
-      <c r="H128" s="32"/>
-      <c r="I128" s="32"/>
-      <c r="J128" s="38"/>
-      <c r="K128" s="32"/>
-    </row>
-    <row r="129" spans="1:11">
-      <c r="A129" s="32"/>
-      <c r="B129" s="38"/>
-      <c r="C129" s="32"/>
-      <c r="D129" s="32"/>
-      <c r="E129" s="32"/>
-      <c r="F129" s="32"/>
-      <c r="G129" s="32"/>
-      <c r="H129" s="32"/>
-      <c r="I129" s="32"/>
-      <c r="J129" s="38"/>
-      <c r="K129" s="32"/>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" s="32"/>
-      <c r="B130" s="38"/>
-      <c r="C130" s="32"/>
-      <c r="D130" s="32"/>
-      <c r="E130" s="32"/>
-      <c r="F130" s="32"/>
-      <c r="G130" s="32"/>
-      <c r="H130" s="32"/>
-      <c r="I130" s="32"/>
-      <c r="J130" s="38"/>
-      <c r="K130" s="32"/>
-    </row>
-    <row r="131" spans="1:11">
-      <c r="A131" s="32"/>
-      <c r="B131" s="38"/>
-      <c r="C131" s="32"/>
-      <c r="D131" s="32"/>
-      <c r="E131" s="32"/>
-      <c r="F131" s="32"/>
-      <c r="G131" s="32"/>
-      <c r="H131" s="32"/>
-      <c r="I131" s="32"/>
-      <c r="J131" s="38"/>
-      <c r="K131" s="32"/>
-    </row>
-    <row r="132" spans="1:11">
-      <c r="A132" s="32"/>
-      <c r="B132" s="38"/>
-      <c r="C132" s="32"/>
-      <c r="D132" s="32"/>
-      <c r="E132" s="32"/>
-      <c r="F132" s="32"/>
-      <c r="G132" s="32"/>
-      <c r="H132" s="32"/>
-      <c r="I132" s="32"/>
-      <c r="J132" s="38"/>
-      <c r="K132" s="32"/>
-    </row>
-    <row r="133" spans="1:11">
-      <c r="A133" s="32"/>
-      <c r="B133" s="38"/>
-      <c r="C133" s="32"/>
-      <c r="D133" s="32"/>
-      <c r="E133" s="32"/>
-      <c r="F133" s="32"/>
-      <c r="G133" s="32"/>
-      <c r="H133" s="32"/>
-      <c r="I133" s="32"/>
-      <c r="J133" s="38"/>
-      <c r="K133" s="32"/>
-    </row>
-    <row r="134" spans="1:11">
-      <c r="A134" s="32"/>
-      <c r="B134" s="38"/>
-      <c r="C134" s="32"/>
-      <c r="D134" s="32"/>
-      <c r="E134" s="32"/>
-      <c r="F134" s="32"/>
-      <c r="G134" s="32"/>
-      <c r="H134" s="32"/>
-      <c r="I134" s="32"/>
-      <c r="J134" s="38"/>
-      <c r="K134" s="32"/>
-    </row>
-    <row r="135" spans="1:11">
-      <c r="A135" s="32"/>
-      <c r="B135" s="38"/>
-      <c r="C135" s="32"/>
-      <c r="D135" s="32"/>
-      <c r="E135" s="32"/>
-      <c r="F135" s="32"/>
-      <c r="G135" s="32"/>
-      <c r="H135" s="32"/>
-      <c r="I135" s="32"/>
-      <c r="J135" s="38"/>
-      <c r="K135" s="32"/>
-    </row>
-    <row r="136" spans="1:11">
-      <c r="A136" s="32"/>
-      <c r="B136" s="38"/>
-      <c r="C136" s="32"/>
-      <c r="D136" s="32"/>
-      <c r="E136" s="32"/>
-      <c r="F136" s="32"/>
-      <c r="G136" s="32"/>
-      <c r="H136" s="32"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="38"/>
-      <c r="K136" s="32"/>
-    </row>
-    <row r="137" spans="1:11">
-      <c r="A137" s="32"/>
-      <c r="B137" s="38"/>
-      <c r="C137" s="32"/>
-      <c r="D137" s="32"/>
-      <c r="E137" s="32"/>
-      <c r="F137" s="32"/>
-      <c r="G137" s="32"/>
-      <c r="H137" s="32"/>
-      <c r="I137" s="32"/>
-      <c r="J137" s="38"/>
-      <c r="K137" s="32"/>
-    </row>
-    <row r="138" spans="1:11">
-      <c r="A138" s="32"/>
-      <c r="B138" s="38"/>
-      <c r="C138" s="32"/>
-      <c r="D138" s="32"/>
-      <c r="E138" s="32"/>
-      <c r="F138" s="32"/>
-      <c r="G138" s="32"/>
-      <c r="H138" s="32"/>
-      <c r="I138" s="32"/>
-      <c r="J138" s="38"/>
-      <c r="K138" s="32"/>
-    </row>
-    <row r="139" spans="1:11">
-      <c r="A139" s="32"/>
-      <c r="B139" s="38"/>
-      <c r="C139" s="32"/>
-      <c r="D139" s="32"/>
-      <c r="E139" s="32"/>
-      <c r="F139" s="32"/>
-      <c r="G139" s="32"/>
-      <c r="H139" s="32"/>
-      <c r="I139" s="32"/>
-      <c r="J139" s="38"/>
-      <c r="K139" s="32"/>
-    </row>
-    <row r="140" spans="1:11">
-      <c r="A140" s="32"/>
-      <c r="B140" s="38"/>
-      <c r="C140" s="32"/>
-      <c r="D140" s="32"/>
-      <c r="E140" s="32"/>
-      <c r="F140" s="32"/>
-      <c r="G140" s="32"/>
-      <c r="H140" s="32"/>
-      <c r="I140" s="32"/>
-      <c r="J140" s="38"/>
-      <c r="K140" s="32"/>
-    </row>
-    <row r="141" spans="1:11">
-      <c r="A141" s="32"/>
-      <c r="B141" s="38"/>
-      <c r="C141" s="32"/>
-      <c r="D141" s="32"/>
-      <c r="E141" s="32"/>
-      <c r="F141" s="32"/>
-      <c r="G141" s="32"/>
-      <c r="H141" s="32"/>
-      <c r="I141" s="32"/>
-      <c r="J141" s="38"/>
-      <c r="K141" s="32"/>
-    </row>
-    <row r="142" spans="1:11">
-      <c r="A142" s="32"/>
-      <c r="B142" s="38"/>
-      <c r="C142" s="32"/>
-      <c r="D142" s="32"/>
-      <c r="E142" s="32"/>
-      <c r="F142" s="32"/>
-      <c r="G142" s="32"/>
-      <c r="H142" s="32"/>
-      <c r="I142" s="32"/>
-      <c r="J142" s="38"/>
-      <c r="K142" s="32"/>
-    </row>
-    <row r="143" spans="1:11">
-      <c r="A143" s="32"/>
-      <c r="B143" s="38"/>
-      <c r="C143" s="32"/>
-      <c r="D143" s="32"/>
-      <c r="E143" s="32"/>
-      <c r="F143" s="32"/>
-      <c r="G143" s="32"/>
-      <c r="H143" s="32"/>
-      <c r="I143" s="32"/>
-      <c r="J143" s="38"/>
-      <c r="K143" s="32"/>
-    </row>
-    <row r="144" spans="1:11">
-      <c r="A144" s="32"/>
-      <c r="B144" s="38"/>
-      <c r="C144" s="32"/>
-      <c r="D144" s="32"/>
-      <c r="E144" s="32"/>
-      <c r="F144" s="32"/>
-      <c r="G144" s="32"/>
-      <c r="H144" s="32"/>
-      <c r="I144" s="32"/>
-      <c r="J144" s="38"/>
-      <c r="K144" s="32"/>
-    </row>
-    <row r="145" spans="1:11">
-      <c r="A145" s="32"/>
-      <c r="B145" s="38"/>
-      <c r="C145" s="32"/>
-      <c r="D145" s="32"/>
-      <c r="E145" s="32"/>
-      <c r="F145" s="32"/>
-      <c r="G145" s="32"/>
-      <c r="H145" s="32"/>
-      <c r="I145" s="32"/>
-      <c r="J145" s="38"/>
-      <c r="K145" s="32"/>
-    </row>
-    <row r="146" spans="1:11">
-      <c r="A146" s="32"/>
-      <c r="B146" s="38"/>
-      <c r="C146" s="32"/>
-      <c r="D146" s="32"/>
-      <c r="E146" s="32"/>
-      <c r="F146" s="32"/>
-      <c r="G146" s="32"/>
-      <c r="H146" s="32"/>
-      <c r="I146" s="32"/>
-      <c r="J146" s="38"/>
-      <c r="K146" s="32"/>
+    <row r="1" ht="17.55" spans="1:11">
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+    </row>
+    <row r="2" ht="17.55" spans="1:11">
+      <c r="A2" s="27"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+    </row>
+    <row r="3" ht="17.55" spans="1:11">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+    </row>
+    <row r="4" ht="17.55" spans="1:11">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+    </row>
+    <row r="5" ht="17.55" spans="1:11">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+    </row>
+    <row r="6" ht="17.55" spans="1:11">
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+    </row>
+    <row r="7" ht="17.55" spans="1:11">
+      <c r="A7" s="30"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+    </row>
+    <row r="8" ht="17.55" spans="1:11">
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="30"/>
+    </row>
+    <row r="9" ht="17.55" spans="1:11">
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="30"/>
+    </row>
+    <row r="10" ht="17.55" spans="1:11">
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="30"/>
+    </row>
+    <row r="11" ht="17.55" spans="1:11">
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="30"/>
+    </row>
+    <row r="12" ht="17.55" spans="1:11">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="30"/>
+    </row>
+    <row r="13" ht="17.55" spans="1:11">
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="30"/>
+    </row>
+    <row r="14" ht="17.55" spans="1:11">
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+    </row>
+    <row r="15" ht="17.55" spans="1:11">
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
+    </row>
+    <row r="16" ht="17.55" spans="1:11">
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+    </row>
+    <row r="17" ht="17.55" spans="1:11">
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+    </row>
+    <row r="18" ht="17.55" spans="1:11">
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+    </row>
+    <row r="19" ht="17.55" spans="1:11">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="30"/>
+    </row>
+    <row r="20" ht="17.55" spans="1:11">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+    </row>
+    <row r="21" ht="17.55" spans="1:11">
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="30"/>
+    </row>
+    <row r="22" ht="17.55" spans="1:11">
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+    </row>
+    <row r="23" ht="17.55" spans="1:11">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+    </row>
+    <row r="24" ht="17.55" spans="1:11">
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+    </row>
+    <row r="25" ht="17.55" spans="1:11">
+      <c r="A25" s="30"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="30"/>
+    </row>
+    <row r="26" ht="17.55" spans="1:11">
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+    </row>
+    <row r="27" ht="17.55" spans="1:11">
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+    </row>
+    <row r="28" ht="17.55" spans="1:11">
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+    </row>
+    <row r="29" ht="17.55" spans="1:11">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+    </row>
+    <row r="30" ht="17.55" spans="1:11">
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
+    </row>
+    <row r="31" ht="17.55" spans="1:11">
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+    </row>
+    <row r="32" ht="17.55" spans="1:11">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+    </row>
+    <row r="33" ht="17.55" spans="1:11">
+      <c r="A33" s="30"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="30"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="30"/>
+    </row>
+    <row r="34" ht="17.55" spans="1:11">
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="30"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="30"/>
+    </row>
+    <row r="35" ht="17.55" spans="1:11">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="30"/>
+      <c r="J35" s="30"/>
+      <c r="K35" s="30"/>
+    </row>
+    <row r="36" ht="17.55" spans="1:11">
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="30"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+    </row>
+    <row r="37" ht="17.55" spans="1:11">
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+    </row>
+    <row r="38" ht="17.55" spans="1:11">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="30"/>
+      <c r="J38" s="30"/>
+      <c r="K38" s="30"/>
+    </row>
+    <row r="39" ht="17.55" spans="1:11">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="30"/>
+      <c r="J39" s="30"/>
+      <c r="K39" s="30"/>
+    </row>
+    <row r="40" ht="17.55" spans="1:11">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+    </row>
+    <row r="41" ht="17.55" spans="1:11">
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="30"/>
+      <c r="J41" s="30"/>
+      <c r="K41" s="30"/>
+    </row>
+    <row r="42" ht="17.55" spans="1:11">
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="30"/>
+    </row>
+    <row r="43" ht="17.55" spans="1:11">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+    </row>
+    <row r="44" ht="17.55" spans="1:11">
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="30"/>
+      <c r="J44" s="30"/>
+      <c r="K44" s="30"/>
+    </row>
+    <row r="45" ht="17.55" spans="1:11">
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+    </row>
+    <row r="46" ht="17.55" spans="1:11">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+    </row>
+    <row r="47" ht="17.55" spans="1:11">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
+    </row>
+    <row r="48" ht="17.55" spans="1:11">
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="30"/>
+      <c r="J48" s="30"/>
+      <c r="K48" s="30"/>
+    </row>
+    <row r="49" ht="17.55" spans="1:11">
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+    </row>
+    <row r="50" ht="17.55" spans="1:11">
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="30"/>
+      <c r="J50" s="30"/>
+      <c r="K50" s="30"/>
+    </row>
+    <row r="51" ht="17.55" spans="1:11">
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="30"/>
+      <c r="J51" s="30"/>
+      <c r="K51" s="30"/>
+    </row>
+    <row r="52" ht="17.55" spans="1:11">
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+    </row>
+    <row r="53" ht="17.55" spans="1:11">
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="30"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+    </row>
+    <row r="54" ht="17.55" spans="1:11">
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="30"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+    </row>
+    <row r="55" ht="17.55" spans="1:11">
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+    </row>
+    <row r="56" ht="17.55" spans="1:11">
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="30"/>
+      <c r="J56" s="30"/>
+      <c r="K56" s="30"/>
+    </row>
+    <row r="57" ht="17.55" spans="1:11">
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="30"/>
+      <c r="J57" s="30"/>
+      <c r="K57" s="30"/>
+    </row>
+    <row r="58" ht="17.55" spans="1:11">
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+    </row>
+    <row r="59" ht="17.55" spans="1:11">
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
+    </row>
+    <row r="60" ht="17.55" spans="1:11">
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30"/>
+      <c r="J60" s="30"/>
+      <c r="K60" s="30"/>
+    </row>
+    <row r="61" ht="17.55" spans="1:11">
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+    </row>
+    <row r="62" ht="17.55" spans="1:11">
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30"/>
+      <c r="J62" s="30"/>
+      <c r="K62" s="30"/>
+    </row>
+    <row r="63" ht="17.55" spans="1:11">
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="30"/>
+    </row>
+    <row r="64" ht="17.55" spans="1:11">
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+    </row>
+    <row r="65" ht="17.55" spans="1:11">
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30"/>
+      <c r="J65" s="30"/>
+      <c r="K65" s="30"/>
+    </row>
+    <row r="66" ht="17.55" spans="1:11">
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30"/>
+      <c r="J66" s="30"/>
+      <c r="K66" s="30"/>
+    </row>
+    <row r="67" ht="17.55" spans="1:11">
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+    </row>
+    <row r="68" ht="17.55" spans="1:11">
+      <c r="A68" s="30"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+    </row>
+    <row r="69" ht="17.55" spans="1:11">
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="30"/>
+      <c r="J69" s="30"/>
+      <c r="K69" s="30"/>
+    </row>
+    <row r="70" ht="17.55" spans="1:11">
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+    </row>
+    <row r="71" ht="17.55" spans="1:11">
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+    </row>
+    <row r="72" ht="17.55" spans="1:11">
+      <c r="A72" s="30"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="30"/>
+      <c r="J72" s="30"/>
+      <c r="K72" s="30"/>
+    </row>
+    <row r="73" ht="17.55" spans="1:11">
+      <c r="A73" s="30"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="30"/>
+      <c r="J73" s="30"/>
+      <c r="K73" s="30"/>
+    </row>
+    <row r="74" ht="17.55" spans="1:11">
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="30"/>
+      <c r="J74" s="30"/>
+      <c r="K74" s="30"/>
+    </row>
+    <row r="75" ht="17.55" spans="1:11">
+      <c r="A75" s="30"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="30"/>
+      <c r="J75" s="30"/>
+      <c r="K75" s="30"/>
+    </row>
+    <row r="76" ht="17.55" spans="1:11">
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+    </row>
+    <row r="77" ht="17.55" spans="1:11">
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="30"/>
+      <c r="J77" s="30"/>
+      <c r="K77" s="30"/>
+    </row>
+    <row r="78" ht="17.55" spans="1:11">
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="30"/>
+      <c r="J78" s="30"/>
+      <c r="K78" s="30"/>
+    </row>
+    <row r="79" ht="17.55" spans="1:11">
+      <c r="A79" s="30"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="30"/>
+      <c r="J79" s="30"/>
+      <c r="K79" s="30"/>
+    </row>
+    <row r="80" ht="17.55" spans="1:11">
+      <c r="A80" s="30"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="30"/>
+      <c r="J80" s="30"/>
+      <c r="K80" s="30"/>
+    </row>
+    <row r="81" ht="17.55" spans="1:11">
+      <c r="A81" s="30"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="30"/>
+      <c r="D81" s="30"/>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="30"/>
+      <c r="H81" s="30"/>
+      <c r="I81" s="30"/>
+      <c r="J81" s="30"/>
+      <c r="K81" s="30"/>
+    </row>
+    <row r="82" ht="17.55" spans="1:11">
+      <c r="A82" s="30"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
+      <c r="D82" s="30"/>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+      <c r="G82" s="30"/>
+      <c r="H82" s="30"/>
+      <c r="I82" s="30"/>
+      <c r="J82" s="30"/>
+      <c r="K82" s="30"/>
+    </row>
+    <row r="83" ht="17.55" spans="1:11">
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="30"/>
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+      <c r="G83" s="30"/>
+      <c r="H83" s="30"/>
+      <c r="I83" s="30"/>
+      <c r="J83" s="30"/>
+      <c r="K83" s="30"/>
+    </row>
+    <row r="84" ht="17.55" spans="1:11">
+      <c r="A84" s="30"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
+      <c r="D84" s="30"/>
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+      <c r="G84" s="30"/>
+      <c r="H84" s="30"/>
+      <c r="I84" s="30"/>
+      <c r="J84" s="30"/>
+      <c r="K84" s="30"/>
+    </row>
+    <row r="85" ht="17.55" spans="1:11">
+      <c r="A85" s="30"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
+      <c r="D85" s="30"/>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+      <c r="G85" s="30"/>
+      <c r="H85" s="30"/>
+      <c r="I85" s="30"/>
+      <c r="J85" s="30"/>
+      <c r="K85" s="30"/>
+    </row>
+    <row r="86" ht="17.55" spans="1:11">
+      <c r="A86" s="30"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
+      <c r="D86" s="30"/>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+      <c r="G86" s="30"/>
+      <c r="H86" s="30"/>
+      <c r="I86" s="30"/>
+      <c r="J86" s="30"/>
+      <c r="K86" s="30"/>
+    </row>
+    <row r="87" ht="17.55" spans="1:11">
+      <c r="A87" s="30"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
+      <c r="D87" s="30"/>
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+      <c r="G87" s="30"/>
+      <c r="H87" s="30"/>
+      <c r="I87" s="30"/>
+      <c r="J87" s="30"/>
+      <c r="K87" s="30"/>
+    </row>
+    <row r="88" ht="17.55" spans="1:11">
+      <c r="A88" s="30"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
+      <c r="D88" s="30"/>
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+      <c r="G88" s="30"/>
+      <c r="H88" s="30"/>
+      <c r="I88" s="30"/>
+      <c r="J88" s="30"/>
+      <c r="K88" s="30"/>
+    </row>
+    <row r="89" ht="17.55" spans="1:11">
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
+      <c r="D89" s="30"/>
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+      <c r="G89" s="30"/>
+      <c r="H89" s="30"/>
+      <c r="I89" s="30"/>
+      <c r="J89" s="30"/>
+      <c r="K89" s="30"/>
+    </row>
+    <row r="90" ht="17.55" spans="1:11">
+      <c r="A90" s="30"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
+      <c r="D90" s="30"/>
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+      <c r="G90" s="30"/>
+      <c r="H90" s="30"/>
+      <c r="I90" s="30"/>
+      <c r="J90" s="30"/>
+      <c r="K90" s="30"/>
+    </row>
+    <row r="91" ht="17.55" spans="1:11">
+      <c r="A91" s="30"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
+      <c r="D91" s="30"/>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
+      <c r="G91" s="30"/>
+      <c r="H91" s="30"/>
+      <c r="I91" s="30"/>
+      <c r="J91" s="30"/>
+      <c r="K91" s="30"/>
+    </row>
+    <row r="92" ht="17.55" spans="1:11">
+      <c r="A92" s="30"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
+      <c r="D92" s="30"/>
+      <c r="E92" s="30"/>
+      <c r="F92" s="30"/>
+      <c r="G92" s="30"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="30"/>
+      <c r="K92" s="30"/>
+    </row>
+    <row r="93" ht="17.55" spans="1:11">
+      <c r="A93" s="30"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
+      <c r="D93" s="30"/>
+      <c r="E93" s="30"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="30"/>
+      <c r="H93" s="30"/>
+      <c r="I93" s="30"/>
+      <c r="J93" s="30"/>
+      <c r="K93" s="30"/>
+    </row>
+    <row r="94" ht="17.55" spans="1:11">
+      <c r="A94" s="30"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
+      <c r="D94" s="30"/>
+      <c r="E94" s="30"/>
+      <c r="F94" s="30"/>
+      <c r="G94" s="30"/>
+      <c r="H94" s="30"/>
+      <c r="I94" s="30"/>
+      <c r="J94" s="30"/>
+      <c r="K94" s="30"/>
+    </row>
+    <row r="95" ht="17.55" spans="1:11">
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
+      <c r="D95" s="30"/>
+      <c r="E95" s="30"/>
+      <c r="F95" s="30"/>
+      <c r="G95" s="30"/>
+      <c r="H95" s="30"/>
+      <c r="I95" s="30"/>
+      <c r="J95" s="30"/>
+      <c r="K95" s="30"/>
+    </row>
+    <row r="96" ht="17.55" spans="1:11">
+      <c r="A96" s="30"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="30"/>
+      <c r="E96" s="30"/>
+      <c r="F96" s="30"/>
+      <c r="G96" s="30"/>
+      <c r="H96" s="30"/>
+      <c r="I96" s="30"/>
+      <c r="J96" s="30"/>
+      <c r="K96" s="30"/>
+    </row>
+    <row r="97" ht="17.55" spans="1:11">
+      <c r="A97" s="30"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="30"/>
+      <c r="H97" s="30"/>
+      <c r="I97" s="30"/>
+      <c r="J97" s="30"/>
+      <c r="K97" s="30"/>
+    </row>
+    <row r="98" ht="17.55" spans="1:11">
+      <c r="A98" s="30"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="30"/>
+      <c r="E98" s="30"/>
+      <c r="F98" s="30"/>
+      <c r="G98" s="30"/>
+      <c r="H98" s="30"/>
+      <c r="I98" s="30"/>
+      <c r="J98" s="30"/>
+      <c r="K98" s="30"/>
+    </row>
+    <row r="99" ht="17.55" spans="1:11">
+      <c r="A99" s="30"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="30"/>
+      <c r="K99" s="30"/>
+    </row>
+    <row r="100" ht="17.55" spans="1:11">
+      <c r="A100" s="30"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="30"/>
+      <c r="K100" s="30"/>
+    </row>
+    <row r="101" ht="17.55" spans="1:11">
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="30"/>
+      <c r="K101" s="30"/>
+    </row>
+    <row r="102" ht="17.55" spans="1:11">
+      <c r="A102" s="26"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="26"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="26"/>
+      <c r="H102" s="26"/>
+      <c r="I102" s="26"/>
+      <c r="J102" s="26"/>
+      <c r="K102" s="26"/>
+    </row>
+    <row r="103" ht="17.55" spans="1:11">
+      <c r="A103" s="26"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="26"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="26"/>
+      <c r="G103" s="26"/>
+      <c r="H103" s="26"/>
+      <c r="I103" s="26"/>
+      <c r="J103" s="26"/>
+      <c r="K103" s="26"/>
+    </row>
+    <row r="104" ht="17.55" spans="1:11">
+      <c r="A104" s="27"/>
+      <c r="B104" s="27"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="27"/>
+      <c r="H104" s="27"/>
+      <c r="I104" s="27"/>
+      <c r="J104" s="27"/>
+      <c r="K104" s="27"/>
+    </row>
+    <row r="105" ht="17.55" spans="1:11">
+      <c r="A105" s="30"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
+      <c r="I105" s="30"/>
+      <c r="J105" s="30"/>
+      <c r="K105" s="30"/>
+    </row>
+    <row r="106" ht="17.55" spans="1:11">
+      <c r="A106" s="30"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="30"/>
+      <c r="D106" s="30"/>
+      <c r="E106" s="30"/>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+      <c r="H106" s="30"/>
+      <c r="I106" s="30"/>
+      <c r="J106" s="30"/>
+      <c r="K106" s="30"/>
+    </row>
+    <row r="107" ht="17.55" spans="1:11">
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
+      <c r="D107" s="30"/>
+      <c r="E107" s="30"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="30"/>
+      <c r="H107" s="30"/>
+      <c r="I107" s="30"/>
+      <c r="J107" s="30"/>
+      <c r="K107" s="30"/>
+    </row>
+    <row r="108" ht="17.55" spans="1:11">
+      <c r="A108" s="30"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
+      <c r="D108" s="30"/>
+      <c r="E108" s="30"/>
+      <c r="F108" s="30"/>
+      <c r="G108" s="30"/>
+      <c r="H108" s="30"/>
+      <c r="I108" s="30"/>
+      <c r="J108" s="30"/>
+      <c r="K108" s="30"/>
+    </row>
+    <row r="109" ht="17.55" spans="1:11">
+      <c r="A109" s="30"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="30"/>
+      <c r="D109" s="30"/>
+      <c r="E109" s="30"/>
+      <c r="F109" s="30"/>
+      <c r="G109" s="30"/>
+      <c r="H109" s="30"/>
+      <c r="I109" s="30"/>
+      <c r="J109" s="30"/>
+      <c r="K109" s="30"/>
+    </row>
+    <row r="110" ht="17.55" spans="1:11">
+      <c r="A110" s="30"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="30"/>
+      <c r="D110" s="30"/>
+      <c r="E110" s="30"/>
+      <c r="F110" s="30"/>
+      <c r="G110" s="30"/>
+      <c r="H110" s="30"/>
+      <c r="I110" s="30"/>
+      <c r="J110" s="30"/>
+      <c r="K110" s="30"/>
+    </row>
+    <row r="111" ht="17.55" spans="1:11">
+      <c r="A111" s="30"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="30"/>
+      <c r="D111" s="30"/>
+      <c r="E111" s="30"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+      <c r="H111" s="30"/>
+      <c r="I111" s="30"/>
+      <c r="J111" s="30"/>
+      <c r="K111" s="30"/>
+    </row>
+    <row r="112" ht="17.55" spans="1:11">
+      <c r="A112" s="30"/>
+      <c r="B112" s="30"/>
+      <c r="C112" s="30"/>
+      <c r="D112" s="30"/>
+      <c r="E112" s="30"/>
+      <c r="F112" s="30"/>
+      <c r="G112" s="30"/>
+      <c r="H112" s="30"/>
+      <c r="I112" s="30"/>
+      <c r="J112" s="30"/>
+      <c r="K112" s="30"/>
+    </row>
+    <row r="113" ht="17.55" spans="1:11">
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
+      <c r="D113" s="30"/>
+      <c r="E113" s="30"/>
+      <c r="F113" s="30"/>
+      <c r="G113" s="30"/>
+      <c r="H113" s="30"/>
+      <c r="I113" s="30"/>
+      <c r="J113" s="30"/>
+      <c r="K113" s="30"/>
+    </row>
+    <row r="114" ht="17.55" spans="1:11">
+      <c r="A114" s="30"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30"/>
+      <c r="E114" s="30"/>
+      <c r="F114" s="30"/>
+      <c r="G114" s="30"/>
+      <c r="H114" s="30"/>
+      <c r="I114" s="30"/>
+      <c r="J114" s="30"/>
+      <c r="K114" s="30"/>
+    </row>
+    <row r="115" ht="17.55" spans="1:11">
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="30"/>
+      <c r="D115" s="30"/>
+      <c r="E115" s="30"/>
+      <c r="F115" s="30"/>
+      <c r="G115" s="30"/>
+      <c r="H115" s="30"/>
+      <c r="I115" s="30"/>
+      <c r="J115" s="30"/>
+      <c r="K115" s="30"/>
+    </row>
+    <row r="116" ht="17.55" spans="1:11">
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="30"/>
+      <c r="D116" s="30"/>
+      <c r="E116" s="30"/>
+      <c r="F116" s="30"/>
+      <c r="G116" s="30"/>
+      <c r="H116" s="30"/>
+      <c r="I116" s="30"/>
+      <c r="J116" s="30"/>
+      <c r="K116" s="30"/>
+    </row>
+    <row r="117" ht="17.55" spans="1:11">
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="30"/>
+      <c r="D117" s="30"/>
+      <c r="E117" s="30"/>
+      <c r="F117" s="30"/>
+      <c r="G117" s="30"/>
+      <c r="H117" s="30"/>
+      <c r="I117" s="30"/>
+      <c r="J117" s="30"/>
+      <c r="K117" s="30"/>
+    </row>
+    <row r="118" ht="17.55" spans="1:11">
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="30"/>
+      <c r="H118" s="30"/>
+      <c r="I118" s="30"/>
+      <c r="J118" s="30"/>
+      <c r="K118" s="30"/>
+    </row>
+    <row r="119" ht="17.55" spans="1:11">
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
+      <c r="D119" s="30"/>
+      <c r="E119" s="30"/>
+      <c r="F119" s="30"/>
+      <c r="G119" s="30"/>
+      <c r="H119" s="30"/>
+      <c r="I119" s="30"/>
+      <c r="J119" s="30"/>
+      <c r="K119" s="30"/>
+    </row>
+    <row r="120" ht="17.55" spans="1:11">
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="30"/>
+      <c r="D120" s="30"/>
+      <c r="E120" s="30"/>
+      <c r="F120" s="30"/>
+      <c r="G120" s="30"/>
+      <c r="H120" s="30"/>
+      <c r="I120" s="30"/>
+      <c r="J120" s="30"/>
+      <c r="K120" s="30"/>
+    </row>
+    <row r="121" ht="17.55" spans="1:11">
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="30"/>
+      <c r="D121" s="30"/>
+      <c r="E121" s="30"/>
+      <c r="F121" s="30"/>
+      <c r="G121" s="30"/>
+      <c r="H121" s="30"/>
+      <c r="I121" s="30"/>
+      <c r="J121" s="30"/>
+      <c r="K121" s="30"/>
+    </row>
+    <row r="122" ht="17.55" spans="1:11">
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="30"/>
+      <c r="D122" s="30"/>
+      <c r="E122" s="30"/>
+      <c r="F122" s="30"/>
+      <c r="G122" s="30"/>
+      <c r="H122" s="30"/>
+      <c r="I122" s="30"/>
+      <c r="J122" s="30"/>
+      <c r="K122" s="30"/>
+    </row>
+    <row r="123" ht="17.55" spans="1:11">
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
+      <c r="D123" s="30"/>
+      <c r="E123" s="30"/>
+      <c r="F123" s="30"/>
+      <c r="G123" s="30"/>
+      <c r="H123" s="30"/>
+      <c r="I123" s="30"/>
+      <c r="J123" s="30"/>
+      <c r="K123" s="30"/>
+    </row>
+    <row r="124" ht="17.55" spans="1:11">
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="30"/>
+      <c r="D124" s="30"/>
+      <c r="E124" s="30"/>
+      <c r="F124" s="30"/>
+      <c r="G124" s="30"/>
+      <c r="H124" s="30"/>
+      <c r="I124" s="30"/>
+      <c r="J124" s="30"/>
+      <c r="K124" s="30"/>
+    </row>
+    <row r="125" ht="17.55" spans="1:11">
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
+      <c r="D125" s="30"/>
+      <c r="E125" s="30"/>
+      <c r="F125" s="30"/>
+      <c r="G125" s="30"/>
+      <c r="H125" s="30"/>
+      <c r="I125" s="30"/>
+      <c r="J125" s="30"/>
+      <c r="K125" s="30"/>
+    </row>
+    <row r="126" ht="17.55" spans="1:11">
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="30"/>
+      <c r="D126" s="30"/>
+      <c r="E126" s="30"/>
+      <c r="F126" s="30"/>
+      <c r="G126" s="30"/>
+      <c r="H126" s="30"/>
+      <c r="I126" s="30"/>
+      <c r="J126" s="30"/>
+      <c r="K126" s="30"/>
+    </row>
+    <row r="127" ht="17.55" spans="1:11">
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="30"/>
+      <c r="D127" s="30"/>
+      <c r="E127" s="30"/>
+      <c r="F127" s="30"/>
+      <c r="G127" s="30"/>
+      <c r="H127" s="30"/>
+      <c r="I127" s="30"/>
+      <c r="J127" s="30"/>
+      <c r="K127" s="30"/>
+    </row>
+    <row r="128" ht="17.55" spans="1:11">
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="30"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="30"/>
+      <c r="G128" s="30"/>
+      <c r="H128" s="30"/>
+      <c r="I128" s="30"/>
+      <c r="J128" s="30"/>
+      <c r="K128" s="30"/>
+    </row>
+    <row r="129" ht="17.55" spans="1:11">
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="30"/>
+      <c r="D129" s="30"/>
+      <c r="E129" s="30"/>
+      <c r="F129" s="30"/>
+      <c r="G129" s="30"/>
+      <c r="H129" s="30"/>
+      <c r="I129" s="30"/>
+      <c r="J129" s="30"/>
+      <c r="K129" s="30"/>
+    </row>
+    <row r="130" ht="17.55" spans="1:11">
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
+      <c r="D130" s="30"/>
+      <c r="E130" s="30"/>
+      <c r="F130" s="30"/>
+      <c r="G130" s="30"/>
+      <c r="H130" s="30"/>
+      <c r="I130" s="30"/>
+      <c r="J130" s="30"/>
+      <c r="K130" s="30"/>
+    </row>
+    <row r="131" ht="17.55" spans="1:11">
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
+      <c r="D131" s="30"/>
+      <c r="E131" s="30"/>
+      <c r="F131" s="30"/>
+      <c r="G131" s="30"/>
+      <c r="H131" s="30"/>
+      <c r="I131" s="30"/>
+      <c r="J131" s="30"/>
+      <c r="K131" s="30"/>
+    </row>
+    <row r="132" ht="17.55" spans="1:11">
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="30"/>
+      <c r="D132" s="30"/>
+      <c r="E132" s="30"/>
+      <c r="F132" s="30"/>
+      <c r="G132" s="30"/>
+      <c r="H132" s="30"/>
+      <c r="I132" s="30"/>
+      <c r="J132" s="30"/>
+      <c r="K132" s="30"/>
+    </row>
+    <row r="133" ht="17.55" spans="1:11">
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="30"/>
+      <c r="D133" s="30"/>
+      <c r="E133" s="30"/>
+      <c r="F133" s="30"/>
+      <c r="G133" s="30"/>
+      <c r="H133" s="30"/>
+      <c r="I133" s="30"/>
+      <c r="J133" s="30"/>
+      <c r="K133" s="30"/>
+    </row>
+    <row r="134" ht="17.55" spans="1:11">
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="30"/>
+      <c r="D134" s="30"/>
+      <c r="E134" s="30"/>
+      <c r="F134" s="30"/>
+      <c r="G134" s="30"/>
+      <c r="H134" s="30"/>
+      <c r="I134" s="30"/>
+      <c r="J134" s="30"/>
+      <c r="K134" s="30"/>
+    </row>
+    <row r="135" ht="17.55" spans="1:11">
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="30"/>
+      <c r="D135" s="30"/>
+      <c r="E135" s="30"/>
+      <c r="F135" s="30"/>
+      <c r="G135" s="30"/>
+      <c r="H135" s="30"/>
+      <c r="I135" s="30"/>
+      <c r="J135" s="30"/>
+      <c r="K135" s="30"/>
+    </row>
+    <row r="136" ht="17.55" spans="1:11">
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="30"/>
+      <c r="F136" s="30"/>
+      <c r="G136" s="30"/>
+      <c r="H136" s="30"/>
+      <c r="I136" s="30"/>
+      <c r="J136" s="30"/>
+      <c r="K136" s="30"/>
+    </row>
+    <row r="137" ht="17.55" spans="1:11">
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
+      <c r="D137" s="30"/>
+      <c r="E137" s="30"/>
+      <c r="F137" s="30"/>
+      <c r="G137" s="30"/>
+      <c r="H137" s="30"/>
+      <c r="I137" s="30"/>
+      <c r="J137" s="30"/>
+      <c r="K137" s="30"/>
+    </row>
+    <row r="138" ht="17.55" spans="1:11">
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="30"/>
+      <c r="D138" s="30"/>
+      <c r="E138" s="30"/>
+      <c r="F138" s="30"/>
+      <c r="G138" s="30"/>
+      <c r="H138" s="30"/>
+      <c r="I138" s="30"/>
+      <c r="J138" s="30"/>
+      <c r="K138" s="30"/>
+    </row>
+    <row r="139" ht="17.55" spans="1:11">
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="30"/>
+      <c r="D139" s="30"/>
+      <c r="E139" s="30"/>
+      <c r="F139" s="30"/>
+      <c r="G139" s="30"/>
+      <c r="H139" s="30"/>
+      <c r="I139" s="30"/>
+      <c r="J139" s="30"/>
+      <c r="K139" s="30"/>
+    </row>
+    <row r="140" ht="17.55" spans="1:11">
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="30"/>
+      <c r="D140" s="30"/>
+      <c r="E140" s="30"/>
+      <c r="F140" s="30"/>
+      <c r="G140" s="30"/>
+      <c r="H140" s="30"/>
+      <c r="I140" s="30"/>
+      <c r="J140" s="30"/>
+      <c r="K140" s="30"/>
+    </row>
+    <row r="141" ht="17.55" spans="1:11">
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="30"/>
+      <c r="E141" s="30"/>
+      <c r="F141" s="30"/>
+      <c r="G141" s="30"/>
+      <c r="H141" s="30"/>
+      <c r="I141" s="30"/>
+      <c r="J141" s="30"/>
+      <c r="K141" s="30"/>
+    </row>
+    <row r="142" ht="17.55" spans="1:11">
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="30"/>
+      <c r="D142" s="30"/>
+      <c r="E142" s="30"/>
+      <c r="F142" s="30"/>
+      <c r="G142" s="30"/>
+      <c r="H142" s="30"/>
+      <c r="I142" s="30"/>
+      <c r="J142" s="30"/>
+      <c r="K142" s="30"/>
+    </row>
+    <row r="143" ht="17.55" spans="1:11">
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
+      <c r="D143" s="30"/>
+      <c r="E143" s="30"/>
+      <c r="F143" s="30"/>
+      <c r="G143" s="30"/>
+      <c r="H143" s="30"/>
+      <c r="I143" s="30"/>
+      <c r="J143" s="30"/>
+      <c r="K143" s="30"/>
+    </row>
+    <row r="144" ht="17.55" spans="1:11">
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="30"/>
+      <c r="E144" s="30"/>
+      <c r="F144" s="30"/>
+      <c r="G144" s="30"/>
+      <c r="H144" s="30"/>
+      <c r="I144" s="30"/>
+      <c r="J144" s="30"/>
+      <c r="K144" s="30"/>
+    </row>
+    <row r="145" ht="17.55" spans="1:11">
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="30"/>
+      <c r="D145" s="30"/>
+      <c r="E145" s="30"/>
+      <c r="F145" s="30"/>
+      <c r="G145" s="30"/>
+      <c r="H145" s="30"/>
+      <c r="I145" s="30"/>
+      <c r="J145" s="30"/>
+      <c r="K145" s="30"/>
+    </row>
+    <row r="146" ht="17.55" spans="1:11">
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="30"/>
+      <c r="D146" s="30"/>
+      <c r="E146" s="30"/>
+      <c r="F146" s="30"/>
+      <c r="G146" s="30"/>
+      <c r="H146" s="30"/>
+      <c r="I146" s="30"/>
+      <c r="J146" s="30"/>
+      <c r="K146" s="30"/>
     </row>
   </sheetData>
   <sortState ref="A2:K107">
@@ -4457,896 +4438,896 @@
   <dimension ref="A1:I80"/>
   <sheetFormatPr defaultColWidth="25.1607142857143" defaultRowHeight="15.2"/>
   <cols>
-    <col min="1" max="1" width="6.83035714285714" style="26" customWidth="1"/>
-    <col min="2" max="2" width="4.83035714285714" style="26" customWidth="1"/>
-    <col min="3" max="3" width="12.8303571428571" style="26" customWidth="1"/>
-    <col min="4" max="5" width="8.66071428571429" style="26" customWidth="1"/>
-    <col min="6" max="6" width="19.5" style="26" customWidth="1"/>
-    <col min="7" max="8" width="8.66071428571429" style="26" customWidth="1"/>
-    <col min="9" max="9" width="20.8303571428571" style="26" customWidth="1"/>
-    <col min="10" max="10" width="25.1607142857143" style="26" customWidth="1"/>
-    <col min="11" max="16384" width="25.1607142857143" style="26"/>
+    <col min="1" max="1" width="6.83035714285714" style="22" customWidth="1"/>
+    <col min="2" max="2" width="4.83035714285714" style="22" customWidth="1"/>
+    <col min="3" max="3" width="12.8303571428571" style="22" customWidth="1"/>
+    <col min="4" max="5" width="8.66071428571429" style="22" customWidth="1"/>
+    <col min="6" max="6" width="19.5" style="22" customWidth="1"/>
+    <col min="7" max="8" width="8.66071428571429" style="22" customWidth="1"/>
+    <col min="9" max="9" width="20.8303571428571" style="22" customWidth="1"/>
+    <col min="10" max="10" width="25.1607142857143" style="22" customWidth="1"/>
+    <col min="11" max="16384" width="25.1607142857143" style="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.55" spans="1:9">
-      <c r="A1" s="27"/>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
+      <c r="A1" s="26"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
     </row>
     <row r="2" ht="17.55" spans="1:9">
-      <c r="A2" s="28"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="31"/>
+      <c r="A2" s="27"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="29"/>
     </row>
     <row r="3" ht="17.55" spans="1:9">
-      <c r="A3" s="32"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="32"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="32"/>
-      <c r="I3" s="34"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="32"/>
     </row>
     <row r="4" ht="17.55" spans="1:9">
-      <c r="A4" s="32"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="32"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="34"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="32"/>
     </row>
     <row r="5" ht="17.55" spans="1:9">
-      <c r="A5" s="32"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="34"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="32"/>
     </row>
     <row r="6" ht="17.55" spans="1:9">
-      <c r="A6" s="32"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="34"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="32"/>
     </row>
     <row r="7" ht="17.55" spans="1:9">
-      <c r="A7" s="32"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="34"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="32"/>
     </row>
     <row r="8" ht="17.55" spans="1:9">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="34"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="32"/>
     </row>
     <row r="9" ht="17.55" spans="1:9">
-      <c r="A9" s="32"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="34"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="32"/>
     </row>
     <row r="10" ht="17.55" spans="1:9">
-      <c r="A10" s="32"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="34"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="32"/>
     </row>
     <row r="11" ht="17.55" spans="1:9">
-      <c r="A11" s="32"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="34"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="31"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="32"/>
     </row>
     <row r="12" ht="17.55" spans="1:9">
-      <c r="A12" s="32"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="34"/>
+      <c r="A12" s="30"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="32"/>
     </row>
     <row r="13" ht="17.55" spans="1:9">
-      <c r="A13" s="32"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="34"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="32"/>
     </row>
     <row r="14" ht="17.55" spans="1:9">
-      <c r="A14" s="32"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
-      <c r="G14" s="32"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="34"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="32"/>
     </row>
     <row r="15" ht="17.55" spans="1:9">
-      <c r="A15" s="32"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="34"/>
+      <c r="A15" s="30"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="32"/>
     </row>
     <row r="16" ht="17.55" spans="1:9">
-      <c r="A16" s="32"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="34"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="32"/>
     </row>
     <row r="17" ht="17.55" spans="1:9">
-      <c r="A17" s="32"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="34"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="32"/>
     </row>
     <row r="18" ht="17.55" spans="1:9">
-      <c r="A18" s="32"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="34"/>
+      <c r="A18" s="30"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="32"/>
     </row>
     <row r="19" ht="17.55" spans="1:9">
-      <c r="A19" s="32"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="34"/>
+      <c r="A19" s="30"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="32"/>
     </row>
     <row r="20" ht="17.55" spans="1:9">
-      <c r="A20" s="32"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="34"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="32"/>
     </row>
     <row r="21" ht="17.55" spans="1:9">
-      <c r="A21" s="32"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="34"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="32"/>
     </row>
     <row r="22" ht="17.55" spans="1:9">
-      <c r="A22" s="32"/>
-      <c r="B22" s="33"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="34"/>
+      <c r="A22" s="30"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="32"/>
     </row>
     <row r="23" ht="17.55" spans="1:9">
-      <c r="A23" s="32"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="32"/>
-      <c r="I23" s="34"/>
+      <c r="A23" s="30"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="32"/>
     </row>
     <row r="24" ht="17.55" spans="1:9">
-      <c r="A24" s="32"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="34"/>
+      <c r="A24" s="30"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="32"/>
     </row>
     <row r="25" ht="17.55" spans="1:9">
-      <c r="A25" s="32"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="34"/>
+      <c r="A25" s="30"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="32"/>
     </row>
     <row r="26" ht="17.55" spans="1:9">
-      <c r="A26" s="32"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="34"/>
+      <c r="A26" s="30"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="32"/>
     </row>
     <row r="27" ht="17.55" spans="1:9">
-      <c r="A27" s="32"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="34"/>
+      <c r="A27" s="30"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="32"/>
     </row>
     <row r="28" ht="17.55" spans="1:9">
-      <c r="A28" s="32"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="34"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="32"/>
     </row>
     <row r="29" ht="17.55" spans="1:9">
-      <c r="A29" s="32"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="34"/>
+      <c r="A29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="32"/>
     </row>
     <row r="30" ht="17.55" spans="1:9">
-      <c r="A30" s="32"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="32"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="34"/>
+      <c r="A30" s="30"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="32"/>
     </row>
     <row r="31" ht="17.55" spans="1:9">
-      <c r="A31" s="32"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="34"/>
+      <c r="A31" s="30"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="32"/>
     </row>
     <row r="32" ht="17.55" spans="1:9">
-      <c r="A32" s="32"/>
-      <c r="B32" s="33"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="34"/>
+      <c r="A32" s="30"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="32"/>
     </row>
     <row r="33" ht="17.55" spans="1:9">
-      <c r="A33" s="32"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="34"/>
+      <c r="A33" s="30"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="30"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
+      <c r="I33" s="32"/>
     </row>
     <row r="34" ht="17.55" spans="1:9">
-      <c r="A34" s="32"/>
-      <c r="B34" s="33"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="34"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
+      <c r="I34" s="32"/>
     </row>
     <row r="35" ht="17.55" spans="1:9">
-      <c r="A35" s="32"/>
-      <c r="B35" s="33"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="34"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
+      <c r="E35" s="30"/>
+      <c r="F35" s="30"/>
+      <c r="G35" s="30"/>
+      <c r="H35" s="30"/>
+      <c r="I35" s="32"/>
     </row>
     <row r="36" ht="17.55" spans="1:9">
-      <c r="A36" s="32"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
-      <c r="G36" s="32"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="34"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="31"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="30"/>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="30"/>
+      <c r="I36" s="32"/>
     </row>
     <row r="37" ht="17.55" spans="1:9">
-      <c r="A37" s="32"/>
-      <c r="B37" s="33"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
-      <c r="G37" s="32"/>
-      <c r="H37" s="32"/>
-      <c r="I37" s="34"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="32"/>
     </row>
     <row r="38" ht="17.55" spans="1:9">
-      <c r="A38" s="32"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="34"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+      <c r="G38" s="30"/>
+      <c r="H38" s="30"/>
+      <c r="I38" s="32"/>
     </row>
     <row r="39" ht="17.55" spans="1:9">
-      <c r="A39" s="32"/>
-      <c r="B39" s="33"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="34"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="30"/>
+      <c r="E39" s="30"/>
+      <c r="F39" s="30"/>
+      <c r="G39" s="30"/>
+      <c r="H39" s="30"/>
+      <c r="I39" s="32"/>
     </row>
     <row r="40" ht="17.55" spans="1:9">
-      <c r="A40" s="32"/>
-      <c r="B40" s="33"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="I40" s="34"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="32"/>
     </row>
     <row r="41" ht="17.55" spans="1:9">
-      <c r="A41" s="32"/>
-      <c r="B41" s="33"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="34"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="32"/>
     </row>
     <row r="42" ht="17.55" spans="1:9">
-      <c r="A42" s="32"/>
-      <c r="B42" s="33"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="34"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="30"/>
+      <c r="D42" s="30"/>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="30"/>
+      <c r="H42" s="30"/>
+      <c r="I42" s="32"/>
     </row>
     <row r="43" ht="17.55" spans="1:9">
-      <c r="A43" s="32"/>
-      <c r="B43" s="33"/>
-      <c r="C43" s="32"/>
-      <c r="D43" s="32"/>
-      <c r="E43" s="32"/>
-      <c r="F43" s="32"/>
-      <c r="G43" s="32"/>
-      <c r="H43" s="32"/>
-      <c r="I43" s="34"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="32"/>
     </row>
     <row r="44" ht="17.55" spans="1:9">
-      <c r="A44" s="32"/>
-      <c r="B44" s="33"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="32"/>
-      <c r="E44" s="32"/>
-      <c r="F44" s="35"/>
-      <c r="G44" s="32"/>
-      <c r="H44" s="32"/>
-      <c r="I44" s="34"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
+      <c r="H44" s="30"/>
+      <c r="I44" s="32"/>
     </row>
     <row r="45" ht="17.55" spans="1:9">
-      <c r="A45" s="32"/>
-      <c r="B45" s="33"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
-      <c r="E45" s="32"/>
-      <c r="F45" s="32"/>
-      <c r="G45" s="32"/>
-      <c r="H45" s="32"/>
-      <c r="I45" s="34"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="30"/>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="32"/>
     </row>
     <row r="46" ht="17.55" spans="1:9">
-      <c r="A46" s="32"/>
-      <c r="B46" s="33"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
-      <c r="E46" s="32"/>
-      <c r="F46" s="32"/>
-      <c r="G46" s="32"/>
-      <c r="H46" s="32"/>
-      <c r="I46" s="34"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="32"/>
     </row>
     <row r="47" ht="17.55" spans="1:9">
-      <c r="A47" s="32"/>
-      <c r="B47" s="33"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
-      <c r="E47" s="32"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="32"/>
-      <c r="H47" s="32"/>
-      <c r="I47" s="34"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+      <c r="G47" s="30"/>
+      <c r="H47" s="30"/>
+      <c r="I47" s="32"/>
     </row>
     <row r="48" ht="17.55" spans="1:9">
-      <c r="A48" s="32"/>
-      <c r="B48" s="33"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
-      <c r="E48" s="32"/>
-      <c r="F48" s="32"/>
-      <c r="G48" s="32"/>
-      <c r="H48" s="32"/>
-      <c r="I48" s="34"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="30"/>
+      <c r="D48" s="30"/>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+      <c r="G48" s="30"/>
+      <c r="H48" s="30"/>
+      <c r="I48" s="32"/>
     </row>
     <row r="49" ht="17.55" spans="1:9">
-      <c r="A49" s="32"/>
-      <c r="B49" s="33"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
-      <c r="E49" s="32"/>
-      <c r="F49" s="32"/>
-      <c r="G49" s="32"/>
-      <c r="H49" s="32"/>
-      <c r="I49" s="34"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="32"/>
     </row>
     <row r="50" ht="17.55" spans="1:9">
-      <c r="A50" s="32"/>
-      <c r="B50" s="33"/>
-      <c r="C50" s="32"/>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="34"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="30"/>
+      <c r="D50" s="30"/>
+      <c r="E50" s="30"/>
+      <c r="F50" s="30"/>
+      <c r="G50" s="30"/>
+      <c r="H50" s="30"/>
+      <c r="I50" s="32"/>
     </row>
     <row r="51" ht="17.55" spans="1:9">
-      <c r="A51" s="32"/>
-      <c r="B51" s="33"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="32"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="34"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="30"/>
+      <c r="D51" s="30"/>
+      <c r="E51" s="30"/>
+      <c r="F51" s="30"/>
+      <c r="G51" s="30"/>
+      <c r="H51" s="30"/>
+      <c r="I51" s="32"/>
     </row>
     <row r="52" ht="17.55" spans="1:9">
-      <c r="A52" s="32"/>
-      <c r="B52" s="33"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="34"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="31"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="32"/>
     </row>
     <row r="53" ht="17.55" spans="1:9">
-      <c r="A53" s="32"/>
-      <c r="B53" s="33"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
-      <c r="E53" s="32"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="32"/>
-      <c r="H53" s="32"/>
-      <c r="I53" s="34"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="31"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="30"/>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+      <c r="G53" s="30"/>
+      <c r="H53" s="30"/>
+      <c r="I53" s="32"/>
     </row>
     <row r="54" ht="17.55" spans="1:9">
-      <c r="A54" s="32"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="32"/>
-      <c r="G54" s="32"/>
-      <c r="H54" s="32"/>
-      <c r="I54" s="34"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="30"/>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+      <c r="G54" s="30"/>
+      <c r="H54" s="30"/>
+      <c r="I54" s="32"/>
     </row>
     <row r="55" ht="17.55" spans="1:9">
-      <c r="A55" s="32"/>
-      <c r="B55" s="33"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
-      <c r="E55" s="32"/>
-      <c r="F55" s="32"/>
-      <c r="G55" s="32"/>
-      <c r="H55" s="32"/>
-      <c r="I55" s="34"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="32"/>
     </row>
     <row r="56" ht="17.55" spans="1:9">
-      <c r="A56" s="32"/>
-      <c r="B56" s="33"/>
-      <c r="C56" s="32"/>
-      <c r="D56" s="32"/>
-      <c r="E56" s="32"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="32"/>
-      <c r="H56" s="32"/>
-      <c r="I56" s="34"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="31"/>
+      <c r="C56" s="30"/>
+      <c r="D56" s="30"/>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+      <c r="G56" s="30"/>
+      <c r="H56" s="30"/>
+      <c r="I56" s="32"/>
     </row>
     <row r="57" ht="17.55" spans="1:9">
-      <c r="A57" s="32"/>
-      <c r="B57" s="33"/>
-      <c r="C57" s="32"/>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="34"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="30"/>
+      <c r="E57" s="30"/>
+      <c r="F57" s="30"/>
+      <c r="G57" s="30"/>
+      <c r="H57" s="30"/>
+      <c r="I57" s="32"/>
     </row>
     <row r="58" ht="17.55" spans="1:9">
-      <c r="A58" s="32"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="32"/>
-      <c r="D58" s="32"/>
-      <c r="E58" s="32"/>
-      <c r="F58" s="32"/>
-      <c r="G58" s="32"/>
-      <c r="H58" s="32"/>
-      <c r="I58" s="34"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="31"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="32"/>
     </row>
     <row r="59" ht="17.55" spans="1:9">
-      <c r="A59" s="32"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="34"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="31"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="32"/>
     </row>
     <row r="60" ht="17.55" spans="1:9">
-      <c r="A60" s="32"/>
-      <c r="B60" s="33"/>
-      <c r="C60" s="32"/>
-      <c r="D60" s="32"/>
-      <c r="E60" s="32"/>
-      <c r="F60" s="32"/>
-      <c r="G60" s="32"/>
-      <c r="H60" s="32"/>
-      <c r="I60" s="34"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="30"/>
+      <c r="D60" s="30"/>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+      <c r="G60" s="30"/>
+      <c r="H60" s="30"/>
+      <c r="I60" s="32"/>
     </row>
     <row r="61" ht="17.55" spans="1:9">
-      <c r="A61" s="32"/>
-      <c r="B61" s="33"/>
-      <c r="C61" s="32"/>
-      <c r="D61" s="32"/>
-      <c r="E61" s="32"/>
-      <c r="F61" s="32"/>
-      <c r="G61" s="32"/>
-      <c r="H61" s="32"/>
-      <c r="I61" s="34"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="31"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="32"/>
     </row>
     <row r="62" ht="17.55" spans="1:9">
-      <c r="A62" s="32"/>
-      <c r="B62" s="33"/>
-      <c r="C62" s="32"/>
-      <c r="D62" s="32"/>
-      <c r="E62" s="32"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="32"/>
-      <c r="H62" s="32"/>
-      <c r="I62" s="34"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="30"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="30"/>
+      <c r="H62" s="30"/>
+      <c r="I62" s="32"/>
     </row>
     <row r="63" ht="17.55" spans="1:9">
-      <c r="A63" s="32"/>
-      <c r="B63" s="33"/>
-      <c r="C63" s="32"/>
-      <c r="D63" s="32"/>
-      <c r="E63" s="32"/>
-      <c r="F63" s="32"/>
-      <c r="G63" s="32"/>
-      <c r="H63" s="32"/>
-      <c r="I63" s="34"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="30"/>
+      <c r="H63" s="30"/>
+      <c r="I63" s="32"/>
     </row>
     <row r="64" ht="17.55" spans="1:9">
-      <c r="A64" s="32"/>
-      <c r="B64" s="33"/>
-      <c r="C64" s="32"/>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="34"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="31"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="32"/>
     </row>
     <row r="65" ht="17.55" spans="1:9">
-      <c r="A65" s="32"/>
-      <c r="B65" s="33"/>
-      <c r="C65" s="32"/>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
-      <c r="H65" s="32"/>
-      <c r="I65" s="34"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="31"/>
+      <c r="C65" s="30"/>
+      <c r="D65" s="30"/>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+      <c r="G65" s="30"/>
+      <c r="H65" s="30"/>
+      <c r="I65" s="32"/>
     </row>
     <row r="66" ht="17.55" spans="1:9">
-      <c r="A66" s="32"/>
-      <c r="B66" s="33"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="32"/>
-      <c r="I66" s="34"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="30"/>
+      <c r="D66" s="30"/>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+      <c r="G66" s="30"/>
+      <c r="H66" s="30"/>
+      <c r="I66" s="32"/>
     </row>
     <row r="67" ht="17.55" spans="1:9">
-      <c r="A67" s="32"/>
-      <c r="B67" s="33"/>
-      <c r="C67" s="32"/>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
-      <c r="G67" s="32"/>
-      <c r="H67" s="32"/>
-      <c r="I67" s="34"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="31"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="32"/>
     </row>
     <row r="68" ht="17.55" spans="1:9">
-      <c r="A68" s="32"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="32"/>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="32"/>
-      <c r="H68" s="32"/>
-      <c r="I68" s="34"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="31"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="32"/>
     </row>
     <row r="69" ht="17.55" spans="1:9">
-      <c r="A69" s="32"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="32"/>
-      <c r="D69" s="32"/>
-      <c r="E69" s="32"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="32"/>
-      <c r="H69" s="32"/>
-      <c r="I69" s="34"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="30"/>
+      <c r="D69" s="30"/>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="30"/>
+      <c r="H69" s="30"/>
+      <c r="I69" s="32"/>
     </row>
     <row r="70" ht="17.55" spans="1:9">
-      <c r="A70" s="32"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="32"/>
-      <c r="D70" s="32"/>
-      <c r="E70" s="32"/>
-      <c r="F70" s="32"/>
-      <c r="G70" s="32"/>
-      <c r="H70" s="32"/>
-      <c r="I70" s="34"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="31"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="32"/>
     </row>
     <row r="71" ht="17.55" spans="1:9">
-      <c r="A71" s="32"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="32"/>
-      <c r="D71" s="32"/>
-      <c r="E71" s="32"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="32"/>
-      <c r="H71" s="32"/>
-      <c r="I71" s="34"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="31"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="32"/>
     </row>
     <row r="72" ht="17.55" spans="1:9">
-      <c r="A72" s="32"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="32"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="34"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="31"/>
+      <c r="C72" s="30"/>
+      <c r="D72" s="30"/>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+      <c r="G72" s="30"/>
+      <c r="H72" s="30"/>
+      <c r="I72" s="32"/>
     </row>
     <row r="73" ht="17.55" spans="1:9">
-      <c r="A73" s="32"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="32"/>
-      <c r="D73" s="32"/>
-      <c r="E73" s="32"/>
-      <c r="F73" s="32"/>
-      <c r="G73" s="32"/>
-      <c r="H73" s="32"/>
-      <c r="I73" s="34"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="31"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="30"/>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="30"/>
+      <c r="I73" s="32"/>
     </row>
     <row r="74" ht="17.55" spans="1:9">
-      <c r="A74" s="32"/>
-      <c r="B74" s="33"/>
-      <c r="C74" s="32"/>
-      <c r="D74" s="32"/>
-      <c r="E74" s="32"/>
-      <c r="F74" s="32"/>
-      <c r="G74" s="32"/>
-      <c r="H74" s="32"/>
-      <c r="I74" s="34"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="31"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="30"/>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+      <c r="G74" s="30"/>
+      <c r="H74" s="30"/>
+      <c r="I74" s="32"/>
     </row>
     <row r="75" ht="17.55" spans="1:9">
-      <c r="A75" s="32"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32"/>
-      <c r="E75" s="32"/>
-      <c r="F75" s="32"/>
-      <c r="G75" s="32"/>
-      <c r="H75" s="32"/>
-      <c r="I75" s="34"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="31"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="30"/>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+      <c r="G75" s="30"/>
+      <c r="H75" s="30"/>
+      <c r="I75" s="32"/>
     </row>
     <row r="76" ht="17.55" spans="1:9">
-      <c r="A76" s="32"/>
-      <c r="B76" s="33"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="32"/>
-      <c r="E76" s="32"/>
-      <c r="F76" s="32"/>
-      <c r="G76" s="32"/>
-      <c r="H76" s="32"/>
-      <c r="I76" s="34"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="31"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="32"/>
     </row>
     <row r="77" ht="17.55" spans="1:9">
-      <c r="A77" s="32"/>
-      <c r="B77" s="33"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="32"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="32"/>
-      <c r="G77" s="32"/>
-      <c r="H77" s="32"/>
-      <c r="I77" s="34"/>
+      <c r="A77" s="30"/>
+      <c r="B77" s="31"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="30"/>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+      <c r="G77" s="30"/>
+      <c r="H77" s="30"/>
+      <c r="I77" s="32"/>
     </row>
     <row r="78" ht="17.55" spans="1:9">
-      <c r="A78" s="32"/>
-      <c r="B78" s="33"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="32"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="32"/>
-      <c r="G78" s="32"/>
-      <c r="H78" s="32"/>
-      <c r="I78" s="34"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="31"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="30"/>
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+      <c r="G78" s="30"/>
+      <c r="H78" s="30"/>
+      <c r="I78" s="32"/>
     </row>
     <row r="79" ht="17.55" spans="1:9">
-      <c r="A79" s="32"/>
-      <c r="B79" s="33"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="34"/>
+      <c r="A79" s="30"/>
+      <c r="B79" s="31"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="30"/>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="30"/>
+      <c r="I79" s="32"/>
     </row>
     <row r="80" ht="17.55" spans="1:9">
-      <c r="A80" s="32"/>
-      <c r="B80" s="33"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
-      <c r="E80" s="32"/>
-      <c r="F80" s="32"/>
-      <c r="G80" s="32"/>
-      <c r="H80" s="32"/>
-      <c r="I80" s="34"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="31"/>
+      <c r="C80" s="30"/>
+      <c r="D80" s="30"/>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+      <c r="G80" s="30"/>
+      <c r="H80" s="30"/>
+      <c r="I80" s="32"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5402,7 +5383,7 @@
       <c r="F2" s="24"/>
       <c r="G2" s="24"/>
       <c r="H2" s="24"/>
-      <c r="I2" s="25"/>
+      <c r="I2" s="24"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
       <c r="L2" s="24"/>
@@ -5423,7 +5404,7 @@
       <c r="F3" s="24"/>
       <c r="G3" s="24"/>
       <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
+      <c r="I3" s="24"/>
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
@@ -5444,7 +5425,7 @@
       <c r="F4" s="24"/>
       <c r="G4" s="24"/>
       <c r="H4" s="24"/>
-      <c r="I4" s="25"/>
+      <c r="I4" s="24"/>
       <c r="J4" s="24"/>
       <c r="K4" s="24"/>
       <c r="L4" s="24"/>
@@ -5465,7 +5446,7 @@
       <c r="F5" s="24"/>
       <c r="G5" s="24"/>
       <c r="H5" s="24"/>
-      <c r="I5" s="25"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="24"/>
       <c r="K5" s="24"/>
       <c r="L5" s="24"/>
@@ -5486,7 +5467,7 @@
       <c r="F6" s="24"/>
       <c r="G6" s="24"/>
       <c r="H6" s="24"/>
-      <c r="I6" s="25"/>
+      <c r="I6" s="24"/>
       <c r="J6" s="24"/>
       <c r="K6" s="24"/>
       <c r="L6" s="24"/>
@@ -5507,7 +5488,7 @@
       <c r="F7" s="24"/>
       <c r="G7" s="24"/>
       <c r="H7" s="24"/>
-      <c r="I7" s="25"/>
+      <c r="I7" s="24"/>
       <c r="J7" s="24"/>
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
@@ -5528,7 +5509,7 @@
       <c r="F8" s="24"/>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
-      <c r="I8" s="25"/>
+      <c r="I8" s="24"/>
       <c r="J8" s="24"/>
       <c r="K8" s="24"/>
       <c r="L8" s="24"/>
@@ -5549,7 +5530,7 @@
       <c r="F9" s="24"/>
       <c r="G9" s="24"/>
       <c r="H9" s="24"/>
-      <c r="I9" s="25"/>
+      <c r="I9" s="24"/>
       <c r="J9" s="24"/>
       <c r="K9" s="24"/>
       <c r="L9" s="24"/>
@@ -5570,7 +5551,7 @@
       <c r="F10" s="24"/>
       <c r="G10" s="24"/>
       <c r="H10" s="24"/>
-      <c r="I10" s="25"/>
+      <c r="I10" s="24"/>
       <c r="J10" s="24"/>
       <c r="K10" s="24"/>
       <c r="L10" s="24"/>
@@ -5591,7 +5572,7 @@
       <c r="F11" s="24"/>
       <c r="G11" s="24"/>
       <c r="H11" s="24"/>
-      <c r="I11" s="25"/>
+      <c r="I11" s="24"/>
       <c r="J11" s="24"/>
       <c r="K11" s="24"/>
       <c r="L11" s="24"/>
@@ -5612,7 +5593,7 @@
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
       <c r="H12" s="24"/>
-      <c r="I12" s="25"/>
+      <c r="I12" s="24"/>
       <c r="J12" s="24"/>
       <c r="K12" s="24"/>
       <c r="L12" s="24"/>
@@ -5633,7 +5614,7 @@
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="24"/>
       <c r="J13" s="24"/>
       <c r="K13" s="24"/>
       <c r="L13" s="24"/>
@@ -5654,7 +5635,7 @@
       <c r="F14" s="24"/>
       <c r="G14" s="24"/>
       <c r="H14" s="24"/>
-      <c r="I14" s="25"/>
+      <c r="I14" s="24"/>
       <c r="J14" s="24"/>
       <c r="K14" s="24"/>
       <c r="L14" s="24"/>
@@ -5675,7 +5656,7 @@
       <c r="F15" s="24"/>
       <c r="G15" s="24"/>
       <c r="H15" s="24"/>
-      <c r="I15" s="25"/>
+      <c r="I15" s="24"/>
       <c r="J15" s="24"/>
       <c r="K15" s="24"/>
       <c r="L15" s="24"/>
@@ -5696,7 +5677,7 @@
       <c r="F16" s="24"/>
       <c r="G16" s="24"/>
       <c r="H16" s="24"/>
-      <c r="I16" s="25"/>
+      <c r="I16" s="24"/>
       <c r="J16" s="24"/>
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
@@ -5717,7 +5698,7 @@
       <c r="F17" s="24"/>
       <c r="G17" s="24"/>
       <c r="H17" s="24"/>
-      <c r="I17" s="25"/>
+      <c r="I17" s="24"/>
       <c r="J17" s="24"/>
       <c r="K17" s="24"/>
       <c r="L17" s="24"/>
@@ -5738,7 +5719,7 @@
       <c r="F18" s="24"/>
       <c r="G18" s="24"/>
       <c r="H18" s="24"/>
-      <c r="I18" s="25"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="24"/>
       <c r="K18" s="24"/>
       <c r="L18" s="24"/>
@@ -5759,7 +5740,7 @@
       <c r="F19" s="24"/>
       <c r="G19" s="24"/>
       <c r="H19" s="24"/>
-      <c r="I19" s="25"/>
+      <c r="I19" s="24"/>
       <c r="J19" s="24"/>
       <c r="K19" s="24"/>
       <c r="L19" s="24"/>
@@ -5780,7 +5761,7 @@
       <c r="F20" s="24"/>
       <c r="G20" s="24"/>
       <c r="H20" s="24"/>
-      <c r="I20" s="25"/>
+      <c r="I20" s="24"/>
       <c r="J20" s="24"/>
       <c r="K20" s="24"/>
       <c r="L20" s="24"/>
@@ -5801,7 +5782,7 @@
       <c r="F21" s="24"/>
       <c r="G21" s="24"/>
       <c r="H21" s="24"/>
-      <c r="I21" s="25"/>
+      <c r="I21" s="24"/>
       <c r="J21" s="24"/>
       <c r="K21" s="24"/>
       <c r="L21" s="24"/>
@@ -5822,7 +5803,7 @@
       <c r="F22" s="24"/>
       <c r="G22" s="24"/>
       <c r="H22" s="24"/>
-      <c r="I22" s="25"/>
+      <c r="I22" s="24"/>
       <c r="J22" s="24"/>
       <c r="K22" s="24"/>
       <c r="L22" s="24"/>
@@ -5843,7 +5824,7 @@
       <c r="F23" s="24"/>
       <c r="G23" s="24"/>
       <c r="H23" s="24"/>
-      <c r="I23" s="25"/>
+      <c r="I23" s="24"/>
       <c r="J23" s="24"/>
       <c r="K23" s="24"/>
       <c r="L23" s="24"/>
@@ -5864,7 +5845,7 @@
       <c r="F24" s="24"/>
       <c r="G24" s="24"/>
       <c r="H24" s="24"/>
-      <c r="I24" s="25"/>
+      <c r="I24" s="24"/>
       <c r="J24" s="24"/>
       <c r="K24" s="24"/>
       <c r="L24" s="24"/>
@@ -5885,7 +5866,7 @@
       <c r="F25" s="24"/>
       <c r="G25" s="24"/>
       <c r="H25" s="24"/>
-      <c r="I25" s="25"/>
+      <c r="I25" s="24"/>
       <c r="J25" s="24"/>
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
@@ -5906,7 +5887,7 @@
       <c r="F26" s="24"/>
       <c r="G26" s="24"/>
       <c r="H26" s="24"/>
-      <c r="I26" s="25"/>
+      <c r="I26" s="24"/>
       <c r="J26" s="24"/>
       <c r="K26" s="24"/>
       <c r="L26" s="24"/>
@@ -5927,7 +5908,7 @@
       <c r="F27" s="24"/>
       <c r="G27" s="24"/>
       <c r="H27" s="24"/>
-      <c r="I27" s="25"/>
+      <c r="I27" s="24"/>
       <c r="J27" s="24"/>
       <c r="K27" s="24"/>
       <c r="L27" s="24"/>
@@ -5948,7 +5929,7 @@
       <c r="F28" s="24"/>
       <c r="G28" s="24"/>
       <c r="H28" s="24"/>
-      <c r="I28" s="25"/>
+      <c r="I28" s="24"/>
       <c r="J28" s="24"/>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -5969,7 +5950,7 @@
       <c r="F29" s="24"/>
       <c r="G29" s="24"/>
       <c r="H29" s="24"/>
-      <c r="I29" s="25"/>
+      <c r="I29" s="24"/>
       <c r="J29" s="24"/>
       <c r="K29" s="24"/>
       <c r="L29" s="24"/>
@@ -5990,7 +5971,7 @@
       <c r="F30" s="24"/>
       <c r="G30" s="24"/>
       <c r="H30" s="24"/>
-      <c r="I30" s="25"/>
+      <c r="I30" s="24"/>
       <c r="J30" s="24"/>
       <c r="K30" s="24"/>
       <c r="L30" s="24"/>
@@ -6011,7 +5992,7 @@
       <c r="F31" s="24"/>
       <c r="G31" s="24"/>
       <c r="H31" s="24"/>
-      <c r="I31" s="25"/>
+      <c r="I31" s="24"/>
       <c r="J31" s="24"/>
       <c r="K31" s="24"/>
       <c r="L31" s="24"/>
@@ -6032,7 +6013,7 @@
       <c r="F32" s="24"/>
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
-      <c r="I32" s="25"/>
+      <c r="I32" s="24"/>
       <c r="J32" s="24"/>
       <c r="K32" s="24"/>
       <c r="L32" s="24"/>
@@ -6053,7 +6034,7 @@
       <c r="F33" s="24"/>
       <c r="G33" s="24"/>
       <c r="H33" s="24"/>
-      <c r="I33" s="25"/>
+      <c r="I33" s="24"/>
       <c r="J33" s="24"/>
       <c r="K33" s="24"/>
       <c r="L33" s="24"/>
@@ -6074,7 +6055,7 @@
       <c r="F34" s="24"/>
       <c r="G34" s="24"/>
       <c r="H34" s="24"/>
-      <c r="I34" s="25"/>
+      <c r="I34" s="24"/>
       <c r="J34" s="24"/>
       <c r="K34" s="24"/>
       <c r="L34" s="24"/>
@@ -6095,7 +6076,7 @@
       <c r="F35" s="24"/>
       <c r="G35" s="24"/>
       <c r="H35" s="24"/>
-      <c r="I35" s="25"/>
+      <c r="I35" s="24"/>
       <c r="J35" s="24"/>
       <c r="K35" s="24"/>
       <c r="L35" s="24"/>
@@ -6116,7 +6097,7 @@
       <c r="F36" s="24"/>
       <c r="G36" s="24"/>
       <c r="H36" s="24"/>
-      <c r="I36" s="25"/>
+      <c r="I36" s="24"/>
       <c r="J36" s="24"/>
       <c r="K36" s="24"/>
       <c r="L36" s="24"/>
@@ -6137,7 +6118,7 @@
       <c r="F37" s="24"/>
       <c r="G37" s="24"/>
       <c r="H37" s="24"/>
-      <c r="I37" s="25"/>
+      <c r="I37" s="24"/>
       <c r="J37" s="24"/>
       <c r="K37" s="24"/>
       <c r="L37" s="24"/>
@@ -6158,7 +6139,7 @@
       <c r="F38" s="24"/>
       <c r="G38" s="24"/>
       <c r="H38" s="24"/>
-      <c r="I38" s="25"/>
+      <c r="I38" s="24"/>
       <c r="J38" s="24"/>
       <c r="K38" s="24"/>
       <c r="L38" s="24"/>
@@ -6179,7 +6160,7 @@
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
       <c r="H39" s="24"/>
-      <c r="I39" s="25"/>
+      <c r="I39" s="24"/>
       <c r="J39" s="24"/>
       <c r="K39" s="24"/>
       <c r="L39" s="24"/>
@@ -6200,7 +6181,7 @@
       <c r="F40" s="24"/>
       <c r="G40" s="24"/>
       <c r="H40" s="24"/>
-      <c r="I40" s="25"/>
+      <c r="I40" s="24"/>
       <c r="J40" s="24"/>
       <c r="K40" s="24"/>
       <c r="L40" s="24"/>
@@ -6221,7 +6202,7 @@
       <c r="F41" s="24"/>
       <c r="G41" s="24"/>
       <c r="H41" s="24"/>
-      <c r="I41" s="25"/>
+      <c r="I41" s="24"/>
       <c r="J41" s="24"/>
       <c r="K41" s="24"/>
       <c r="L41" s="24"/>
@@ -6242,7 +6223,7 @@
       <c r="F42" s="24"/>
       <c r="G42" s="24"/>
       <c r="H42" s="24"/>
-      <c r="I42" s="25"/>
+      <c r="I42" s="24"/>
       <c r="J42" s="24"/>
       <c r="K42" s="24"/>
       <c r="L42" s="24"/>
@@ -6263,7 +6244,7 @@
       <c r="F43" s="24"/>
       <c r="G43" s="24"/>
       <c r="H43" s="24"/>
-      <c r="I43" s="25"/>
+      <c r="I43" s="24"/>
       <c r="J43" s="24"/>
       <c r="K43" s="24"/>
       <c r="L43" s="24"/>
@@ -6284,7 +6265,7 @@
       <c r="F44" s="24"/>
       <c r="G44" s="24"/>
       <c r="H44" s="24"/>
-      <c r="I44" s="25"/>
+      <c r="I44" s="24"/>
       <c r="J44" s="24"/>
       <c r="K44" s="24"/>
       <c r="L44" s="24"/>
@@ -6305,7 +6286,7 @@
       <c r="F45" s="24"/>
       <c r="G45" s="24"/>
       <c r="H45" s="24"/>
-      <c r="I45" s="25"/>
+      <c r="I45" s="24"/>
       <c r="J45" s="24"/>
       <c r="K45" s="24"/>
       <c r="L45" s="24"/>
@@ -6326,7 +6307,7 @@
       <c r="F46" s="24"/>
       <c r="G46" s="24"/>
       <c r="H46" s="24"/>
-      <c r="I46" s="25"/>
+      <c r="I46" s="24"/>
       <c r="J46" s="24"/>
       <c r="K46" s="24"/>
       <c r="L46" s="24"/>
@@ -6347,7 +6328,7 @@
       <c r="F47" s="24"/>
       <c r="G47" s="24"/>
       <c r="H47" s="24"/>
-      <c r="I47" s="25"/>
+      <c r="I47" s="24"/>
       <c r="J47" s="24"/>
       <c r="K47" s="24"/>
       <c r="L47" s="24"/>
@@ -6368,7 +6349,7 @@
       <c r="F48" s="24"/>
       <c r="G48" s="24"/>
       <c r="H48" s="24"/>
-      <c r="I48" s="25"/>
+      <c r="I48" s="24"/>
       <c r="J48" s="24"/>
       <c r="K48" s="24"/>
       <c r="L48" s="24"/>
@@ -6389,7 +6370,7 @@
       <c r="F49" s="24"/>
       <c r="G49" s="24"/>
       <c r="H49" s="24"/>
-      <c r="I49" s="25"/>
+      <c r="I49" s="24"/>
       <c r="J49" s="24"/>
       <c r="K49" s="24"/>
       <c r="L49" s="24"/>
@@ -6410,7 +6391,7 @@
       <c r="F50" s="24"/>
       <c r="G50" s="24"/>
       <c r="H50" s="24"/>
-      <c r="I50" s="25"/>
+      <c r="I50" s="24"/>
       <c r="J50" s="24"/>
       <c r="K50" s="24"/>
       <c r="L50" s="24"/>
@@ -6431,7 +6412,7 @@
       <c r="F51" s="24"/>
       <c r="G51" s="24"/>
       <c r="H51" s="24"/>
-      <c r="I51" s="25"/>
+      <c r="I51" s="24"/>
       <c r="J51" s="24"/>
       <c r="K51" s="24"/>
       <c r="L51" s="24"/>
@@ -6452,7 +6433,7 @@
       <c r="F52" s="24"/>
       <c r="G52" s="24"/>
       <c r="H52" s="24"/>
-      <c r="I52" s="25"/>
+      <c r="I52" s="24"/>
       <c r="J52" s="24"/>
       <c r="K52" s="24"/>
       <c r="L52" s="24"/>
@@ -6473,7 +6454,7 @@
       <c r="F53" s="24"/>
       <c r="G53" s="24"/>
       <c r="H53" s="24"/>
-      <c r="I53" s="25"/>
+      <c r="I53" s="24"/>
       <c r="J53" s="24"/>
       <c r="K53" s="24"/>
       <c r="L53" s="24"/>
@@ -6494,7 +6475,7 @@
       <c r="F54" s="24"/>
       <c r="G54" s="24"/>
       <c r="H54" s="24"/>
-      <c r="I54" s="25"/>
+      <c r="I54" s="24"/>
       <c r="J54" s="24"/>
       <c r="K54" s="24"/>
       <c r="L54" s="24"/>
@@ -6515,7 +6496,7 @@
       <c r="F55" s="24"/>
       <c r="G55" s="24"/>
       <c r="H55" s="24"/>
-      <c r="I55" s="25"/>
+      <c r="I55" s="24"/>
       <c r="J55" s="24"/>
       <c r="K55" s="24"/>
       <c r="L55" s="24"/>
@@ -6536,7 +6517,7 @@
       <c r="F56" s="24"/>
       <c r="G56" s="24"/>
       <c r="H56" s="24"/>
-      <c r="I56" s="25"/>
+      <c r="I56" s="24"/>
       <c r="J56" s="24"/>
       <c r="K56" s="24"/>
       <c r="L56" s="24"/>
@@ -6545,8 +6526,8 @@
       <c r="O56" s="24"/>
       <c r="P56" s="24"/>
       <c r="Q56" s="24"/>
-      <c r="R56"/>
-      <c r="S56"/>
+      <c r="R56" s="25"/>
+      <c r="S56" s="25"/>
     </row>
     <row r="57" ht="17.55" spans="1:19">
       <c r="A57" s="24"/>
@@ -6557,7 +6538,7 @@
       <c r="F57" s="24"/>
       <c r="G57" s="24"/>
       <c r="H57" s="24"/>
-      <c r="I57" s="25"/>
+      <c r="I57" s="24"/>
       <c r="J57" s="24"/>
       <c r="K57" s="24"/>
       <c r="L57" s="24"/>
@@ -6578,7 +6559,7 @@
       <c r="F58" s="24"/>
       <c r="G58" s="24"/>
       <c r="H58" s="24"/>
-      <c r="I58" s="25"/>
+      <c r="I58" s="24"/>
       <c r="J58" s="24"/>
       <c r="K58" s="24"/>
       <c r="L58" s="24"/>
@@ -6599,7 +6580,7 @@
       <c r="F59" s="24"/>
       <c r="G59" s="24"/>
       <c r="H59" s="24"/>
-      <c r="I59" s="25"/>
+      <c r="I59" s="24"/>
       <c r="J59" s="24"/>
       <c r="K59" s="24"/>
       <c r="L59" s="24"/>
@@ -6620,7 +6601,7 @@
       <c r="F60" s="24"/>
       <c r="G60" s="24"/>
       <c r="H60" s="24"/>
-      <c r="I60" s="25"/>
+      <c r="I60" s="24"/>
       <c r="J60" s="24"/>
       <c r="K60" s="24"/>
       <c r="L60" s="24"/>
@@ -6641,7 +6622,7 @@
       <c r="F61" s="24"/>
       <c r="G61" s="24"/>
       <c r="H61" s="24"/>
-      <c r="I61" s="25"/>
+      <c r="I61" s="24"/>
       <c r="J61" s="24"/>
       <c r="K61" s="24"/>
       <c r="L61" s="24"/>
@@ -6662,7 +6643,7 @@
       <c r="F62" s="24"/>
       <c r="G62" s="24"/>
       <c r="H62" s="24"/>
-      <c r="I62" s="25"/>
+      <c r="I62" s="24"/>
       <c r="J62" s="24"/>
       <c r="K62" s="24"/>
       <c r="L62" s="24"/>
@@ -6683,7 +6664,7 @@
       <c r="F63" s="24"/>
       <c r="G63" s="24"/>
       <c r="H63" s="24"/>
-      <c r="I63" s="25"/>
+      <c r="I63" s="24"/>
       <c r="J63" s="24"/>
       <c r="K63" s="24"/>
       <c r="L63" s="24"/>
@@ -6704,7 +6685,7 @@
       <c r="F64" s="24"/>
       <c r="G64" s="24"/>
       <c r="H64" s="24"/>
-      <c r="I64" s="25"/>
+      <c r="I64" s="24"/>
       <c r="J64" s="24"/>
       <c r="K64" s="24"/>
       <c r="L64" s="24"/>
@@ -6713,8 +6694,8 @@
       <c r="O64" s="24"/>
       <c r="P64" s="24"/>
       <c r="Q64" s="24"/>
-      <c r="R64"/>
-      <c r="S64"/>
+      <c r="R64" s="25"/>
+      <c r="S64" s="25"/>
     </row>
     <row r="65" ht="17.55" spans="1:19">
       <c r="A65" s="24"/>
@@ -6725,7 +6706,7 @@
       <c r="F65" s="24"/>
       <c r="G65" s="24"/>
       <c r="H65" s="24"/>
-      <c r="I65" s="25"/>
+      <c r="I65" s="24"/>
       <c r="J65" s="24"/>
       <c r="K65" s="24"/>
       <c r="L65" s="24"/>
@@ -6746,7 +6727,7 @@
       <c r="F66" s="24"/>
       <c r="G66" s="24"/>
       <c r="H66" s="24"/>
-      <c r="I66" s="25"/>
+      <c r="I66" s="24"/>
       <c r="J66" s="24"/>
       <c r="K66" s="24"/>
       <c r="L66" s="24"/>
@@ -6767,7 +6748,7 @@
       <c r="F67" s="24"/>
       <c r="G67" s="24"/>
       <c r="H67" s="24"/>
-      <c r="I67" s="25"/>
+      <c r="I67" s="24"/>
       <c r="J67" s="24"/>
       <c r="K67" s="24"/>
       <c r="L67" s="24"/>
@@ -6788,7 +6769,7 @@
       <c r="F68" s="24"/>
       <c r="G68" s="24"/>
       <c r="H68" s="24"/>
-      <c r="I68" s="25"/>
+      <c r="I68" s="24"/>
       <c r="J68" s="24"/>
       <c r="K68" s="24"/>
       <c r="L68" s="24"/>
@@ -6809,7 +6790,7 @@
       <c r="F69" s="24"/>
       <c r="G69" s="24"/>
       <c r="H69" s="24"/>
-      <c r="I69" s="25"/>
+      <c r="I69" s="24"/>
       <c r="J69" s="24"/>
       <c r="K69" s="24"/>
       <c r="L69" s="24"/>
@@ -6830,7 +6811,7 @@
       <c r="F70" s="24"/>
       <c r="G70" s="24"/>
       <c r="H70" s="24"/>
-      <c r="I70" s="25"/>
+      <c r="I70" s="24"/>
       <c r="J70" s="24"/>
       <c r="K70" s="24"/>
       <c r="L70" s="24"/>
@@ -6851,7 +6832,7 @@
       <c r="F71" s="24"/>
       <c r="G71" s="24"/>
       <c r="H71" s="24"/>
-      <c r="I71" s="25"/>
+      <c r="I71" s="24"/>
       <c r="J71" s="24"/>
       <c r="K71" s="24"/>
       <c r="L71" s="24"/>
@@ -6872,7 +6853,7 @@
       <c r="F72" s="24"/>
       <c r="G72" s="24"/>
       <c r="H72" s="24"/>
-      <c r="I72" s="25"/>
+      <c r="I72" s="24"/>
       <c r="J72" s="24"/>
       <c r="K72" s="24"/>
       <c r="L72" s="24"/>
@@ -6893,7 +6874,7 @@
       <c r="F73" s="24"/>
       <c r="G73" s="24"/>
       <c r="H73" s="24"/>
-      <c r="I73" s="25"/>
+      <c r="I73" s="24"/>
       <c r="J73" s="24"/>
       <c r="K73" s="24"/>
       <c r="L73" s="24"/>
@@ -6914,7 +6895,7 @@
       <c r="F74" s="24"/>
       <c r="G74" s="24"/>
       <c r="H74" s="24"/>
-      <c r="I74" s="25"/>
+      <c r="I74" s="24"/>
       <c r="J74" s="24"/>
       <c r="K74" s="24"/>
       <c r="L74" s="24"/>
@@ -6935,7 +6916,7 @@
       <c r="F75" s="24"/>
       <c r="G75" s="24"/>
       <c r="H75" s="24"/>
-      <c r="I75" s="25"/>
+      <c r="I75" s="24"/>
       <c r="J75" s="24"/>
       <c r="K75" s="24"/>
       <c r="L75" s="24"/>
@@ -6956,7 +6937,7 @@
       <c r="F76" s="24"/>
       <c r="G76" s="24"/>
       <c r="H76" s="24"/>
-      <c r="I76" s="25"/>
+      <c r="I76" s="24"/>
       <c r="J76" s="24"/>
       <c r="K76" s="24"/>
       <c r="L76" s="24"/>
@@ -6977,7 +6958,7 @@
       <c r="F77" s="24"/>
       <c r="G77" s="24"/>
       <c r="H77" s="24"/>
-      <c r="I77" s="25"/>
+      <c r="I77" s="24"/>
       <c r="J77" s="24"/>
       <c r="K77" s="24"/>
       <c r="L77" s="24"/>
@@ -6998,7 +6979,7 @@
       <c r="F78" s="24"/>
       <c r="G78" s="24"/>
       <c r="H78" s="24"/>
-      <c r="I78" s="25"/>
+      <c r="I78" s="24"/>
       <c r="J78" s="24"/>
       <c r="K78" s="24"/>
       <c r="L78" s="24"/>
@@ -7019,7 +7000,7 @@
       <c r="F79" s="24"/>
       <c r="G79" s="24"/>
       <c r="H79" s="24"/>
-      <c r="I79" s="25"/>
+      <c r="I79" s="24"/>
       <c r="J79" s="24"/>
       <c r="K79" s="24"/>
       <c r="L79" s="24"/>
@@ -7040,7 +7021,7 @@
       <c r="F80" s="24"/>
       <c r="G80" s="24"/>
       <c r="H80" s="24"/>
-      <c r="I80" s="25"/>
+      <c r="I80" s="24"/>
       <c r="J80" s="24"/>
       <c r="K80" s="24"/>
       <c r="L80" s="24"/>
@@ -7061,7 +7042,7 @@
       <c r="F81" s="24"/>
       <c r="G81" s="24"/>
       <c r="H81" s="24"/>
-      <c r="I81" s="25"/>
+      <c r="I81" s="24"/>
       <c r="J81" s="24"/>
       <c r="K81" s="24"/>
       <c r="L81" s="24"/>
@@ -7082,7 +7063,7 @@
       <c r="F82" s="24"/>
       <c r="G82" s="24"/>
       <c r="H82" s="24"/>
-      <c r="I82" s="25"/>
+      <c r="I82" s="24"/>
       <c r="J82" s="24"/>
       <c r="K82" s="24"/>
       <c r="L82" s="24"/>
@@ -7103,7 +7084,7 @@
       <c r="F83" s="24"/>
       <c r="G83" s="24"/>
       <c r="H83" s="24"/>
-      <c r="I83" s="25"/>
+      <c r="I83" s="24"/>
       <c r="J83" s="24"/>
       <c r="K83" s="24"/>
       <c r="L83" s="24"/>
@@ -7112,8 +7093,8 @@
       <c r="O83" s="24"/>
       <c r="P83" s="24"/>
       <c r="Q83" s="24"/>
-      <c r="R83"/>
-      <c r="S83"/>
+      <c r="R83" s="25"/>
+      <c r="S83" s="25"/>
     </row>
   </sheetData>
   <sortState ref="A2:S52">
@@ -7265,7 +7246,7 @@
       </c>
       <c r="R2" s="21">
         <f ca="1">TODAY()</f>
-        <v>46032</v>
+        <v>46067</v>
       </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
@@ -17146,7 +17127,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="str">
         <f ca="1">TEXT(TODAY(),"yyyy年m月")</f>
-        <v>2026年1月</v>
+        <v>2026年2月</v>
       </c>
       <c r="F1" s="3"/>
     </row>

--- a/hema/3-单袋比.xlsx
+++ b/hema/3-单袋比.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="32000" windowHeight="17120" activeTab="1"/>
+    <workbookView windowHeight="17120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="盘点表" sheetId="2" r:id="rId1"/>
@@ -1871,7 +1871,7 @@
     <row r="1" spans="1:12">
       <c r="A1" s="41">
         <f ca="1">TODAY()</f>
-        <v>46067</v>
+        <v>46120</v>
       </c>
       <c r="B1" s="41"/>
       <c r="C1" s="41"/>
@@ -2514,7 +2514,7 @@
     <col min="12" max="16384" width="110.714285714286" style="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.55" spans="1:11">
+    <row r="1" spans="1:11">
       <c r="A1" s="26"/>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -2527,7 +2527,7 @@
       <c r="J1" s="26"/>
       <c r="K1" s="26"/>
     </row>
-    <row r="2" ht="17.55" spans="1:11">
+    <row r="2" spans="1:11">
       <c r="A2" s="27"/>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -2540,7 +2540,7 @@
       <c r="J2" s="27"/>
       <c r="K2" s="27"/>
     </row>
-    <row r="3" ht="17.55" spans="1:11">
+    <row r="3" spans="1:11">
       <c r="A3" s="30"/>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -2553,7 +2553,7 @@
       <c r="J3" s="30"/>
       <c r="K3" s="30"/>
     </row>
-    <row r="4" ht="17.55" spans="1:11">
+    <row r="4" spans="1:11">
       <c r="A4" s="30"/>
       <c r="B4" s="30"/>
       <c r="C4" s="30"/>
@@ -2566,7 +2566,7 @@
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
     </row>
-    <row r="5" ht="17.55" spans="1:11">
+    <row r="5" spans="1:11">
       <c r="A5" s="30"/>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -2579,7 +2579,7 @@
       <c r="J5" s="30"/>
       <c r="K5" s="30"/>
     </row>
-    <row r="6" ht="17.55" spans="1:11">
+    <row r="6" spans="1:11">
       <c r="A6" s="30"/>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -2592,7 +2592,7 @@
       <c r="J6" s="30"/>
       <c r="K6" s="30"/>
     </row>
-    <row r="7" ht="17.55" spans="1:11">
+    <row r="7" spans="1:11">
       <c r="A7" s="30"/>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -2605,7 +2605,7 @@
       <c r="J7" s="30"/>
       <c r="K7" s="30"/>
     </row>
-    <row r="8" ht="17.55" spans="1:11">
+    <row r="8" spans="1:11">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
@@ -2618,7 +2618,7 @@
       <c r="J8" s="30"/>
       <c r="K8" s="30"/>
     </row>
-    <row r="9" ht="17.55" spans="1:11">
+    <row r="9" spans="1:11">
       <c r="A9" s="30"/>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
@@ -2631,7 +2631,7 @@
       <c r="J9" s="30"/>
       <c r="K9" s="30"/>
     </row>
-    <row r="10" ht="17.55" spans="1:11">
+    <row r="10" spans="1:11">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -2644,7 +2644,7 @@
       <c r="J10" s="30"/>
       <c r="K10" s="30"/>
     </row>
-    <row r="11" ht="17.55" spans="1:11">
+    <row r="11" spans="1:11">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -2657,7 +2657,7 @@
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
     </row>
-    <row r="12" ht="17.55" spans="1:11">
+    <row r="12" spans="1:11">
       <c r="A12" s="30"/>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -2670,7 +2670,7 @@
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
     </row>
-    <row r="13" ht="17.55" spans="1:11">
+    <row r="13" spans="1:11">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -2683,7 +2683,7 @@
       <c r="J13" s="30"/>
       <c r="K13" s="30"/>
     </row>
-    <row r="14" ht="17.55" spans="1:11">
+    <row r="14" spans="1:11">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -2696,7 +2696,7 @@
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
     </row>
-    <row r="15" ht="17.55" spans="1:11">
+    <row r="15" spans="1:11">
       <c r="A15" s="30"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
@@ -2709,7 +2709,7 @@
       <c r="J15" s="30"/>
       <c r="K15" s="30"/>
     </row>
-    <row r="16" ht="17.55" spans="1:11">
+    <row r="16" spans="1:11">
       <c r="A16" s="30"/>
       <c r="B16" s="30"/>
       <c r="C16" s="30"/>
@@ -2722,7 +2722,7 @@
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
     </row>
-    <row r="17" ht="17.55" spans="1:11">
+    <row r="17" spans="1:11">
       <c r="A17" s="30"/>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
@@ -2735,7 +2735,7 @@
       <c r="J17" s="30"/>
       <c r="K17" s="30"/>
     </row>
-    <row r="18" ht="17.55" spans="1:11">
+    <row r="18" spans="1:11">
       <c r="A18" s="30"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
@@ -2748,7 +2748,7 @@
       <c r="J18" s="30"/>
       <c r="K18" s="30"/>
     </row>
-    <row r="19" ht="17.55" spans="1:11">
+    <row r="19" spans="1:11">
       <c r="A19" s="30"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -2761,7 +2761,7 @@
       <c r="J19" s="30"/>
       <c r="K19" s="30"/>
     </row>
-    <row r="20" ht="17.55" spans="1:11">
+    <row r="20" spans="1:11">
       <c r="A20" s="30"/>
       <c r="B20" s="30"/>
       <c r="C20" s="30"/>
@@ -2774,7 +2774,7 @@
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
     </row>
-    <row r="21" ht="17.55" spans="1:11">
+    <row r="21" spans="1:11">
       <c r="A21" s="30"/>
       <c r="B21" s="30"/>
       <c r="C21" s="30"/>
@@ -2787,7 +2787,7 @@
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
     </row>
-    <row r="22" ht="17.55" spans="1:11">
+    <row r="22" spans="1:11">
       <c r="A22" s="30"/>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
@@ -2800,7 +2800,7 @@
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
     </row>
-    <row r="23" ht="17.55" spans="1:11">
+    <row r="23" spans="1:11">
       <c r="A23" s="30"/>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
@@ -2813,7 +2813,7 @@
       <c r="J23" s="30"/>
       <c r="K23" s="30"/>
     </row>
-    <row r="24" ht="17.55" spans="1:11">
+    <row r="24" spans="1:11">
       <c r="A24" s="30"/>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
@@ -2826,7 +2826,7 @@
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
     </row>
-    <row r="25" ht="17.55" spans="1:11">
+    <row r="25" spans="1:11">
       <c r="A25" s="30"/>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
@@ -2839,7 +2839,7 @@
       <c r="J25" s="30"/>
       <c r="K25" s="30"/>
     </row>
-    <row r="26" ht="17.55" spans="1:11">
+    <row r="26" spans="1:11">
       <c r="A26" s="30"/>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
@@ -2852,7 +2852,7 @@
       <c r="J26" s="30"/>
       <c r="K26" s="30"/>
     </row>
-    <row r="27" ht="17.55" spans="1:11">
+    <row r="27" spans="1:11">
       <c r="A27" s="30"/>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -2865,7 +2865,7 @@
       <c r="J27" s="30"/>
       <c r="K27" s="30"/>
     </row>
-    <row r="28" ht="17.55" spans="1:11">
+    <row r="28" spans="1:11">
       <c r="A28" s="30"/>
       <c r="B28" s="30"/>
       <c r="C28" s="30"/>
@@ -2878,7 +2878,7 @@
       <c r="J28" s="30"/>
       <c r="K28" s="30"/>
     </row>
-    <row r="29" ht="17.55" spans="1:11">
+    <row r="29" spans="1:11">
       <c r="A29" s="30"/>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
@@ -2891,7 +2891,7 @@
       <c r="J29" s="30"/>
       <c r="K29" s="30"/>
     </row>
-    <row r="30" ht="17.55" spans="1:11">
+    <row r="30" spans="1:11">
       <c r="A30" s="30"/>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
@@ -2904,7 +2904,7 @@
       <c r="J30" s="30"/>
       <c r="K30" s="30"/>
     </row>
-    <row r="31" ht="17.55" spans="1:11">
+    <row r="31" spans="1:11">
       <c r="A31" s="30"/>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
@@ -2917,7 +2917,7 @@
       <c r="J31" s="30"/>
       <c r="K31" s="30"/>
     </row>
-    <row r="32" ht="17.55" spans="1:11">
+    <row r="32" spans="1:11">
       <c r="A32" s="30"/>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
@@ -2930,7 +2930,7 @@
       <c r="J32" s="30"/>
       <c r="K32" s="30"/>
     </row>
-    <row r="33" ht="17.55" spans="1:11">
+    <row r="33" spans="1:11">
       <c r="A33" s="30"/>
       <c r="B33" s="30"/>
       <c r="C33" s="30"/>
@@ -2943,7 +2943,7 @@
       <c r="J33" s="30"/>
       <c r="K33" s="30"/>
     </row>
-    <row r="34" ht="17.55" spans="1:11">
+    <row r="34" spans="1:11">
       <c r="A34" s="30"/>
       <c r="B34" s="30"/>
       <c r="C34" s="30"/>
@@ -2956,7 +2956,7 @@
       <c r="J34" s="30"/>
       <c r="K34" s="30"/>
     </row>
-    <row r="35" ht="17.55" spans="1:11">
+    <row r="35" spans="1:11">
       <c r="A35" s="30"/>
       <c r="B35" s="30"/>
       <c r="C35" s="30"/>
@@ -2969,7 +2969,7 @@
       <c r="J35" s="30"/>
       <c r="K35" s="30"/>
     </row>
-    <row r="36" ht="17.55" spans="1:11">
+    <row r="36" spans="1:11">
       <c r="A36" s="30"/>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
@@ -2982,7 +2982,7 @@
       <c r="J36" s="30"/>
       <c r="K36" s="30"/>
     </row>
-    <row r="37" ht="17.55" spans="1:11">
+    <row r="37" spans="1:11">
       <c r="A37" s="30"/>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
@@ -2995,7 +2995,7 @@
       <c r="J37" s="30"/>
       <c r="K37" s="30"/>
     </row>
-    <row r="38" ht="17.55" spans="1:11">
+    <row r="38" spans="1:11">
       <c r="A38" s="30"/>
       <c r="B38" s="30"/>
       <c r="C38" s="30"/>
@@ -3008,7 +3008,7 @@
       <c r="J38" s="30"/>
       <c r="K38" s="30"/>
     </row>
-    <row r="39" ht="17.55" spans="1:11">
+    <row r="39" spans="1:11">
       <c r="A39" s="30"/>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
@@ -3021,7 +3021,7 @@
       <c r="J39" s="30"/>
       <c r="K39" s="30"/>
     </row>
-    <row r="40" ht="17.55" spans="1:11">
+    <row r="40" spans="1:11">
       <c r="A40" s="30"/>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
@@ -3034,7 +3034,7 @@
       <c r="J40" s="30"/>
       <c r="K40" s="30"/>
     </row>
-    <row r="41" ht="17.55" spans="1:11">
+    <row r="41" spans="1:11">
       <c r="A41" s="30"/>
       <c r="B41" s="30"/>
       <c r="C41" s="30"/>
@@ -3047,7 +3047,7 @@
       <c r="J41" s="30"/>
       <c r="K41" s="30"/>
     </row>
-    <row r="42" ht="17.55" spans="1:11">
+    <row r="42" spans="1:11">
       <c r="A42" s="30"/>
       <c r="B42" s="30"/>
       <c r="C42" s="30"/>
@@ -3060,7 +3060,7 @@
       <c r="J42" s="30"/>
       <c r="K42" s="30"/>
     </row>
-    <row r="43" ht="17.55" spans="1:11">
+    <row r="43" spans="1:11">
       <c r="A43" s="30"/>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
@@ -3073,7 +3073,7 @@
       <c r="J43" s="30"/>
       <c r="K43" s="30"/>
     </row>
-    <row r="44" ht="17.55" spans="1:11">
+    <row r="44" spans="1:11">
       <c r="A44" s="30"/>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
@@ -3086,7 +3086,7 @@
       <c r="J44" s="30"/>
       <c r="K44" s="30"/>
     </row>
-    <row r="45" ht="17.55" spans="1:11">
+    <row r="45" spans="1:11">
       <c r="A45" s="30"/>
       <c r="B45" s="30"/>
       <c r="C45" s="30"/>
@@ -3099,7 +3099,7 @@
       <c r="J45" s="30"/>
       <c r="K45" s="30"/>
     </row>
-    <row r="46" ht="17.55" spans="1:11">
+    <row r="46" spans="1:11">
       <c r="A46" s="30"/>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
@@ -3112,7 +3112,7 @@
       <c r="J46" s="30"/>
       <c r="K46" s="30"/>
     </row>
-    <row r="47" ht="17.55" spans="1:11">
+    <row r="47" spans="1:11">
       <c r="A47" s="30"/>
       <c r="B47" s="30"/>
       <c r="C47" s="30"/>
@@ -3125,7 +3125,7 @@
       <c r="J47" s="30"/>
       <c r="K47" s="30"/>
     </row>
-    <row r="48" ht="17.55" spans="1:11">
+    <row r="48" spans="1:11">
       <c r="A48" s="30"/>
       <c r="B48" s="30"/>
       <c r="C48" s="30"/>
@@ -3138,7 +3138,7 @@
       <c r="J48" s="30"/>
       <c r="K48" s="30"/>
     </row>
-    <row r="49" ht="17.55" spans="1:11">
+    <row r="49" spans="1:11">
       <c r="A49" s="30"/>
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
@@ -3151,7 +3151,7 @@
       <c r="J49" s="30"/>
       <c r="K49" s="30"/>
     </row>
-    <row r="50" ht="17.55" spans="1:11">
+    <row r="50" spans="1:11">
       <c r="A50" s="30"/>
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
@@ -3164,7 +3164,7 @@
       <c r="J50" s="30"/>
       <c r="K50" s="30"/>
     </row>
-    <row r="51" ht="17.55" spans="1:11">
+    <row r="51" spans="1:11">
       <c r="A51" s="30"/>
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
@@ -3177,7 +3177,7 @@
       <c r="J51" s="30"/>
       <c r="K51" s="30"/>
     </row>
-    <row r="52" ht="17.55" spans="1:11">
+    <row r="52" spans="1:11">
       <c r="A52" s="30"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
@@ -3190,7 +3190,7 @@
       <c r="J52" s="30"/>
       <c r="K52" s="30"/>
     </row>
-    <row r="53" ht="17.55" spans="1:11">
+    <row r="53" spans="1:11">
       <c r="A53" s="30"/>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
@@ -3203,7 +3203,7 @@
       <c r="J53" s="30"/>
       <c r="K53" s="30"/>
     </row>
-    <row r="54" ht="17.55" spans="1:11">
+    <row r="54" spans="1:11">
       <c r="A54" s="30"/>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
@@ -3216,7 +3216,7 @@
       <c r="J54" s="30"/>
       <c r="K54" s="30"/>
     </row>
-    <row r="55" ht="17.55" spans="1:11">
+    <row r="55" spans="1:11">
       <c r="A55" s="30"/>
       <c r="B55" s="30"/>
       <c r="C55" s="30"/>
@@ -3229,7 +3229,7 @@
       <c r="J55" s="30"/>
       <c r="K55" s="30"/>
     </row>
-    <row r="56" ht="17.55" spans="1:11">
+    <row r="56" spans="1:11">
       <c r="A56" s="30"/>
       <c r="B56" s="30"/>
       <c r="C56" s="30"/>
@@ -3242,7 +3242,7 @@
       <c r="J56" s="30"/>
       <c r="K56" s="30"/>
     </row>
-    <row r="57" ht="17.55" spans="1:11">
+    <row r="57" spans="1:11">
       <c r="A57" s="30"/>
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
@@ -3255,7 +3255,7 @@
       <c r="J57" s="30"/>
       <c r="K57" s="30"/>
     </row>
-    <row r="58" ht="17.55" spans="1:11">
+    <row r="58" spans="1:11">
       <c r="A58" s="30"/>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
@@ -3268,7 +3268,7 @@
       <c r="J58" s="30"/>
       <c r="K58" s="30"/>
     </row>
-    <row r="59" ht="17.55" spans="1:11">
+    <row r="59" spans="1:11">
       <c r="A59" s="30"/>
       <c r="B59" s="30"/>
       <c r="C59" s="30"/>
@@ -3281,7 +3281,7 @@
       <c r="J59" s="30"/>
       <c r="K59" s="30"/>
     </row>
-    <row r="60" ht="17.55" spans="1:11">
+    <row r="60" spans="1:11">
       <c r="A60" s="30"/>
       <c r="B60" s="30"/>
       <c r="C60" s="30"/>
@@ -3294,7 +3294,7 @@
       <c r="J60" s="30"/>
       <c r="K60" s="30"/>
     </row>
-    <row r="61" ht="17.55" spans="1:11">
+    <row r="61" spans="1:11">
       <c r="A61" s="30"/>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
@@ -3307,7 +3307,7 @@
       <c r="J61" s="30"/>
       <c r="K61" s="30"/>
     </row>
-    <row r="62" ht="17.55" spans="1:11">
+    <row r="62" spans="1:11">
       <c r="A62" s="30"/>
       <c r="B62" s="30"/>
       <c r="C62" s="30"/>
@@ -3320,7 +3320,7 @@
       <c r="J62" s="30"/>
       <c r="K62" s="30"/>
     </row>
-    <row r="63" ht="17.55" spans="1:11">
+    <row r="63" spans="1:11">
       <c r="A63" s="30"/>
       <c r="B63" s="30"/>
       <c r="C63" s="30"/>
@@ -3333,7 +3333,7 @@
       <c r="J63" s="30"/>
       <c r="K63" s="30"/>
     </row>
-    <row r="64" ht="17.55" spans="1:11">
+    <row r="64" spans="1:11">
       <c r="A64" s="30"/>
       <c r="B64" s="30"/>
       <c r="C64" s="30"/>
@@ -3346,7 +3346,7 @@
       <c r="J64" s="30"/>
       <c r="K64" s="30"/>
     </row>
-    <row r="65" ht="17.55" spans="1:11">
+    <row r="65" spans="1:11">
       <c r="A65" s="30"/>
       <c r="B65" s="30"/>
       <c r="C65" s="30"/>
@@ -3359,7 +3359,7 @@
       <c r="J65" s="30"/>
       <c r="K65" s="30"/>
     </row>
-    <row r="66" ht="17.55" spans="1:11">
+    <row r="66" spans="1:11">
       <c r="A66" s="30"/>
       <c r="B66" s="30"/>
       <c r="C66" s="30"/>
@@ -3372,7 +3372,7 @@
       <c r="J66" s="30"/>
       <c r="K66" s="30"/>
     </row>
-    <row r="67" ht="17.55" spans="1:11">
+    <row r="67" spans="1:11">
       <c r="A67" s="30"/>
       <c r="B67" s="30"/>
       <c r="C67" s="30"/>
@@ -3385,7 +3385,7 @@
       <c r="J67" s="30"/>
       <c r="K67" s="30"/>
     </row>
-    <row r="68" ht="17.55" spans="1:11">
+    <row r="68" spans="1:11">
       <c r="A68" s="30"/>
       <c r="B68" s="30"/>
       <c r="C68" s="30"/>
@@ -3398,7 +3398,7 @@
       <c r="J68" s="30"/>
       <c r="K68" s="30"/>
     </row>
-    <row r="69" ht="17.55" spans="1:11">
+    <row r="69" spans="1:11">
       <c r="A69" s="30"/>
       <c r="B69" s="30"/>
       <c r="C69" s="30"/>
@@ -3411,7 +3411,7 @@
       <c r="J69" s="30"/>
       <c r="K69" s="30"/>
     </row>
-    <row r="70" ht="17.55" spans="1:11">
+    <row r="70" spans="1:11">
       <c r="A70" s="30"/>
       <c r="B70" s="30"/>
       <c r="C70" s="30"/>
@@ -3424,7 +3424,7 @@
       <c r="J70" s="30"/>
       <c r="K70" s="30"/>
     </row>
-    <row r="71" ht="17.55" spans="1:11">
+    <row r="71" spans="1:11">
       <c r="A71" s="30"/>
       <c r="B71" s="30"/>
       <c r="C71" s="30"/>
@@ -3437,7 +3437,7 @@
       <c r="J71" s="30"/>
       <c r="K71" s="30"/>
     </row>
-    <row r="72" ht="17.55" spans="1:11">
+    <row r="72" spans="1:11">
       <c r="A72" s="30"/>
       <c r="B72" s="30"/>
       <c r="C72" s="30"/>
@@ -3450,7 +3450,7 @@
       <c r="J72" s="30"/>
       <c r="K72" s="30"/>
     </row>
-    <row r="73" ht="17.55" spans="1:11">
+    <row r="73" spans="1:11">
       <c r="A73" s="30"/>
       <c r="B73" s="30"/>
       <c r="C73" s="30"/>
@@ -3463,7 +3463,7 @@
       <c r="J73" s="30"/>
       <c r="K73" s="30"/>
     </row>
-    <row r="74" ht="17.55" spans="1:11">
+    <row r="74" spans="1:11">
       <c r="A74" s="30"/>
       <c r="B74" s="30"/>
       <c r="C74" s="30"/>
@@ -3476,7 +3476,7 @@
       <c r="J74" s="30"/>
       <c r="K74" s="30"/>
     </row>
-    <row r="75" ht="17.55" spans="1:11">
+    <row r="75" spans="1:11">
       <c r="A75" s="30"/>
       <c r="B75" s="30"/>
       <c r="C75" s="30"/>
@@ -3489,7 +3489,7 @@
       <c r="J75" s="30"/>
       <c r="K75" s="30"/>
     </row>
-    <row r="76" ht="17.55" spans="1:11">
+    <row r="76" spans="1:11">
       <c r="A76" s="30"/>
       <c r="B76" s="30"/>
       <c r="C76" s="30"/>
@@ -3502,7 +3502,7 @@
       <c r="J76" s="30"/>
       <c r="K76" s="30"/>
     </row>
-    <row r="77" ht="17.55" spans="1:11">
+    <row r="77" spans="1:11">
       <c r="A77" s="30"/>
       <c r="B77" s="30"/>
       <c r="C77" s="30"/>
@@ -3515,7 +3515,7 @@
       <c r="J77" s="30"/>
       <c r="K77" s="30"/>
     </row>
-    <row r="78" ht="17.55" spans="1:11">
+    <row r="78" spans="1:11">
       <c r="A78" s="30"/>
       <c r="B78" s="30"/>
       <c r="C78" s="30"/>
@@ -3528,7 +3528,7 @@
       <c r="J78" s="30"/>
       <c r="K78" s="30"/>
     </row>
-    <row r="79" ht="17.55" spans="1:11">
+    <row r="79" spans="1:11">
       <c r="A79" s="30"/>
       <c r="B79" s="30"/>
       <c r="C79" s="30"/>
@@ -3541,7 +3541,7 @@
       <c r="J79" s="30"/>
       <c r="K79" s="30"/>
     </row>
-    <row r="80" ht="17.55" spans="1:11">
+    <row r="80" spans="1:11">
       <c r="A80" s="30"/>
       <c r="B80" s="30"/>
       <c r="C80" s="30"/>
@@ -3554,7 +3554,7 @@
       <c r="J80" s="30"/>
       <c r="K80" s="30"/>
     </row>
-    <row r="81" ht="17.55" spans="1:11">
+    <row r="81" spans="1:11">
       <c r="A81" s="30"/>
       <c r="B81" s="30"/>
       <c r="C81" s="30"/>
@@ -3567,7 +3567,7 @@
       <c r="J81" s="30"/>
       <c r="K81" s="30"/>
     </row>
-    <row r="82" ht="17.55" spans="1:11">
+    <row r="82" spans="1:11">
       <c r="A82" s="30"/>
       <c r="B82" s="30"/>
       <c r="C82" s="30"/>
@@ -3580,7 +3580,7 @@
       <c r="J82" s="30"/>
       <c r="K82" s="30"/>
     </row>
-    <row r="83" ht="17.55" spans="1:11">
+    <row r="83" spans="1:11">
       <c r="A83" s="30"/>
       <c r="B83" s="30"/>
       <c r="C83" s="30"/>
@@ -3593,7 +3593,7 @@
       <c r="J83" s="30"/>
       <c r="K83" s="30"/>
     </row>
-    <row r="84" ht="17.55" spans="1:11">
+    <row r="84" spans="1:11">
       <c r="A84" s="30"/>
       <c r="B84" s="30"/>
       <c r="C84" s="30"/>
@@ -3606,7 +3606,7 @@
       <c r="J84" s="30"/>
       <c r="K84" s="30"/>
     </row>
-    <row r="85" ht="17.55" spans="1:11">
+    <row r="85" spans="1:11">
       <c r="A85" s="30"/>
       <c r="B85" s="30"/>
       <c r="C85" s="30"/>
@@ -3619,7 +3619,7 @@
       <c r="J85" s="30"/>
       <c r="K85" s="30"/>
     </row>
-    <row r="86" ht="17.55" spans="1:11">
+    <row r="86" spans="1:11">
       <c r="A86" s="30"/>
       <c r="B86" s="30"/>
       <c r="C86" s="30"/>
@@ -3632,7 +3632,7 @@
       <c r="J86" s="30"/>
       <c r="K86" s="30"/>
     </row>
-    <row r="87" ht="17.55" spans="1:11">
+    <row r="87" spans="1:11">
       <c r="A87" s="30"/>
       <c r="B87" s="30"/>
       <c r="C87" s="30"/>
@@ -3645,7 +3645,7 @@
       <c r="J87" s="30"/>
       <c r="K87" s="30"/>
     </row>
-    <row r="88" ht="17.55" spans="1:11">
+    <row r="88" spans="1:11">
       <c r="A88" s="30"/>
       <c r="B88" s="30"/>
       <c r="C88" s="30"/>
@@ -3658,7 +3658,7 @@
       <c r="J88" s="30"/>
       <c r="K88" s="30"/>
     </row>
-    <row r="89" ht="17.55" spans="1:11">
+    <row r="89" spans="1:11">
       <c r="A89" s="30"/>
       <c r="B89" s="30"/>
       <c r="C89" s="30"/>
@@ -3671,7 +3671,7 @@
       <c r="J89" s="30"/>
       <c r="K89" s="30"/>
     </row>
-    <row r="90" ht="17.55" spans="1:11">
+    <row r="90" spans="1:11">
       <c r="A90" s="30"/>
       <c r="B90" s="30"/>
       <c r="C90" s="30"/>
@@ -3684,7 +3684,7 @@
       <c r="J90" s="30"/>
       <c r="K90" s="30"/>
     </row>
-    <row r="91" ht="17.55" spans="1:11">
+    <row r="91" spans="1:11">
       <c r="A91" s="30"/>
       <c r="B91" s="30"/>
       <c r="C91" s="30"/>
@@ -3697,7 +3697,7 @@
       <c r="J91" s="30"/>
       <c r="K91" s="30"/>
     </row>
-    <row r="92" ht="17.55" spans="1:11">
+    <row r="92" spans="1:11">
       <c r="A92" s="30"/>
       <c r="B92" s="30"/>
       <c r="C92" s="30"/>
@@ -3710,7 +3710,7 @@
       <c r="J92" s="30"/>
       <c r="K92" s="30"/>
     </row>
-    <row r="93" ht="17.55" spans="1:11">
+    <row r="93" spans="1:11">
       <c r="A93" s="30"/>
       <c r="B93" s="30"/>
       <c r="C93" s="30"/>
@@ -3723,7 +3723,7 @@
       <c r="J93" s="30"/>
       <c r="K93" s="30"/>
     </row>
-    <row r="94" ht="17.55" spans="1:11">
+    <row r="94" spans="1:11">
       <c r="A94" s="30"/>
       <c r="B94" s="30"/>
       <c r="C94" s="30"/>
@@ -3736,7 +3736,7 @@
       <c r="J94" s="30"/>
       <c r="K94" s="30"/>
     </row>
-    <row r="95" ht="17.55" spans="1:11">
+    <row r="95" spans="1:11">
       <c r="A95" s="30"/>
       <c r="B95" s="30"/>
       <c r="C95" s="30"/>
@@ -3749,7 +3749,7 @@
       <c r="J95" s="30"/>
       <c r="K95" s="30"/>
     </row>
-    <row r="96" ht="17.55" spans="1:11">
+    <row r="96" spans="1:11">
       <c r="A96" s="30"/>
       <c r="B96" s="30"/>
       <c r="C96" s="30"/>
@@ -3762,7 +3762,7 @@
       <c r="J96" s="30"/>
       <c r="K96" s="30"/>
     </row>
-    <row r="97" ht="17.55" spans="1:11">
+    <row r="97" spans="1:11">
       <c r="A97" s="30"/>
       <c r="B97" s="30"/>
       <c r="C97" s="30"/>
@@ -3775,7 +3775,7 @@
       <c r="J97" s="30"/>
       <c r="K97" s="30"/>
     </row>
-    <row r="98" ht="17.55" spans="1:11">
+    <row r="98" spans="1:11">
       <c r="A98" s="30"/>
       <c r="B98" s="30"/>
       <c r="C98" s="30"/>
@@ -3788,7 +3788,7 @@
       <c r="J98" s="30"/>
       <c r="K98" s="30"/>
     </row>
-    <row r="99" ht="17.55" spans="1:11">
+    <row r="99" spans="1:11">
       <c r="A99" s="30"/>
       <c r="B99" s="30"/>
       <c r="C99" s="30"/>
@@ -3801,7 +3801,7 @@
       <c r="J99" s="30"/>
       <c r="K99" s="30"/>
     </row>
-    <row r="100" ht="17.55" spans="1:11">
+    <row r="100" spans="1:11">
       <c r="A100" s="30"/>
       <c r="B100" s="30"/>
       <c r="C100" s="30"/>
@@ -3814,7 +3814,7 @@
       <c r="J100" s="30"/>
       <c r="K100" s="30"/>
     </row>
-    <row r="101" ht="17.55" spans="1:11">
+    <row r="101" spans="1:11">
       <c r="A101" s="30"/>
       <c r="B101" s="30"/>
       <c r="C101" s="30"/>
@@ -3827,7 +3827,7 @@
       <c r="J101" s="30"/>
       <c r="K101" s="30"/>
     </row>
-    <row r="102" ht="17.55" spans="1:11">
+    <row r="102" spans="1:11">
       <c r="A102" s="26"/>
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
@@ -3840,7 +3840,7 @@
       <c r="J102" s="26"/>
       <c r="K102" s="26"/>
     </row>
-    <row r="103" ht="17.55" spans="1:11">
+    <row r="103" spans="1:11">
       <c r="A103" s="26"/>
       <c r="B103" s="26"/>
       <c r="C103" s="26"/>
@@ -3853,7 +3853,7 @@
       <c r="J103" s="26"/>
       <c r="K103" s="26"/>
     </row>
-    <row r="104" ht="17.55" spans="1:11">
+    <row r="104" spans="1:11">
       <c r="A104" s="27"/>
       <c r="B104" s="27"/>
       <c r="C104" s="27"/>
@@ -3866,7 +3866,7 @@
       <c r="J104" s="27"/>
       <c r="K104" s="27"/>
     </row>
-    <row r="105" ht="17.55" spans="1:11">
+    <row r="105" spans="1:11">
       <c r="A105" s="30"/>
       <c r="B105" s="30"/>
       <c r="C105" s="30"/>
@@ -3879,7 +3879,7 @@
       <c r="J105" s="30"/>
       <c r="K105" s="30"/>
     </row>
-    <row r="106" ht="17.55" spans="1:11">
+    <row r="106" spans="1:11">
       <c r="A106" s="30"/>
       <c r="B106" s="30"/>
       <c r="C106" s="30"/>
@@ -3892,7 +3892,7 @@
       <c r="J106" s="30"/>
       <c r="K106" s="30"/>
     </row>
-    <row r="107" ht="17.55" spans="1:11">
+    <row r="107" spans="1:11">
       <c r="A107" s="30"/>
       <c r="B107" s="30"/>
       <c r="C107" s="30"/>
@@ -3905,7 +3905,7 @@
       <c r="J107" s="30"/>
       <c r="K107" s="30"/>
     </row>
-    <row r="108" ht="17.55" spans="1:11">
+    <row r="108" spans="1:11">
       <c r="A108" s="30"/>
       <c r="B108" s="30"/>
       <c r="C108" s="30"/>
@@ -3918,7 +3918,7 @@
       <c r="J108" s="30"/>
       <c r="K108" s="30"/>
     </row>
-    <row r="109" ht="17.55" spans="1:11">
+    <row r="109" spans="1:11">
       <c r="A109" s="30"/>
       <c r="B109" s="30"/>
       <c r="C109" s="30"/>
@@ -3931,7 +3931,7 @@
       <c r="J109" s="30"/>
       <c r="K109" s="30"/>
     </row>
-    <row r="110" ht="17.55" spans="1:11">
+    <row r="110" spans="1:11">
       <c r="A110" s="30"/>
       <c r="B110" s="30"/>
       <c r="C110" s="30"/>
@@ -3944,7 +3944,7 @@
       <c r="J110" s="30"/>
       <c r="K110" s="30"/>
     </row>
-    <row r="111" ht="17.55" spans="1:11">
+    <row r="111" spans="1:11">
       <c r="A111" s="30"/>
       <c r="B111" s="30"/>
       <c r="C111" s="30"/>
@@ -3957,7 +3957,7 @@
       <c r="J111" s="30"/>
       <c r="K111" s="30"/>
     </row>
-    <row r="112" ht="17.55" spans="1:11">
+    <row r="112" spans="1:11">
       <c r="A112" s="30"/>
       <c r="B112" s="30"/>
       <c r="C112" s="30"/>
@@ -3970,7 +3970,7 @@
       <c r="J112" s="30"/>
       <c r="K112" s="30"/>
     </row>
-    <row r="113" ht="17.55" spans="1:11">
+    <row r="113" spans="1:11">
       <c r="A113" s="30"/>
       <c r="B113" s="30"/>
       <c r="C113" s="30"/>
@@ -3983,7 +3983,7 @@
       <c r="J113" s="30"/>
       <c r="K113" s="30"/>
     </row>
-    <row r="114" ht="17.55" spans="1:11">
+    <row r="114" spans="1:11">
       <c r="A114" s="30"/>
       <c r="B114" s="30"/>
       <c r="C114" s="30"/>
@@ -3996,7 +3996,7 @@
       <c r="J114" s="30"/>
       <c r="K114" s="30"/>
     </row>
-    <row r="115" ht="17.55" spans="1:11">
+    <row r="115" spans="1:11">
       <c r="A115" s="30"/>
       <c r="B115" s="30"/>
       <c r="C115" s="30"/>
@@ -4009,7 +4009,7 @@
       <c r="J115" s="30"/>
       <c r="K115" s="30"/>
     </row>
-    <row r="116" ht="17.55" spans="1:11">
+    <row r="116" spans="1:11">
       <c r="A116" s="30"/>
       <c r="B116" s="30"/>
       <c r="C116" s="30"/>
@@ -4022,7 +4022,7 @@
       <c r="J116" s="30"/>
       <c r="K116" s="30"/>
     </row>
-    <row r="117" ht="17.55" spans="1:11">
+    <row r="117" spans="1:11">
       <c r="A117" s="30"/>
       <c r="B117" s="30"/>
       <c r="C117" s="30"/>
@@ -4035,7 +4035,7 @@
       <c r="J117" s="30"/>
       <c r="K117" s="30"/>
     </row>
-    <row r="118" ht="17.55" spans="1:11">
+    <row r="118" spans="1:11">
       <c r="A118" s="30"/>
       <c r="B118" s="30"/>
       <c r="C118" s="30"/>
@@ -4048,7 +4048,7 @@
       <c r="J118" s="30"/>
       <c r="K118" s="30"/>
     </row>
-    <row r="119" ht="17.55" spans="1:11">
+    <row r="119" spans="1:11">
       <c r="A119" s="30"/>
       <c r="B119" s="30"/>
       <c r="C119" s="30"/>
@@ -4061,7 +4061,7 @@
       <c r="J119" s="30"/>
       <c r="K119" s="30"/>
     </row>
-    <row r="120" ht="17.55" spans="1:11">
+    <row r="120" spans="1:11">
       <c r="A120" s="30"/>
       <c r="B120" s="30"/>
       <c r="C120" s="30"/>
@@ -4074,7 +4074,7 @@
       <c r="J120" s="30"/>
       <c r="K120" s="30"/>
     </row>
-    <row r="121" ht="17.55" spans="1:11">
+    <row r="121" spans="1:11">
       <c r="A121" s="30"/>
       <c r="B121" s="30"/>
       <c r="C121" s="30"/>
@@ -4087,7 +4087,7 @@
       <c r="J121" s="30"/>
       <c r="K121" s="30"/>
     </row>
-    <row r="122" ht="17.55" spans="1:11">
+    <row r="122" spans="1:11">
       <c r="A122" s="30"/>
       <c r="B122" s="30"/>
       <c r="C122" s="30"/>
@@ -4100,7 +4100,7 @@
       <c r="J122" s="30"/>
       <c r="K122" s="30"/>
     </row>
-    <row r="123" ht="17.55" spans="1:11">
+    <row r="123" spans="1:11">
       <c r="A123" s="30"/>
       <c r="B123" s="30"/>
       <c r="C123" s="30"/>
@@ -4113,7 +4113,7 @@
       <c r="J123" s="30"/>
       <c r="K123" s="30"/>
     </row>
-    <row r="124" ht="17.55" spans="1:11">
+    <row r="124" spans="1:11">
       <c r="A124" s="30"/>
       <c r="B124" s="30"/>
       <c r="C124" s="30"/>
@@ -4126,7 +4126,7 @@
       <c r="J124" s="30"/>
       <c r="K124" s="30"/>
     </row>
-    <row r="125" ht="17.55" spans="1:11">
+    <row r="125" spans="1:11">
       <c r="A125" s="30"/>
       <c r="B125" s="30"/>
       <c r="C125" s="30"/>
@@ -4139,7 +4139,7 @@
       <c r="J125" s="30"/>
       <c r="K125" s="30"/>
     </row>
-    <row r="126" ht="17.55" spans="1:11">
+    <row r="126" spans="1:11">
       <c r="A126" s="30"/>
       <c r="B126" s="30"/>
       <c r="C126" s="30"/>
@@ -4152,7 +4152,7 @@
       <c r="J126" s="30"/>
       <c r="K126" s="30"/>
     </row>
-    <row r="127" ht="17.55" spans="1:11">
+    <row r="127" spans="1:11">
       <c r="A127" s="30"/>
       <c r="B127" s="30"/>
       <c r="C127" s="30"/>
@@ -4165,7 +4165,7 @@
       <c r="J127" s="30"/>
       <c r="K127" s="30"/>
     </row>
-    <row r="128" ht="17.55" spans="1:11">
+    <row r="128" spans="1:11">
       <c r="A128" s="30"/>
       <c r="B128" s="30"/>
       <c r="C128" s="30"/>
@@ -4178,7 +4178,7 @@
       <c r="J128" s="30"/>
       <c r="K128" s="30"/>
     </row>
-    <row r="129" ht="17.55" spans="1:11">
+    <row r="129" spans="1:11">
       <c r="A129" s="30"/>
       <c r="B129" s="30"/>
       <c r="C129" s="30"/>
@@ -4191,7 +4191,7 @@
       <c r="J129" s="30"/>
       <c r="K129" s="30"/>
     </row>
-    <row r="130" ht="17.55" spans="1:11">
+    <row r="130" spans="1:11">
       <c r="A130" s="30"/>
       <c r="B130" s="30"/>
       <c r="C130" s="30"/>
@@ -4204,7 +4204,7 @@
       <c r="J130" s="30"/>
       <c r="K130" s="30"/>
     </row>
-    <row r="131" ht="17.55" spans="1:11">
+    <row r="131" spans="1:11">
       <c r="A131" s="30"/>
       <c r="B131" s="30"/>
       <c r="C131" s="30"/>
@@ -4217,7 +4217,7 @@
       <c r="J131" s="30"/>
       <c r="K131" s="30"/>
     </row>
-    <row r="132" ht="17.55" spans="1:11">
+    <row r="132" spans="1:11">
       <c r="A132" s="30"/>
       <c r="B132" s="30"/>
       <c r="C132" s="30"/>
@@ -4230,7 +4230,7 @@
       <c r="J132" s="30"/>
       <c r="K132" s="30"/>
     </row>
-    <row r="133" ht="17.55" spans="1:11">
+    <row r="133" spans="1:11">
       <c r="A133" s="30"/>
       <c r="B133" s="30"/>
       <c r="C133" s="30"/>
@@ -4243,7 +4243,7 @@
       <c r="J133" s="30"/>
       <c r="K133" s="30"/>
     </row>
-    <row r="134" ht="17.55" spans="1:11">
+    <row r="134" spans="1:11">
       <c r="A134" s="30"/>
       <c r="B134" s="30"/>
       <c r="C134" s="30"/>
@@ -4256,7 +4256,7 @@
       <c r="J134" s="30"/>
       <c r="K134" s="30"/>
     </row>
-    <row r="135" ht="17.55" spans="1:11">
+    <row r="135" spans="1:11">
       <c r="A135" s="30"/>
       <c r="B135" s="30"/>
       <c r="C135" s="30"/>
@@ -4269,7 +4269,7 @@
       <c r="J135" s="30"/>
       <c r="K135" s="30"/>
     </row>
-    <row r="136" ht="17.55" spans="1:11">
+    <row r="136" spans="1:11">
       <c r="A136" s="30"/>
       <c r="B136" s="30"/>
       <c r="C136" s="30"/>
@@ -4282,7 +4282,7 @@
       <c r="J136" s="30"/>
       <c r="K136" s="30"/>
     </row>
-    <row r="137" ht="17.55" spans="1:11">
+    <row r="137" spans="1:11">
       <c r="A137" s="30"/>
       <c r="B137" s="30"/>
       <c r="C137" s="30"/>
@@ -4295,7 +4295,7 @@
       <c r="J137" s="30"/>
       <c r="K137" s="30"/>
     </row>
-    <row r="138" ht="17.55" spans="1:11">
+    <row r="138" spans="1:11">
       <c r="A138" s="30"/>
       <c r="B138" s="30"/>
       <c r="C138" s="30"/>
@@ -4308,7 +4308,7 @@
       <c r="J138" s="30"/>
       <c r="K138" s="30"/>
     </row>
-    <row r="139" ht="17.55" spans="1:11">
+    <row r="139" spans="1:11">
       <c r="A139" s="30"/>
       <c r="B139" s="30"/>
       <c r="C139" s="30"/>
@@ -4321,7 +4321,7 @@
       <c r="J139" s="30"/>
       <c r="K139" s="30"/>
     </row>
-    <row r="140" ht="17.55" spans="1:11">
+    <row r="140" spans="1:11">
       <c r="A140" s="30"/>
       <c r="B140" s="30"/>
       <c r="C140" s="30"/>
@@ -4334,7 +4334,7 @@
       <c r="J140" s="30"/>
       <c r="K140" s="30"/>
     </row>
-    <row r="141" ht="17.55" spans="1:11">
+    <row r="141" spans="1:11">
       <c r="A141" s="30"/>
       <c r="B141" s="30"/>
       <c r="C141" s="30"/>
@@ -4347,7 +4347,7 @@
       <c r="J141" s="30"/>
       <c r="K141" s="30"/>
     </row>
-    <row r="142" ht="17.55" spans="1:11">
+    <row r="142" spans="1:11">
       <c r="A142" s="30"/>
       <c r="B142" s="30"/>
       <c r="C142" s="30"/>
@@ -4360,7 +4360,7 @@
       <c r="J142" s="30"/>
       <c r="K142" s="30"/>
     </row>
-    <row r="143" ht="17.55" spans="1:11">
+    <row r="143" spans="1:11">
       <c r="A143" s="30"/>
       <c r="B143" s="30"/>
       <c r="C143" s="30"/>
@@ -4373,7 +4373,7 @@
       <c r="J143" s="30"/>
       <c r="K143" s="30"/>
     </row>
-    <row r="144" ht="17.55" spans="1:11">
+    <row r="144" spans="1:11">
       <c r="A144" s="30"/>
       <c r="B144" s="30"/>
       <c r="C144" s="30"/>
@@ -4386,7 +4386,7 @@
       <c r="J144" s="30"/>
       <c r="K144" s="30"/>
     </row>
-    <row r="145" ht="17.55" spans="1:11">
+    <row r="145" spans="1:11">
       <c r="A145" s="30"/>
       <c r="B145" s="30"/>
       <c r="C145" s="30"/>
@@ -4399,7 +4399,7 @@
       <c r="J145" s="30"/>
       <c r="K145" s="30"/>
     </row>
-    <row r="146" ht="17.55" spans="1:11">
+    <row r="146" spans="1:11">
       <c r="A146" s="30"/>
       <c r="B146" s="30"/>
       <c r="C146" s="30"/>
@@ -7194,8 +7194,8 @@
         <f t="array" ref="B2:B300">IFERROR(INDEX(单袋比导出!$A$2:$Z$300,MATCH($A$2:$A$300,单袋比导出!$N$2:$N$300,0),MATCH(B$1,单袋比导出!$A$1:$Z$1,0)),"0")</f>
         <v>0</v>
       </c>
-      <c r="C2" s="19" t="str" cm="1">
-        <f t="array" ref="C2:C300">IFERROR(INDEX(单袋比导出!$A$2:$Z$300,MATCH($A$2:$A$300,单袋比导出!$N$2:$N$300,0),MATCH(C$1,单袋比导出!$A$1:$Z$1,0)),"0")</f>
+      <c r="C2" s="19" cm="1">
+        <f t="array" ref="C2:C300">SUMIFS(配送员履约明细表!W2:W5000,配送员履约明细表!J2:J5000,A2:A300)</f>
         <v>0</v>
       </c>
       <c r="D2" s="15" t="str" cm="1">
@@ -7246,16 +7246,16 @@
       </c>
       <c r="R2" s="21">
         <f ca="1">TODAY()</f>
-        <v>46067</v>
+        <v>46120</v>
       </c>
       <c r="S2" s="19"/>
       <c r="T2" s="19"/>
     </row>
-    <row r="3" ht="24" spans="1:115">
+    <row r="3" spans="1:115">
       <c r="B3" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C3" s="19" t="str">
+      <c r="C3" s="19">
         <v>0</v>
       </c>
       <c r="D3" s="15" t="str">
@@ -7292,7 +7292,7 @@
       <c r="B4" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C4" s="15" t="str">
+      <c r="C4" s="15">
         <v>0</v>
       </c>
       <c r="D4" s="15" t="str">
@@ -7329,7 +7329,7 @@
       <c r="B5" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C5" s="15" t="str">
+      <c r="C5" s="15">
         <v>0</v>
       </c>
       <c r="D5" s="15" t="str">
@@ -7364,7 +7364,7 @@
       <c r="B6" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C6" s="15" t="str">
+      <c r="C6" s="15">
         <v>0</v>
       </c>
       <c r="D6" s="15" t="str">
@@ -7399,7 +7399,7 @@
       <c r="B7" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C7" s="15" t="str">
+      <c r="C7" s="15">
         <v>0</v>
       </c>
       <c r="D7" s="15" t="str">
@@ -7434,7 +7434,7 @@
       <c r="B8" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C8" s="15" t="str">
+      <c r="C8" s="15">
         <v>0</v>
       </c>
       <c r="D8" s="15" t="str">
@@ -7469,7 +7469,7 @@
       <c r="B9" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C9" s="15" t="str">
+      <c r="C9" s="15">
         <v>0</v>
       </c>
       <c r="D9" s="15" t="str">
@@ -7504,7 +7504,7 @@
       <c r="B10" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C10" s="15" t="str">
+      <c r="C10" s="15">
         <v>0</v>
       </c>
       <c r="D10" s="15" t="str">
@@ -7539,7 +7539,7 @@
       <c r="B11" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C11" s="15" t="str">
+      <c r="C11" s="15">
         <v>0</v>
       </c>
       <c r="D11" s="15" t="str">
@@ -7574,7 +7574,7 @@
       <c r="B12" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C12" s="15" t="str">
+      <c r="C12" s="15">
         <v>0</v>
       </c>
       <c r="D12" s="15" t="str">
@@ -7609,7 +7609,7 @@
       <c r="B13" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C13" s="15" t="str">
+      <c r="C13" s="15">
         <v>0</v>
       </c>
       <c r="D13" s="15" t="str">
@@ -7644,7 +7644,7 @@
       <c r="B14" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C14" s="15" t="str">
+      <c r="C14" s="15">
         <v>0</v>
       </c>
       <c r="D14" s="15" t="str">
@@ -7679,7 +7679,7 @@
       <c r="B15" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C15" s="15" t="str">
+      <c r="C15" s="15">
         <v>0</v>
       </c>
       <c r="D15" s="15" t="str">
@@ -7714,7 +7714,7 @@
       <c r="B16" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C16" s="15" t="str">
+      <c r="C16" s="15">
         <v>0</v>
       </c>
       <c r="D16" s="15" t="str">
@@ -7749,7 +7749,7 @@
       <c r="B17" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C17" s="15" t="str">
+      <c r="C17" s="15">
         <v>0</v>
       </c>
       <c r="D17" s="15" t="str">
@@ -7784,7 +7784,7 @@
       <c r="B18" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C18" s="15" t="str">
+      <c r="C18" s="15">
         <v>0</v>
       </c>
       <c r="D18" s="15" t="str">
@@ -7819,7 +7819,7 @@
       <c r="B19" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C19" s="15" t="str">
+      <c r="C19" s="15">
         <v>0</v>
       </c>
       <c r="D19" s="15" t="str">
@@ -7854,7 +7854,7 @@
       <c r="B20" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C20" s="15" t="str">
+      <c r="C20" s="15">
         <v>0</v>
       </c>
       <c r="D20" s="15" t="str">
@@ -7889,7 +7889,7 @@
       <c r="B21" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C21" s="15" t="str">
+      <c r="C21" s="15">
         <v>0</v>
       </c>
       <c r="D21" s="15" t="str">
@@ -7924,7 +7924,7 @@
       <c r="B22" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C22" s="15" t="str">
+      <c r="C22" s="15">
         <v>0</v>
       </c>
       <c r="D22" s="15" t="str">
@@ -7959,7 +7959,7 @@
       <c r="B23" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C23" s="15" t="str">
+      <c r="C23" s="15">
         <v>0</v>
       </c>
       <c r="D23" s="15" t="str">
@@ -7994,7 +7994,7 @@
       <c r="B24" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C24" s="15" t="str">
+      <c r="C24" s="15">
         <v>0</v>
       </c>
       <c r="D24" s="15" t="str">
@@ -8029,7 +8029,7 @@
       <c r="B25" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C25" s="15" t="str">
+      <c r="C25" s="15">
         <v>0</v>
       </c>
       <c r="D25" s="15" t="str">
@@ -8064,7 +8064,7 @@
       <c r="B26" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C26" s="15" t="str">
+      <c r="C26" s="15">
         <v>0</v>
       </c>
       <c r="D26" s="15" t="str">
@@ -8099,7 +8099,7 @@
       <c r="B27" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C27" s="15" t="str">
+      <c r="C27" s="15">
         <v>0</v>
       </c>
       <c r="D27" s="15" t="str">
@@ -8134,7 +8134,7 @@
       <c r="B28" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C28" s="15" t="str">
+      <c r="C28" s="15">
         <v>0</v>
       </c>
       <c r="D28" s="15" t="str">
@@ -8169,7 +8169,7 @@
       <c r="B29" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C29" s="15" t="str">
+      <c r="C29" s="15">
         <v>0</v>
       </c>
       <c r="D29" s="15" t="str">
@@ -8204,7 +8204,7 @@
       <c r="B30" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C30" s="15" t="str">
+      <c r="C30" s="15">
         <v>0</v>
       </c>
       <c r="D30" s="15" t="str">
@@ -8239,7 +8239,7 @@
       <c r="B31" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C31" s="15" t="str">
+      <c r="C31" s="15">
         <v>0</v>
       </c>
       <c r="D31" s="15" t="str">
@@ -8274,7 +8274,7 @@
       <c r="B32" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C32" s="15" t="str">
+      <c r="C32" s="15">
         <v>0</v>
       </c>
       <c r="D32" s="15" t="str">
@@ -8309,7 +8309,7 @@
       <c r="B33" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C33" s="15" t="str">
+      <c r="C33" s="15">
         <v>0</v>
       </c>
       <c r="D33" s="15" t="str">
@@ -8344,7 +8344,7 @@
       <c r="B34" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C34" s="15" t="str">
+      <c r="C34" s="15">
         <v>0</v>
       </c>
       <c r="D34" s="15" t="str">
@@ -8379,7 +8379,7 @@
       <c r="B35" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C35" s="15" t="str">
+      <c r="C35" s="15">
         <v>0</v>
       </c>
       <c r="D35" s="15" t="str">
@@ -8414,7 +8414,7 @@
       <c r="B36" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C36" s="15" t="str">
+      <c r="C36" s="15">
         <v>0</v>
       </c>
       <c r="D36" s="15" t="str">
@@ -8449,7 +8449,7 @@
       <c r="B37" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C37" s="15" t="str">
+      <c r="C37" s="15">
         <v>0</v>
       </c>
       <c r="D37" s="15" t="str">
@@ -8484,7 +8484,7 @@
       <c r="B38" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C38" s="15" t="str">
+      <c r="C38" s="15">
         <v>0</v>
       </c>
       <c r="D38" s="15" t="str">
@@ -8519,7 +8519,7 @@
       <c r="B39" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C39" s="15" t="str">
+      <c r="C39" s="15">
         <v>0</v>
       </c>
       <c r="D39" s="15" t="str">
@@ -8554,7 +8554,7 @@
       <c r="B40" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C40" s="15" t="str">
+      <c r="C40" s="15">
         <v>0</v>
       </c>
       <c r="D40" s="15" t="str">
@@ -8589,7 +8589,7 @@
       <c r="B41" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C41" s="15" t="str">
+      <c r="C41" s="15">
         <v>0</v>
       </c>
       <c r="D41" s="15" t="str">
@@ -8624,7 +8624,7 @@
       <c r="B42" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C42" s="15" t="str">
+      <c r="C42" s="15">
         <v>0</v>
       </c>
       <c r="D42" s="15" t="str">
@@ -8659,7 +8659,7 @@
       <c r="B43" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C43" s="15" t="str">
+      <c r="C43" s="15">
         <v>0</v>
       </c>
       <c r="D43" s="15" t="str">
@@ -8694,7 +8694,7 @@
       <c r="B44" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C44" s="15" t="str">
+      <c r="C44" s="15">
         <v>0</v>
       </c>
       <c r="D44" s="15" t="str">
@@ -8729,7 +8729,7 @@
       <c r="B45" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C45" s="15" t="str">
+      <c r="C45" s="15">
         <v>0</v>
       </c>
       <c r="D45" s="15" t="str">
@@ -8764,7 +8764,7 @@
       <c r="B46" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C46" s="15" t="str">
+      <c r="C46" s="15">
         <v>0</v>
       </c>
       <c r="D46" s="15" t="str">
@@ -8799,7 +8799,7 @@
       <c r="B47" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C47" s="15" t="str">
+      <c r="C47" s="15">
         <v>0</v>
       </c>
       <c r="D47" s="15" t="str">
@@ -8834,7 +8834,7 @@
       <c r="B48" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C48" s="15" t="str">
+      <c r="C48" s="15">
         <v>0</v>
       </c>
       <c r="D48" s="15" t="str">
@@ -8869,7 +8869,7 @@
       <c r="B49" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C49" s="15" t="str">
+      <c r="C49" s="15">
         <v>0</v>
       </c>
       <c r="D49" s="15" t="str">
@@ -8904,7 +8904,7 @@
       <c r="B50" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C50" s="15" t="str">
+      <c r="C50" s="15">
         <v>0</v>
       </c>
       <c r="D50" s="15" t="str">
@@ -8939,7 +8939,7 @@
       <c r="B51" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C51" s="15" t="str">
+      <c r="C51" s="15">
         <v>0</v>
       </c>
       <c r="D51" s="15" t="str">
@@ -8974,7 +8974,7 @@
       <c r="B52" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C52" s="15" t="str">
+      <c r="C52" s="15">
         <v>0</v>
       </c>
       <c r="D52" s="15" t="str">
@@ -9009,7 +9009,7 @@
       <c r="B53" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C53" s="15" t="str">
+      <c r="C53" s="15">
         <v>0</v>
       </c>
       <c r="D53" s="15" t="str">
@@ -9044,7 +9044,7 @@
       <c r="B54" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C54" s="15" t="str">
+      <c r="C54" s="15">
         <v>0</v>
       </c>
       <c r="D54" s="15" t="str">
@@ -9079,7 +9079,7 @@
       <c r="B55" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C55" s="15" t="str">
+      <c r="C55" s="15">
         <v>0</v>
       </c>
       <c r="D55" s="15" t="str">
@@ -9114,7 +9114,7 @@
       <c r="B56" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C56" s="15" t="str">
+      <c r="C56" s="15">
         <v>0</v>
       </c>
       <c r="D56" s="15" t="str">
@@ -9149,7 +9149,7 @@
       <c r="B57" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C57" s="15" t="str">
+      <c r="C57" s="15">
         <v>0</v>
       </c>
       <c r="D57" s="15" t="str">
@@ -9184,7 +9184,7 @@
       <c r="B58" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C58" s="15" t="str">
+      <c r="C58" s="15">
         <v>0</v>
       </c>
       <c r="D58" s="15" t="str">
@@ -9219,7 +9219,7 @@
       <c r="B59" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C59" s="15" t="str">
+      <c r="C59" s="15">
         <v>0</v>
       </c>
       <c r="D59" s="15" t="str">
@@ -9254,7 +9254,7 @@
       <c r="B60" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C60" s="15" t="str">
+      <c r="C60" s="15">
         <v>0</v>
       </c>
       <c r="D60" s="15" t="str">
@@ -9289,7 +9289,7 @@
       <c r="B61" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C61" s="15" t="str">
+      <c r="C61" s="15">
         <v>0</v>
       </c>
       <c r="D61" s="15" t="str">
@@ -9324,7 +9324,7 @@
       <c r="B62" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C62" s="15" t="str">
+      <c r="C62" s="15">
         <v>0</v>
       </c>
       <c r="D62" s="15" t="str">
@@ -9359,7 +9359,7 @@
       <c r="B63" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C63" s="15" t="str">
+      <c r="C63" s="15">
         <v>0</v>
       </c>
       <c r="D63" s="15" t="str">
@@ -9394,7 +9394,7 @@
       <c r="B64" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C64" s="15" t="str">
+      <c r="C64" s="15">
         <v>0</v>
       </c>
       <c r="D64" s="15" t="str">
@@ -9429,7 +9429,7 @@
       <c r="B65" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C65" s="15" t="str">
+      <c r="C65" s="15">
         <v>0</v>
       </c>
       <c r="D65" s="15" t="str">
@@ -9464,7 +9464,7 @@
       <c r="B66" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C66" s="15" t="str">
+      <c r="C66" s="15">
         <v>0</v>
       </c>
       <c r="D66" s="15" t="str">
@@ -9499,7 +9499,7 @@
       <c r="B67" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C67" s="15" t="str">
+      <c r="C67" s="15">
         <v>0</v>
       </c>
       <c r="D67" s="15" t="str">
@@ -9534,7 +9534,7 @@
       <c r="B68" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C68" s="15" t="str">
+      <c r="C68" s="15">
         <v>0</v>
       </c>
       <c r="D68" s="15" t="str">
@@ -9569,7 +9569,7 @@
       <c r="B69" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C69" s="15" t="str">
+      <c r="C69" s="15">
         <v>0</v>
       </c>
       <c r="D69" s="15" t="str">
@@ -9604,7 +9604,7 @@
       <c r="B70" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C70" s="15" t="str">
+      <c r="C70" s="15">
         <v>0</v>
       </c>
       <c r="D70" s="15" t="str">
@@ -9639,7 +9639,7 @@
       <c r="B71" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C71" s="15" t="str">
+      <c r="C71" s="15">
         <v>0</v>
       </c>
       <c r="D71" s="15" t="str">
@@ -9674,7 +9674,7 @@
       <c r="B72" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C72" s="15" t="str">
+      <c r="C72" s="15">
         <v>0</v>
       </c>
       <c r="D72" s="15" t="str">
@@ -9709,7 +9709,7 @@
       <c r="B73" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C73" s="15" t="str">
+      <c r="C73" s="15">
         <v>0</v>
       </c>
       <c r="D73" s="15" t="str">
@@ -9744,7 +9744,7 @@
       <c r="B74" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C74" s="15" t="str">
+      <c r="C74" s="15">
         <v>0</v>
       </c>
       <c r="D74" s="15" t="str">
@@ -9779,7 +9779,7 @@
       <c r="B75" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C75" s="15" t="str">
+      <c r="C75" s="15">
         <v>0</v>
       </c>
       <c r="D75" s="15" t="str">
@@ -9814,7 +9814,7 @@
       <c r="B76" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C76" s="15" t="str">
+      <c r="C76" s="15">
         <v>0</v>
       </c>
       <c r="D76" s="15" t="str">
@@ -9849,7 +9849,7 @@
       <c r="B77" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C77" s="15" t="str">
+      <c r="C77" s="15">
         <v>0</v>
       </c>
       <c r="D77" s="15" t="str">
@@ -9884,7 +9884,7 @@
       <c r="B78" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C78" s="15" t="str">
+      <c r="C78" s="15">
         <v>0</v>
       </c>
       <c r="D78" s="15" t="str">
@@ -9919,7 +9919,7 @@
       <c r="B79" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C79" s="15" t="str">
+      <c r="C79" s="15">
         <v>0</v>
       </c>
       <c r="D79" s="15" t="str">
@@ -9954,7 +9954,7 @@
       <c r="B80" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C80" s="15" t="str">
+      <c r="C80" s="15">
         <v>0</v>
       </c>
       <c r="D80" s="15" t="str">
@@ -9989,7 +9989,7 @@
       <c r="B81" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C81" s="15" t="str">
+      <c r="C81" s="15">
         <v>0</v>
       </c>
       <c r="D81" s="15" t="str">
@@ -10024,7 +10024,7 @@
       <c r="B82" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C82" s="15" t="str">
+      <c r="C82" s="15">
         <v>0</v>
       </c>
       <c r="D82" s="15" t="str">
@@ -10059,7 +10059,7 @@
       <c r="B83" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C83" s="15" t="str">
+      <c r="C83" s="15">
         <v>0</v>
       </c>
       <c r="D83" s="15" t="str">
@@ -10094,7 +10094,7 @@
       <c r="B84" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C84" s="15" t="str">
+      <c r="C84" s="15">
         <v>0</v>
       </c>
       <c r="D84" s="15" t="str">
@@ -10129,7 +10129,7 @@
       <c r="B85" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C85" s="15" t="str">
+      <c r="C85" s="15">
         <v>0</v>
       </c>
       <c r="D85" s="15" t="str">
@@ -10164,7 +10164,7 @@
       <c r="B86" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C86" s="15" t="str">
+      <c r="C86" s="15">
         <v>0</v>
       </c>
       <c r="D86" s="15" t="str">
@@ -10199,7 +10199,7 @@
       <c r="B87" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C87" s="15" t="str">
+      <c r="C87" s="15">
         <v>0</v>
       </c>
       <c r="D87" s="15" t="str">
@@ -10234,7 +10234,7 @@
       <c r="B88" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C88" s="15" t="str">
+      <c r="C88" s="15">
         <v>0</v>
       </c>
       <c r="D88" s="15" t="str">
@@ -10269,7 +10269,7 @@
       <c r="B89" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C89" s="15" t="str">
+      <c r="C89" s="15">
         <v>0</v>
       </c>
       <c r="D89" s="15" t="str">
@@ -10304,7 +10304,7 @@
       <c r="B90" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C90" s="15" t="str">
+      <c r="C90" s="15">
         <v>0</v>
       </c>
       <c r="D90" s="15" t="str">
@@ -10339,7 +10339,7 @@
       <c r="B91" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C91" s="15" t="str">
+      <c r="C91" s="15">
         <v>0</v>
       </c>
       <c r="D91" s="15" t="str">
@@ -10374,7 +10374,7 @@
       <c r="B92" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C92" s="15" t="str">
+      <c r="C92" s="15">
         <v>0</v>
       </c>
       <c r="D92" s="15" t="str">
@@ -10409,7 +10409,7 @@
       <c r="B93" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C93" s="15" t="str">
+      <c r="C93" s="15">
         <v>0</v>
       </c>
       <c r="D93" s="15" t="str">
@@ -10444,7 +10444,7 @@
       <c r="B94" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C94" s="15" t="str">
+      <c r="C94" s="15">
         <v>0</v>
       </c>
       <c r="D94" s="15" t="str">
@@ -10479,7 +10479,7 @@
       <c r="B95" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C95" s="15" t="str">
+      <c r="C95" s="15">
         <v>0</v>
       </c>
       <c r="D95" s="15" t="str">
@@ -10514,7 +10514,7 @@
       <c r="B96" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C96" s="15" t="str">
+      <c r="C96" s="15">
         <v>0</v>
       </c>
       <c r="D96" s="15" t="str">
@@ -10549,7 +10549,7 @@
       <c r="B97" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C97" s="15" t="str">
+      <c r="C97" s="15">
         <v>0</v>
       </c>
       <c r="D97" s="15" t="str">
@@ -10584,7 +10584,7 @@
       <c r="B98" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C98" s="15" t="str">
+      <c r="C98" s="15">
         <v>0</v>
       </c>
       <c r="D98" s="15" t="str">
@@ -10619,7 +10619,7 @@
       <c r="B99" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C99" s="15" t="str">
+      <c r="C99" s="15">
         <v>0</v>
       </c>
       <c r="D99" s="15" t="str">
@@ -10654,7 +10654,7 @@
       <c r="B100" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C100" s="15" t="str">
+      <c r="C100" s="15">
         <v>0</v>
       </c>
       <c r="D100" s="15" t="str">
@@ -10689,7 +10689,7 @@
       <c r="B101" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C101" s="15" t="str">
+      <c r="C101" s="15">
         <v>0</v>
       </c>
       <c r="D101" s="15" t="str">
@@ -10724,7 +10724,7 @@
       <c r="B102" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C102" s="15" t="str">
+      <c r="C102" s="15">
         <v>0</v>
       </c>
       <c r="D102" s="15" t="str">
@@ -10759,7 +10759,7 @@
       <c r="B103" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C103" s="15" t="str">
+      <c r="C103" s="15">
         <v>0</v>
       </c>
       <c r="D103" s="15" t="str">
@@ -10794,7 +10794,7 @@
       <c r="B104" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C104" s="15" t="str">
+      <c r="C104" s="15">
         <v>0</v>
       </c>
       <c r="D104" s="15" t="str">
@@ -10829,7 +10829,7 @@
       <c r="B105" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C105" s="15" t="str">
+      <c r="C105" s="15">
         <v>0</v>
       </c>
       <c r="D105" s="15" t="str">
@@ -10864,7 +10864,7 @@
       <c r="B106" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C106" s="15" t="str">
+      <c r="C106" s="15">
         <v>0</v>
       </c>
       <c r="D106" s="15" t="str">
@@ -10899,7 +10899,7 @@
       <c r="B107" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C107" s="15" t="str">
+      <c r="C107" s="15">
         <v>0</v>
       </c>
       <c r="D107" s="15" t="str">
@@ -10934,7 +10934,7 @@
       <c r="B108" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C108" s="15" t="str">
+      <c r="C108" s="15">
         <v>0</v>
       </c>
       <c r="D108" s="15" t="str">
@@ -10969,7 +10969,7 @@
       <c r="B109" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C109" s="15" t="str">
+      <c r="C109" s="15">
         <v>0</v>
       </c>
       <c r="D109" s="15" t="str">
@@ -11004,7 +11004,7 @@
       <c r="B110" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C110" s="15" t="str">
+      <c r="C110" s="15">
         <v>0</v>
       </c>
       <c r="D110" s="15" t="str">
@@ -11039,7 +11039,7 @@
       <c r="B111" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C111" s="15" t="str">
+      <c r="C111" s="15">
         <v>0</v>
       </c>
       <c r="D111" s="15" t="str">
@@ -11074,7 +11074,7 @@
       <c r="B112" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C112" s="15" t="str">
+      <c r="C112" s="15">
         <v>0</v>
       </c>
       <c r="D112" s="15" t="str">
@@ -11109,7 +11109,7 @@
       <c r="B113" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C113" s="15" t="str">
+      <c r="C113" s="15">
         <v>0</v>
       </c>
       <c r="D113" s="15" t="str">
@@ -11144,7 +11144,7 @@
       <c r="B114" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C114" s="15" t="str">
+      <c r="C114" s="15">
         <v>0</v>
       </c>
       <c r="D114" s="15" t="str">
@@ -11179,7 +11179,7 @@
       <c r="B115" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C115" s="15" t="str">
+      <c r="C115" s="15">
         <v>0</v>
       </c>
       <c r="D115" s="15" t="str">
@@ -11214,7 +11214,7 @@
       <c r="B116" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C116" s="15" t="str">
+      <c r="C116" s="15">
         <v>0</v>
       </c>
       <c r="D116" s="15" t="str">
@@ -11249,7 +11249,7 @@
       <c r="B117" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C117" s="15" t="str">
+      <c r="C117" s="15">
         <v>0</v>
       </c>
       <c r="D117" s="15" t="str">
@@ -11284,7 +11284,7 @@
       <c r="B118" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C118" s="15" t="str">
+      <c r="C118" s="15">
         <v>0</v>
       </c>
       <c r="D118" s="15" t="str">
@@ -11319,7 +11319,7 @@
       <c r="B119" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C119" s="15" t="str">
+      <c r="C119" s="15">
         <v>0</v>
       </c>
       <c r="D119" s="15" t="str">
@@ -11354,7 +11354,7 @@
       <c r="B120" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C120" s="15" t="str">
+      <c r="C120" s="15">
         <v>0</v>
       </c>
       <c r="D120" s="15" t="str">
@@ -11389,7 +11389,7 @@
       <c r="B121" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C121" s="15" t="str">
+      <c r="C121" s="15">
         <v>0</v>
       </c>
       <c r="D121" s="15" t="str">
@@ -11424,7 +11424,7 @@
       <c r="B122" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C122" s="15" t="str">
+      <c r="C122" s="15">
         <v>0</v>
       </c>
       <c r="D122" s="15" t="str">
@@ -11459,7 +11459,7 @@
       <c r="B123" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C123" s="15" t="str">
+      <c r="C123" s="15">
         <v>0</v>
       </c>
       <c r="D123" s="15" t="str">
@@ -11494,7 +11494,7 @@
       <c r="B124" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C124" s="15" t="str">
+      <c r="C124" s="15">
         <v>0</v>
       </c>
       <c r="D124" s="15" t="str">
@@ -11529,7 +11529,7 @@
       <c r="B125" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C125" s="15" t="str">
+      <c r="C125" s="15">
         <v>0</v>
       </c>
       <c r="D125" s="15" t="str">
@@ -11564,7 +11564,7 @@
       <c r="B126" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C126" s="15" t="str">
+      <c r="C126" s="15">
         <v>0</v>
       </c>
       <c r="D126" s="15" t="str">
@@ -11599,7 +11599,7 @@
       <c r="B127" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C127" s="15" t="str">
+      <c r="C127" s="15">
         <v>0</v>
       </c>
       <c r="D127" s="15" t="str">
@@ -11634,7 +11634,7 @@
       <c r="B128" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C128" s="15" t="str">
+      <c r="C128" s="15">
         <v>0</v>
       </c>
       <c r="D128" s="15" t="str">
@@ -11669,7 +11669,7 @@
       <c r="B129" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C129" s="15" t="str">
+      <c r="C129" s="15">
         <v>0</v>
       </c>
       <c r="D129" s="15" t="str">
@@ -11704,7 +11704,7 @@
       <c r="B130" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C130" s="15" t="str">
+      <c r="C130" s="15">
         <v>0</v>
       </c>
       <c r="D130" s="15" t="str">
@@ -11739,7 +11739,7 @@
       <c r="B131" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C131" s="15" t="str">
+      <c r="C131" s="15">
         <v>0</v>
       </c>
       <c r="D131" s="15" t="str">
@@ -11774,7 +11774,7 @@
       <c r="B132" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C132" s="15" t="str">
+      <c r="C132" s="15">
         <v>0</v>
       </c>
       <c r="D132" s="15" t="str">
@@ -11809,7 +11809,7 @@
       <c r="B133" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C133" s="15" t="str">
+      <c r="C133" s="15">
         <v>0</v>
       </c>
       <c r="D133" s="15" t="str">
@@ -11844,7 +11844,7 @@
       <c r="B134" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C134" s="15" t="str">
+      <c r="C134" s="15">
         <v>0</v>
       </c>
       <c r="D134" s="15" t="str">
@@ -11879,7 +11879,7 @@
       <c r="B135" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C135" s="15" t="str">
+      <c r="C135" s="15">
         <v>0</v>
       </c>
       <c r="D135" s="15" t="str">
@@ -11914,7 +11914,7 @@
       <c r="B136" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C136" s="15" t="str">
+      <c r="C136" s="15">
         <v>0</v>
       </c>
       <c r="D136" s="15" t="str">
@@ -11949,7 +11949,7 @@
       <c r="B137" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C137" s="15" t="str">
+      <c r="C137" s="15">
         <v>0</v>
       </c>
       <c r="D137" s="15" t="str">
@@ -11984,7 +11984,7 @@
       <c r="B138" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C138" s="15" t="str">
+      <c r="C138" s="15">
         <v>0</v>
       </c>
       <c r="D138" s="15" t="str">
@@ -12019,7 +12019,7 @@
       <c r="B139" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C139" s="15" t="str">
+      <c r="C139" s="15">
         <v>0</v>
       </c>
       <c r="D139" s="15" t="str">
@@ -12054,7 +12054,7 @@
       <c r="B140" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C140" s="15" t="str">
+      <c r="C140" s="15">
         <v>0</v>
       </c>
       <c r="D140" s="15" t="str">
@@ -12089,7 +12089,7 @@
       <c r="B141" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C141" s="15" t="str">
+      <c r="C141" s="15">
         <v>0</v>
       </c>
       <c r="D141" s="15" t="str">
@@ -12124,7 +12124,7 @@
       <c r="B142" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C142" s="15" t="str">
+      <c r="C142" s="15">
         <v>0</v>
       </c>
       <c r="D142" s="15" t="str">
@@ -12159,7 +12159,7 @@
       <c r="B143" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C143" s="15" t="str">
+      <c r="C143" s="15">
         <v>0</v>
       </c>
       <c r="D143" s="15" t="str">
@@ -12194,7 +12194,7 @@
       <c r="B144" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C144" s="15" t="str">
+      <c r="C144" s="15">
         <v>0</v>
       </c>
       <c r="D144" s="15" t="str">
@@ -12229,7 +12229,7 @@
       <c r="B145" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C145" s="15" t="str">
+      <c r="C145" s="15">
         <v>0</v>
       </c>
       <c r="D145" s="15" t="str">
@@ -12264,7 +12264,7 @@
       <c r="B146" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C146" s="15" t="str">
+      <c r="C146" s="15">
         <v>0</v>
       </c>
       <c r="D146" s="15" t="str">
@@ -12299,7 +12299,7 @@
       <c r="B147" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C147" s="15" t="str">
+      <c r="C147" s="15">
         <v>0</v>
       </c>
       <c r="D147" s="15" t="str">
@@ -12334,7 +12334,7 @@
       <c r="B148" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C148" s="15" t="str">
+      <c r="C148" s="15">
         <v>0</v>
       </c>
       <c r="D148" s="15" t="str">
@@ -12369,7 +12369,7 @@
       <c r="B149" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C149" s="15" t="str">
+      <c r="C149" s="15">
         <v>0</v>
       </c>
       <c r="D149" s="15" t="str">
@@ -12404,7 +12404,7 @@
       <c r="B150" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C150" s="15" t="str">
+      <c r="C150" s="15">
         <v>0</v>
       </c>
       <c r="D150" s="15" t="str">
@@ -12439,7 +12439,7 @@
       <c r="B151" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C151" s="15" t="str">
+      <c r="C151" s="15">
         <v>0</v>
       </c>
       <c r="D151" s="15" t="str">
@@ -12474,7 +12474,7 @@
       <c r="B152" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C152" s="15" t="str">
+      <c r="C152" s="15">
         <v>0</v>
       </c>
       <c r="D152" s="15" t="str">
@@ -12509,7 +12509,7 @@
       <c r="B153" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C153" s="15" t="str">
+      <c r="C153" s="15">
         <v>0</v>
       </c>
       <c r="D153" s="15" t="str">
@@ -12544,7 +12544,7 @@
       <c r="B154" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C154" s="15" t="str">
+      <c r="C154" s="15">
         <v>0</v>
       </c>
       <c r="D154" s="15" t="str">
@@ -12579,7 +12579,7 @@
       <c r="B155" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C155" s="15" t="str">
+      <c r="C155" s="15">
         <v>0</v>
       </c>
       <c r="D155" s="15" t="str">
@@ -12614,7 +12614,7 @@
       <c r="B156" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C156" s="15" t="str">
+      <c r="C156" s="15">
         <v>0</v>
       </c>
       <c r="D156" s="15" t="str">
@@ -12649,7 +12649,7 @@
       <c r="B157" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C157" s="15" t="str">
+      <c r="C157" s="15">
         <v>0</v>
       </c>
       <c r="D157" s="15" t="str">
@@ -12684,7 +12684,7 @@
       <c r="B158" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C158" s="15" t="str">
+      <c r="C158" s="15">
         <v>0</v>
       </c>
       <c r="D158" s="15" t="str">
@@ -12719,7 +12719,7 @@
       <c r="B159" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C159" s="15" t="str">
+      <c r="C159" s="15">
         <v>0</v>
       </c>
       <c r="D159" s="15" t="str">
@@ -12754,7 +12754,7 @@
       <c r="B160" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C160" s="15" t="str">
+      <c r="C160" s="15">
         <v>0</v>
       </c>
       <c r="D160" s="15" t="str">
@@ -12789,7 +12789,7 @@
       <c r="B161" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C161" s="15" t="str">
+      <c r="C161" s="15">
         <v>0</v>
       </c>
       <c r="D161" s="15" t="str">
@@ -12824,7 +12824,7 @@
       <c r="B162" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C162" s="15" t="str">
+      <c r="C162" s="15">
         <v>0</v>
       </c>
       <c r="D162" s="15" t="str">
@@ -12859,7 +12859,7 @@
       <c r="B163" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C163" s="15" t="str">
+      <c r="C163" s="15">
         <v>0</v>
       </c>
       <c r="D163" s="15" t="str">
@@ -12894,7 +12894,7 @@
       <c r="B164" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C164" s="15" t="str">
+      <c r="C164" s="15">
         <v>0</v>
       </c>
       <c r="D164" s="15" t="str">
@@ -12929,7 +12929,7 @@
       <c r="B165" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C165" s="15" t="str">
+      <c r="C165" s="15">
         <v>0</v>
       </c>
       <c r="D165" s="15" t="str">
@@ -12964,7 +12964,7 @@
       <c r="B166" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C166" s="15" t="str">
+      <c r="C166" s="15">
         <v>0</v>
       </c>
       <c r="D166" s="15" t="str">
@@ -12999,7 +12999,7 @@
       <c r="B167" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C167" s="15" t="str">
+      <c r="C167" s="15">
         <v>0</v>
       </c>
       <c r="D167" s="15" t="str">
@@ -13034,7 +13034,7 @@
       <c r="B168" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C168" s="15" t="str">
+      <c r="C168" s="15">
         <v>0</v>
       </c>
       <c r="D168" s="15" t="str">
@@ -13069,7 +13069,7 @@
       <c r="B169" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C169" s="15" t="str">
+      <c r="C169" s="15">
         <v>0</v>
       </c>
       <c r="D169" s="15" t="str">
@@ -13104,7 +13104,7 @@
       <c r="B170" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C170" s="15" t="str">
+      <c r="C170" s="15">
         <v>0</v>
       </c>
       <c r="D170" s="15" t="str">
@@ -13139,7 +13139,7 @@
       <c r="B171" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C171" s="15" t="str">
+      <c r="C171" s="15">
         <v>0</v>
       </c>
       <c r="D171" s="15" t="str">
@@ -13174,7 +13174,7 @@
       <c r="B172" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C172" s="15" t="str">
+      <c r="C172" s="15">
         <v>0</v>
       </c>
       <c r="D172" s="15" t="str">
@@ -13209,7 +13209,7 @@
       <c r="B173" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C173" s="15" t="str">
+      <c r="C173" s="15">
         <v>0</v>
       </c>
       <c r="D173" s="15" t="str">
@@ -13244,7 +13244,7 @@
       <c r="B174" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C174" s="15" t="str">
+      <c r="C174" s="15">
         <v>0</v>
       </c>
       <c r="D174" s="15" t="str">
@@ -13279,7 +13279,7 @@
       <c r="B175" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C175" s="15" t="str">
+      <c r="C175" s="15">
         <v>0</v>
       </c>
       <c r="D175" s="15" t="str">
@@ -13314,7 +13314,7 @@
       <c r="B176" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C176" s="15" t="str">
+      <c r="C176" s="15">
         <v>0</v>
       </c>
       <c r="D176" s="15" t="str">
@@ -13349,7 +13349,7 @@
       <c r="B177" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C177" s="15" t="str">
+      <c r="C177" s="15">
         <v>0</v>
       </c>
       <c r="D177" s="15" t="str">
@@ -13384,7 +13384,7 @@
       <c r="B178" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C178" s="15" t="str">
+      <c r="C178" s="15">
         <v>0</v>
       </c>
       <c r="D178" s="15" t="str">
@@ -13419,7 +13419,7 @@
       <c r="B179" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C179" s="15" t="str">
+      <c r="C179" s="15">
         <v>0</v>
       </c>
       <c r="D179" s="15" t="str">
@@ -13454,7 +13454,7 @@
       <c r="B180" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C180" s="15" t="str">
+      <c r="C180" s="15">
         <v>0</v>
       </c>
       <c r="D180" s="15" t="str">
@@ -13489,7 +13489,7 @@
       <c r="B181" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C181" s="15" t="str">
+      <c r="C181" s="15">
         <v>0</v>
       </c>
       <c r="D181" s="15" t="str">
@@ -13524,7 +13524,7 @@
       <c r="B182" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C182" s="15" t="str">
+      <c r="C182" s="15">
         <v>0</v>
       </c>
       <c r="D182" s="15" t="str">
@@ -13559,7 +13559,7 @@
       <c r="B183" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C183" s="15" t="str">
+      <c r="C183" s="15">
         <v>0</v>
       </c>
       <c r="D183" s="15" t="str">
@@ -13594,7 +13594,7 @@
       <c r="B184" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C184" s="15" t="str">
+      <c r="C184" s="15">
         <v>0</v>
       </c>
       <c r="D184" s="15" t="str">
@@ -13629,7 +13629,7 @@
       <c r="B185" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C185" s="15" t="str">
+      <c r="C185" s="15">
         <v>0</v>
       </c>
       <c r="D185" s="15" t="str">
@@ -13664,7 +13664,7 @@
       <c r="B186" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C186" s="15" t="str">
+      <c r="C186" s="15">
         <v>0</v>
       </c>
       <c r="D186" s="15" t="str">
@@ -13699,7 +13699,7 @@
       <c r="B187" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C187" s="15" t="str">
+      <c r="C187" s="15">
         <v>0</v>
       </c>
       <c r="D187" s="15" t="str">
@@ -13734,7 +13734,7 @@
       <c r="B188" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C188" s="15" t="str">
+      <c r="C188" s="15">
         <v>0</v>
       </c>
       <c r="D188" s="15" t="str">
@@ -13769,7 +13769,7 @@
       <c r="B189" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C189" s="15" t="str">
+      <c r="C189" s="15">
         <v>0</v>
       </c>
       <c r="D189" s="15" t="str">
@@ -13804,7 +13804,7 @@
       <c r="B190" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C190" s="15" t="str">
+      <c r="C190" s="15">
         <v>0</v>
       </c>
       <c r="D190" s="15" t="str">
@@ -13839,7 +13839,7 @@
       <c r="B191" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C191" s="15" t="str">
+      <c r="C191" s="15">
         <v>0</v>
       </c>
       <c r="D191" s="15" t="str">
@@ -13874,7 +13874,7 @@
       <c r="B192" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C192" s="15" t="str">
+      <c r="C192" s="15">
         <v>0</v>
       </c>
       <c r="D192" s="15" t="str">
@@ -13909,7 +13909,7 @@
       <c r="B193" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C193" s="15" t="str">
+      <c r="C193" s="15">
         <v>0</v>
       </c>
       <c r="D193" s="15" t="str">
@@ -13944,7 +13944,7 @@
       <c r="B194" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C194" s="15" t="str">
+      <c r="C194" s="15">
         <v>0</v>
       </c>
       <c r="D194" s="15" t="str">
@@ -13979,7 +13979,7 @@
       <c r="B195" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C195" s="15" t="str">
+      <c r="C195" s="15">
         <v>0</v>
       </c>
       <c r="D195" s="15" t="str">
@@ -14014,7 +14014,7 @@
       <c r="B196" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C196" s="15" t="str">
+      <c r="C196" s="15">
         <v>0</v>
       </c>
       <c r="D196" s="15" t="str">
@@ -14049,7 +14049,7 @@
       <c r="B197" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C197" s="15" t="str">
+      <c r="C197" s="15">
         <v>0</v>
       </c>
       <c r="D197" s="15" t="str">
@@ -14084,7 +14084,7 @@
       <c r="B198" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C198" s="15" t="str">
+      <c r="C198" s="15">
         <v>0</v>
       </c>
       <c r="D198" s="15" t="str">
@@ -14119,7 +14119,7 @@
       <c r="B199" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C199" s="15" t="str">
+      <c r="C199" s="15">
         <v>0</v>
       </c>
       <c r="D199" s="15" t="str">
@@ -14154,7 +14154,7 @@
       <c r="B200" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C200" s="15" t="str">
+      <c r="C200" s="15">
         <v>0</v>
       </c>
       <c r="D200" s="15" t="str">
@@ -14189,7 +14189,7 @@
       <c r="B201" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C201" s="15" t="str">
+      <c r="C201" s="15">
         <v>0</v>
       </c>
       <c r="D201" s="15" t="str">
@@ -14218,7 +14218,7 @@
       <c r="B202" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C202" s="15" t="str">
+      <c r="C202" s="15">
         <v>0</v>
       </c>
       <c r="D202" s="15" t="str">
@@ -14247,7 +14247,7 @@
       <c r="B203" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C203" s="15" t="str">
+      <c r="C203" s="15">
         <v>0</v>
       </c>
       <c r="D203" s="15" t="str">
@@ -14276,7 +14276,7 @@
       <c r="B204" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C204" s="15" t="str">
+      <c r="C204" s="15">
         <v>0</v>
       </c>
       <c r="D204" s="15" t="str">
@@ -14305,7 +14305,7 @@
       <c r="B205" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C205" s="15" t="str">
+      <c r="C205" s="15">
         <v>0</v>
       </c>
       <c r="D205" s="15" t="str">
@@ -14334,7 +14334,7 @@
       <c r="B206" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C206" s="15" t="str">
+      <c r="C206" s="15">
         <v>0</v>
       </c>
       <c r="D206" s="15" t="str">
@@ -14363,7 +14363,7 @@
       <c r="B207" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C207" s="15" t="str">
+      <c r="C207" s="15">
         <v>0</v>
       </c>
       <c r="D207" s="15" t="str">
@@ -14392,7 +14392,7 @@
       <c r="B208" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C208" s="15" t="str">
+      <c r="C208" s="15">
         <v>0</v>
       </c>
       <c r="D208" s="15" t="str">
@@ -14421,7 +14421,7 @@
       <c r="B209" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C209" s="15" t="str">
+      <c r="C209" s="15">
         <v>0</v>
       </c>
       <c r="D209" s="15" t="str">
@@ -14450,7 +14450,7 @@
       <c r="B210" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C210" s="15" t="str">
+      <c r="C210" s="15">
         <v>0</v>
       </c>
       <c r="D210" s="15" t="str">
@@ -14479,7 +14479,7 @@
       <c r="B211" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C211" s="15" t="str">
+      <c r="C211" s="15">
         <v>0</v>
       </c>
       <c r="D211" s="15" t="str">
@@ -14508,7 +14508,7 @@
       <c r="B212" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C212" s="15" t="str">
+      <c r="C212" s="15">
         <v>0</v>
       </c>
       <c r="D212" s="15" t="str">
@@ -14537,7 +14537,7 @@
       <c r="B213" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C213" s="15" t="str">
+      <c r="C213" s="15">
         <v>0</v>
       </c>
       <c r="D213" s="15" t="str">
@@ -14566,7 +14566,7 @@
       <c r="B214" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C214" s="15" t="str">
+      <c r="C214" s="15">
         <v>0</v>
       </c>
       <c r="D214" s="15" t="str">
@@ -14595,7 +14595,7 @@
       <c r="B215" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C215" s="15" t="str">
+      <c r="C215" s="15">
         <v>0</v>
       </c>
       <c r="D215" s="15" t="str">
@@ -14624,7 +14624,7 @@
       <c r="B216" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C216" s="15" t="str">
+      <c r="C216" s="15">
         <v>0</v>
       </c>
       <c r="D216" s="15" t="str">
@@ -14653,7 +14653,7 @@
       <c r="B217" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C217" s="15" t="str">
+      <c r="C217" s="15">
         <v>0</v>
       </c>
       <c r="D217" s="15" t="str">
@@ -14682,7 +14682,7 @@
       <c r="B218" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C218" s="15" t="str">
+      <c r="C218" s="15">
         <v>0</v>
       </c>
       <c r="D218" s="15" t="str">
@@ -14711,7 +14711,7 @@
       <c r="B219" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C219" s="15" t="str">
+      <c r="C219" s="15">
         <v>0</v>
       </c>
       <c r="D219" s="15" t="str">
@@ -14740,7 +14740,7 @@
       <c r="B220" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C220" s="15" t="str">
+      <c r="C220" s="15">
         <v>0</v>
       </c>
       <c r="D220" s="15" t="str">
@@ -14769,7 +14769,7 @@
       <c r="B221" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C221" s="15" t="str">
+      <c r="C221" s="15">
         <v>0</v>
       </c>
       <c r="D221" s="15" t="str">
@@ -14798,7 +14798,7 @@
       <c r="B222" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C222" s="15" t="str">
+      <c r="C222" s="15">
         <v>0</v>
       </c>
       <c r="D222" s="15" t="str">
@@ -14827,7 +14827,7 @@
       <c r="B223" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C223" s="15" t="str">
+      <c r="C223" s="15">
         <v>0</v>
       </c>
       <c r="D223" s="15" t="str">
@@ -14856,7 +14856,7 @@
       <c r="B224" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C224" s="15" t="str">
+      <c r="C224" s="15">
         <v>0</v>
       </c>
       <c r="D224" s="15" t="str">
@@ -14885,7 +14885,7 @@
       <c r="B225" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C225" s="15" t="str">
+      <c r="C225" s="15">
         <v>0</v>
       </c>
       <c r="D225" s="15" t="str">
@@ -14914,7 +14914,7 @@
       <c r="B226" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C226" s="15" t="str">
+      <c r="C226" s="15">
         <v>0</v>
       </c>
       <c r="D226" s="15" t="str">
@@ -14943,7 +14943,7 @@
       <c r="B227" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C227" s="15" t="str">
+      <c r="C227" s="15">
         <v>0</v>
       </c>
       <c r="D227" s="15" t="str">
@@ -14972,7 +14972,7 @@
       <c r="B228" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C228" s="15" t="str">
+      <c r="C228" s="15">
         <v>0</v>
       </c>
       <c r="D228" s="15" t="str">
@@ -15001,7 +15001,7 @@
       <c r="B229" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C229" s="15" t="str">
+      <c r="C229" s="15">
         <v>0</v>
       </c>
       <c r="D229" s="15" t="str">
@@ -15030,7 +15030,7 @@
       <c r="B230" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C230" s="15" t="str">
+      <c r="C230" s="15">
         <v>0</v>
       </c>
       <c r="D230" s="15" t="str">
@@ -15059,7 +15059,7 @@
       <c r="B231" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C231" s="15" t="str">
+      <c r="C231" s="15">
         <v>0</v>
       </c>
       <c r="D231" s="15" t="str">
@@ -15088,7 +15088,7 @@
       <c r="B232" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C232" s="15" t="str">
+      <c r="C232" s="15">
         <v>0</v>
       </c>
       <c r="D232" s="15" t="str">
@@ -15117,7 +15117,7 @@
       <c r="B233" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C233" s="15" t="str">
+      <c r="C233" s="15">
         <v>0</v>
       </c>
       <c r="D233" s="15" t="str">
@@ -15146,7 +15146,7 @@
       <c r="B234" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C234" s="15" t="str">
+      <c r="C234" s="15">
         <v>0</v>
       </c>
       <c r="D234" s="15" t="str">
@@ -15175,7 +15175,7 @@
       <c r="B235" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C235" s="15" t="str">
+      <c r="C235" s="15">
         <v>0</v>
       </c>
       <c r="D235" s="15" t="str">
@@ -15204,7 +15204,7 @@
       <c r="B236" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C236" s="15" t="str">
+      <c r="C236" s="15">
         <v>0</v>
       </c>
       <c r="D236" s="15" t="str">
@@ -15233,7 +15233,7 @@
       <c r="B237" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C237" s="15" t="str">
+      <c r="C237" s="15">
         <v>0</v>
       </c>
       <c r="D237" s="15" t="str">
@@ -15262,7 +15262,7 @@
       <c r="B238" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C238" s="15" t="str">
+      <c r="C238" s="15">
         <v>0</v>
       </c>
       <c r="D238" s="15" t="str">
@@ -15291,7 +15291,7 @@
       <c r="B239" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C239" s="15" t="str">
+      <c r="C239" s="15">
         <v>0</v>
       </c>
       <c r="D239" s="15" t="str">
@@ -15320,7 +15320,7 @@
       <c r="B240" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C240" s="15" t="str">
+      <c r="C240" s="15">
         <v>0</v>
       </c>
       <c r="D240" s="15" t="str">
@@ -15349,7 +15349,7 @@
       <c r="B241" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C241" s="15" t="str">
+      <c r="C241" s="15">
         <v>0</v>
       </c>
       <c r="D241" s="15" t="str">
@@ -15378,7 +15378,7 @@
       <c r="B242" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C242" s="15" t="str">
+      <c r="C242" s="15">
         <v>0</v>
       </c>
       <c r="D242" s="15" t="str">
@@ -15407,7 +15407,7 @@
       <c r="B243" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C243" s="15" t="str">
+      <c r="C243" s="15">
         <v>0</v>
       </c>
       <c r="D243" s="15" t="str">
@@ -15436,7 +15436,7 @@
       <c r="B244" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C244" s="15" t="str">
+      <c r="C244" s="15">
         <v>0</v>
       </c>
       <c r="D244" s="15" t="str">
@@ -15465,7 +15465,7 @@
       <c r="B245" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C245" s="15" t="str">
+      <c r="C245" s="15">
         <v>0</v>
       </c>
       <c r="D245" s="15" t="str">
@@ -15494,7 +15494,7 @@
       <c r="B246" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C246" s="15" t="str">
+      <c r="C246" s="15">
         <v>0</v>
       </c>
       <c r="D246" s="15" t="str">
@@ -15523,7 +15523,7 @@
       <c r="B247" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C247" s="15" t="str">
+      <c r="C247" s="15">
         <v>0</v>
       </c>
       <c r="D247" s="15" t="str">
@@ -15552,7 +15552,7 @@
       <c r="B248" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C248" s="15" t="str">
+      <c r="C248" s="15">
         <v>0</v>
       </c>
       <c r="D248" s="15" t="str">
@@ -15581,7 +15581,7 @@
       <c r="B249" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C249" s="15" t="str">
+      <c r="C249" s="15">
         <v>0</v>
       </c>
       <c r="D249" s="15" t="str">
@@ -15610,7 +15610,7 @@
       <c r="B250" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C250" s="15" t="str">
+      <c r="C250" s="15">
         <v>0</v>
       </c>
       <c r="D250" s="15" t="str">
@@ -15639,7 +15639,7 @@
       <c r="B251" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C251" s="15" t="str">
+      <c r="C251" s="15">
         <v>0</v>
       </c>
       <c r="D251" s="15" t="str">
@@ -15668,7 +15668,7 @@
       <c r="B252" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C252" s="15" t="str">
+      <c r="C252" s="15">
         <v>0</v>
       </c>
       <c r="D252" s="15" t="str">
@@ -15697,7 +15697,7 @@
       <c r="B253" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C253" s="15" t="str">
+      <c r="C253" s="15">
         <v>0</v>
       </c>
       <c r="D253" s="15" t="str">
@@ -15726,7 +15726,7 @@
       <c r="B254" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C254" s="15" t="str">
+      <c r="C254" s="15">
         <v>0</v>
       </c>
       <c r="D254" s="15" t="str">
@@ -15755,7 +15755,7 @@
       <c r="B255" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C255" s="15" t="str">
+      <c r="C255" s="15">
         <v>0</v>
       </c>
       <c r="D255" s="15" t="str">
@@ -15784,7 +15784,7 @@
       <c r="B256" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C256" s="15" t="str">
+      <c r="C256" s="15">
         <v>0</v>
       </c>
       <c r="D256" s="15" t="str">
@@ -15813,7 +15813,7 @@
       <c r="B257" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C257" s="15" t="str">
+      <c r="C257" s="15">
         <v>0</v>
       </c>
       <c r="D257" s="15" t="str">
@@ -15842,7 +15842,7 @@
       <c r="B258" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C258" s="15" t="str">
+      <c r="C258" s="15">
         <v>0</v>
       </c>
       <c r="D258" s="15" t="str">
@@ -15871,7 +15871,7 @@
       <c r="B259" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C259" s="15" t="str">
+      <c r="C259" s="15">
         <v>0</v>
       </c>
       <c r="D259" s="15" t="str">
@@ -15900,7 +15900,7 @@
       <c r="B260" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C260" s="15" t="str">
+      <c r="C260" s="15">
         <v>0</v>
       </c>
       <c r="D260" s="15" t="str">
@@ -15929,7 +15929,7 @@
       <c r="B261" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C261" s="15" t="str">
+      <c r="C261" s="15">
         <v>0</v>
       </c>
       <c r="D261" s="15" t="str">
@@ -15958,7 +15958,7 @@
       <c r="B262" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C262" s="15" t="str">
+      <c r="C262" s="15">
         <v>0</v>
       </c>
       <c r="D262" s="15" t="str">
@@ -15987,7 +15987,7 @@
       <c r="B263" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C263" s="15" t="str">
+      <c r="C263" s="15">
         <v>0</v>
       </c>
       <c r="D263" s="15" t="str">
@@ -16016,7 +16016,7 @@
       <c r="B264" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C264" s="15" t="str">
+      <c r="C264" s="15">
         <v>0</v>
       </c>
       <c r="D264" s="15" t="str">
@@ -16045,7 +16045,7 @@
       <c r="B265" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C265" s="15" t="str">
+      <c r="C265" s="15">
         <v>0</v>
       </c>
       <c r="D265" s="15" t="str">
@@ -16074,7 +16074,7 @@
       <c r="B266" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C266" s="15" t="str">
+      <c r="C266" s="15">
         <v>0</v>
       </c>
       <c r="D266" s="15" t="str">
@@ -16103,7 +16103,7 @@
       <c r="B267" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C267" s="15" t="str">
+      <c r="C267" s="15">
         <v>0</v>
       </c>
       <c r="D267" s="15" t="str">
@@ -16132,7 +16132,7 @@
       <c r="B268" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C268" s="15" t="str">
+      <c r="C268" s="15">
         <v>0</v>
       </c>
       <c r="D268" s="15" t="str">
@@ -16161,7 +16161,7 @@
       <c r="B269" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C269" s="15" t="str">
+      <c r="C269" s="15">
         <v>0</v>
       </c>
       <c r="D269" s="15" t="str">
@@ -16190,7 +16190,7 @@
       <c r="B270" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C270" s="15" t="str">
+      <c r="C270" s="15">
         <v>0</v>
       </c>
       <c r="D270" s="15" t="str">
@@ -16219,7 +16219,7 @@
       <c r="B271" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C271" s="15" t="str">
+      <c r="C271" s="15">
         <v>0</v>
       </c>
       <c r="D271" s="15" t="str">
@@ -16248,7 +16248,7 @@
       <c r="B272" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C272" s="15" t="str">
+      <c r="C272" s="15">
         <v>0</v>
       </c>
       <c r="D272" s="15" t="str">
@@ -16277,7 +16277,7 @@
       <c r="B273" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C273" s="15" t="str">
+      <c r="C273" s="15">
         <v>0</v>
       </c>
       <c r="D273" s="15" t="str">
@@ -16306,7 +16306,7 @@
       <c r="B274" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C274" s="15" t="str">
+      <c r="C274" s="15">
         <v>0</v>
       </c>
       <c r="D274" s="15" t="str">
@@ -16335,7 +16335,7 @@
       <c r="B275" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C275" s="15" t="str">
+      <c r="C275" s="15">
         <v>0</v>
       </c>
       <c r="D275" s="15" t="str">
@@ -16364,7 +16364,7 @@
       <c r="B276" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C276" s="15" t="str">
+      <c r="C276" s="15">
         <v>0</v>
       </c>
       <c r="D276" s="15" t="str">
@@ -16393,7 +16393,7 @@
       <c r="B277" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C277" s="15" t="str">
+      <c r="C277" s="15">
         <v>0</v>
       </c>
       <c r="D277" s="15" t="str">
@@ -16422,7 +16422,7 @@
       <c r="B278" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C278" s="15" t="str">
+      <c r="C278" s="15">
         <v>0</v>
       </c>
       <c r="D278" s="15" t="str">
@@ -16451,7 +16451,7 @@
       <c r="B279" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C279" s="15" t="str">
+      <c r="C279" s="15">
         <v>0</v>
       </c>
       <c r="D279" s="15" t="str">
@@ -16480,7 +16480,7 @@
       <c r="B280" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C280" s="15" t="str">
+      <c r="C280" s="15">
         <v>0</v>
       </c>
       <c r="D280" s="15" t="str">
@@ -16509,7 +16509,7 @@
       <c r="B281" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C281" s="15" t="str">
+      <c r="C281" s="15">
         <v>0</v>
       </c>
       <c r="D281" s="15" t="str">
@@ -16538,7 +16538,7 @@
       <c r="B282" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C282" s="15" t="str">
+      <c r="C282" s="15">
         <v>0</v>
       </c>
       <c r="D282" s="15" t="str">
@@ -16567,7 +16567,7 @@
       <c r="B283" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C283" s="15" t="str">
+      <c r="C283" s="15">
         <v>0</v>
       </c>
       <c r="D283" s="15" t="str">
@@ -16596,7 +16596,7 @@
       <c r="B284" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C284" s="15" t="str">
+      <c r="C284" s="15">
         <v>0</v>
       </c>
       <c r="D284" s="15" t="str">
@@ -16625,7 +16625,7 @@
       <c r="B285" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C285" s="15" t="str">
+      <c r="C285" s="15">
         <v>0</v>
       </c>
       <c r="D285" s="15" t="str">
@@ -16654,7 +16654,7 @@
       <c r="B286" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C286" s="15" t="str">
+      <c r="C286" s="15">
         <v>0</v>
       </c>
       <c r="D286" s="15" t="str">
@@ -16683,7 +16683,7 @@
       <c r="B287" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C287" s="15" t="str">
+      <c r="C287" s="15">
         <v>0</v>
       </c>
       <c r="D287" s="15" t="str">
@@ -16712,7 +16712,7 @@
       <c r="B288" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C288" s="15" t="str">
+      <c r="C288" s="15">
         <v>0</v>
       </c>
       <c r="D288" s="15" t="str">
@@ -16741,7 +16741,7 @@
       <c r="B289" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C289" s="15" t="str">
+      <c r="C289" s="15">
         <v>0</v>
       </c>
       <c r="D289" s="15" t="str">
@@ -16770,7 +16770,7 @@
       <c r="B290" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C290" s="15" t="str">
+      <c r="C290" s="15">
         <v>0</v>
       </c>
       <c r="D290" s="15" t="str">
@@ -16799,7 +16799,7 @@
       <c r="B291" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C291" s="15" t="str">
+      <c r="C291" s="15">
         <v>0</v>
       </c>
       <c r="D291" s="15" t="str">
@@ -16828,7 +16828,7 @@
       <c r="B292" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C292" s="15" t="str">
+      <c r="C292" s="15">
         <v>0</v>
       </c>
       <c r="D292" s="15" t="str">
@@ -16857,7 +16857,7 @@
       <c r="B293" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C293" s="15" t="str">
+      <c r="C293" s="15">
         <v>0</v>
       </c>
       <c r="D293" s="15" t="str">
@@ -16886,7 +16886,7 @@
       <c r="B294" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C294" s="15" t="str">
+      <c r="C294" s="15">
         <v>0</v>
       </c>
       <c r="D294" s="15" t="str">
@@ -16915,7 +16915,7 @@
       <c r="B295" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C295" s="15" t="str">
+      <c r="C295" s="15">
         <v>0</v>
       </c>
       <c r="D295" s="15" t="str">
@@ -16944,7 +16944,7 @@
       <c r="B296" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C296" s="15" t="str">
+      <c r="C296" s="15">
         <v>0</v>
       </c>
       <c r="D296" s="15" t="str">
@@ -16973,7 +16973,7 @@
       <c r="B297" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C297" s="15" t="str">
+      <c r="C297" s="15">
         <v>0</v>
       </c>
       <c r="D297" s="15" t="str">
@@ -17002,7 +17002,7 @@
       <c r="B298" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C298" s="15" t="str">
+      <c r="C298" s="15">
         <v>0</v>
       </c>
       <c r="D298" s="15" t="str">
@@ -17031,7 +17031,7 @@
       <c r="B299" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C299" s="15" t="str">
+      <c r="C299" s="15">
         <v>0</v>
       </c>
       <c r="D299" s="15" t="str">
@@ -17060,7 +17060,7 @@
       <c r="B300" s="15" t="str">
         <v>0</v>
       </c>
-      <c r="C300" s="15" t="str">
+      <c r="C300" s="15">
         <v>0</v>
       </c>
       <c r="D300" s="15" t="str">
@@ -17127,7 +17127,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="3" t="str">
         <f ca="1">TEXT(TODAY(),"yyyy年m月")</f>
-        <v>2026年2月</v>
+        <v>2026年4月</v>
       </c>
       <c r="F1" s="3"/>
     </row>
